--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -647,7 +647,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-05 10:22</t>
+          <t>Son Güncelleme: 2026-06-10 13:37</t>
         </is>
       </c>
       <c r="B3" s="3" t="n"/>
@@ -1261,7 +1261,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-05 10:22</t>
+          <t>Son Güncelleme: 2026-06-10 13:37</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -2229,7 +2229,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-05 10:22</t>
+          <t>Son Güncelleme: 2026-06-10 13:37</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -3061,7 +3061,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-05 10:22</t>
+          <t>Son Güncelleme: 2026-06-10 13:37</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -3180,7 +3180,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-05 10:22</t>
+          <t>Son Güncelleme: 2026-06-10 13:37</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -3431,7 +3431,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-05 10:22</t>
+          <t>Son Güncelleme: 2026-06-10 13:37</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -3556,7 +3556,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-05 10:22</t>
+          <t>Son Güncelleme: 2026-06-10 13:37</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -3633,7 +3633,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="29" t="n">
-        <v>940000</v>
+        <v>1360000</v>
       </c>
       <c r="H4" s="30" t="n">
         <v>0</v>
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="29" t="n">
-        <v>940000</v>
+        <v>1360000</v>
       </c>
       <c r="H5" s="30" t="n">
         <v>0</v>
@@ -3693,7 +3693,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="29" t="n">
-        <v>940000</v>
+        <v>1360000</v>
       </c>
       <c r="H6" s="30" t="n">
         <v>0</v>
@@ -3723,7 +3723,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="29" t="n">
-        <v>940000</v>
+        <v>1360000</v>
       </c>
       <c r="H7" s="30" t="n">
         <v>0</v>
@@ -3753,7 +3753,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>940000</v>
+        <v>1360000</v>
       </c>
       <c r="H8" s="30" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="29" t="n">
-        <v>940000</v>
+        <v>1360000</v>
       </c>
       <c r="H9" s="30" t="n">
         <v>0</v>
@@ -3813,7 +3813,7 @@
         <v>-3.637978807091713e-12</v>
       </c>
       <c r="G10" s="29" t="n">
-        <v>940000</v>
+        <v>1360000</v>
       </c>
       <c r="H10" s="30" t="n">
         <v>0</v>
@@ -3843,7 +3843,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="29" t="n">
-        <v>940000</v>
+        <v>1360000</v>
       </c>
       <c r="H11" s="30" t="n">
         <v>0</v>
@@ -3873,7 +3873,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="29" t="n">
-        <v>940000</v>
+        <v>1360000</v>
       </c>
       <c r="H12" s="30" t="n">
         <v>0</v>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YONETICI_OZETI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PORTFOY_ONERISI" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ILK_20_SIRALAMA" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AL_SAT_OZET" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PORTFOY_DEGISIMI" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIYASA_REJIMI" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAPER_TRADE" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="YONETICI_OZETI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="PORTFOY_ONERISI" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ILK_20_SIRALAMA" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="AL_SAT_OZET" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="PORTFOY_DEGISIMI" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="PIYASA_REJIMI" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="PAPER_TRADE" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$25</definedName>
@@ -629,7 +629,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-24 01:23</t>
+          <t>Son Güncelleme: 2026-06-24 05:56</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1012,7 +1012,7 @@
         <v>0.0768720785569736</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>830.864036650928</v>
+        <v>830.8640366509281</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>425.0952530103654</v>
@@ -1044,16 +1044,16 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.09261351611588012</v>
+        <v>0.09261351611588006</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>9261.351611588012</v>
+        <v>9261.351611588007</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0426715939840771</v>
+        <v>0.0426715939840769</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>395.1966357134618</v>
+        <v>395.1966357134597</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>149.8319048735307</v>
@@ -1062,7 +1062,7 @@
         <v>136.1580975269861</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.8130455715182764</v>
+        <v>0.8130455715182726</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
@@ -1085,16 +1085,16 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.09145120548407606</v>
+        <v>0.09145120548407609</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>9145.120548407607</v>
+        <v>9145.120548407609</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>0.0433601726374674</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>396.5340057694044</v>
+        <v>396.5340057694045</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>42.08914952339957</v>
@@ -1103,7 +1103,7 @@
         <v>38.0275160674077</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.7563941226758241</v>
+        <v>0.7563941226758264</v>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-24 01:23</t>
+          <t>Son Güncelleme: 2026-06-24 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1560,7 +1560,7 @@
         <v>0.0213779187417526</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>0.1020952413749239</v>
+        <v>0.1020952413749238</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>377.5937136635377</v>
@@ -1842,7 +1842,7 @@
         <v>-0.0082889988742848</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>0.0426715939840771</v>
+        <v>0.0426715939840769</v>
       </c>
       <c r="G15" s="19" t="n">
         <v>0.1446541396482852</v>
@@ -1896,7 +1896,7 @@
         <v>40.34000015258789</v>
       </c>
       <c r="E16" s="19" t="n">
-        <v>-0.0573248407643312</v>
+        <v>-0.057324840764331</v>
       </c>
       <c r="F16" s="19" t="n">
         <v>0.0433601726374674</v>
@@ -1953,16 +1953,16 @@
         <v>113.1999969482422</v>
       </c>
       <c r="E17" s="22" t="n">
-        <v>-0.0669128100843053</v>
+        <v>-0.0669128100843052</v>
       </c>
       <c r="F17" s="22" t="n">
         <v>-0.0163197887030124</v>
       </c>
       <c r="G17" s="22" t="n">
-        <v>0.0289375192237391</v>
+        <v>0.0289375192237388</v>
       </c>
       <c r="H17" s="21" t="n">
-        <v>105.6254670509005</v>
+        <v>105.6254670509006</v>
       </c>
       <c r="I17" s="21" t="n">
         <v>111.3525969168652</v>
@@ -1971,7 +1971,7 @@
         <v>116.4757240360591</v>
       </c>
       <c r="K17" s="21" t="n">
-        <v>105.6254670509005</v>
+        <v>105.6254670509006</v>
       </c>
       <c r="L17" s="20" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-24 01:23</t>
+          <t>Son Güncelleme: 2026-06-24 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="E6" s="16" t="n">
-        <v>-0.0299835584767572</v>
+        <v>-0.0299835584767574</v>
       </c>
       <c r="F6" s="16" t="n">
         <v>0.1213361981009177</v>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="J6" s="16" t="n">
-        <v>0.0211148533864321</v>
+        <v>0.0211148533864322</v>
       </c>
       <c r="K6" s="16" t="n">
         <v>0.0213779187417526</v>
@@ -2266,7 +2266,7 @@
         <v>0.1653136531365313</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>0.8699667862938347</v>
+        <v>0.8699667862938349</v>
       </c>
       <c r="H7" s="19" t="n">
         <v>-0.0591229013786693</v>
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="J7" s="19" t="n">
-        <v>0.0310679439959384</v>
+        <v>0.0310679439959383</v>
       </c>
       <c r="K7" s="19" t="n">
         <v>0.0768720785569736</v>
@@ -2309,7 +2309,7 @@
         <v>0.1429801894918174</v>
       </c>
       <c r="G8" s="22" t="n">
-        <v>0.4539139831828924</v>
+        <v>0.4539139831828926</v>
       </c>
       <c r="H8" s="22" t="n">
         <v>-0.2081217061911366</v>
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="J10" s="22" t="n">
-        <v>0.0228216736000703</v>
+        <v>0.0228216736000704</v>
       </c>
       <c r="K10" s="22" t="n">
         <v>-0.0276025019756407</v>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="E11" s="19" t="n">
-        <v>0.1749795041904276</v>
+        <v>0.1749795041904278</v>
       </c>
       <c r="F11" s="19" t="n">
         <v>0.106639870007295</v>
@@ -2452,7 +2452,7 @@
         <v>0.0262418217864421</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>0.0426715939840771</v>
+        <v>0.0426715939840769</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>0.0570968227884278</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>0.4655377772831777</v>
+        <v>0.4655377772831774</v>
       </c>
       <c r="G12" s="19" t="n">
         <v>0.6648414617414236</v>
@@ -2518,10 +2518,10 @@
         </is>
       </c>
       <c r="E13" s="22" t="n">
-        <v>0.0629107694670627</v>
+        <v>0.06291076946706289</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>0.0619136826322126</v>
+        <v>0.0619136826322128</v>
       </c>
       <c r="G13" s="22" t="n">
         <v>0.1418368479304974</v>
@@ -2564,10 +2564,10 @@
         <v>0.0345423149419388</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>-0.1816940257117537</v>
+        <v>-0.1816940257117536</v>
       </c>
       <c r="G14" s="24" t="n">
-        <v>-0.0253416715336882</v>
+        <v>-0.025341671533688</v>
       </c>
       <c r="H14" s="24" t="n">
         <v>0.1964250089917667</v>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="J14" s="24" t="n">
-        <v>0.022792917168649</v>
+        <v>0.0227929171686489</v>
       </c>
       <c r="K14" s="24" t="n">
         <v>0.1212597571915075</v>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="J15" s="24" t="n">
-        <v>0.0216298884764837</v>
+        <v>0.0216298884764838</v>
       </c>
       <c r="K15" s="24" t="n">
         <v>0.0194030930076112</v>
@@ -2667,7 +2667,7 @@
         <v>0.0217920353963226</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.009701613552635499</v>
+        <v>0.0097016135526356</v>
       </c>
     </row>
     <row r="17">
@@ -2690,13 +2690,13 @@
         </is>
       </c>
       <c r="E17" s="24" t="n">
-        <v>0.0371797344514563</v>
+        <v>0.0371797344514566</v>
       </c>
       <c r="F17" s="24" t="n">
         <v>0.0601449391773718</v>
       </c>
       <c r="G17" s="24" t="n">
-        <v>0.2087071438141818</v>
+        <v>0.2087071438141816</v>
       </c>
       <c r="H17" s="24" t="n">
         <v>-0.2858393418307774</v>
@@ -2733,7 +2733,7 @@
         </is>
       </c>
       <c r="E18" s="24" t="n">
-        <v>-0.0921431863137641</v>
+        <v>-0.092143186313764</v>
       </c>
       <c r="F18" s="24" t="n">
         <v>-0.1285291334718965</v>
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="J18" s="24" t="n">
-        <v>0.023247051091997</v>
+        <v>0.0232470510919971</v>
       </c>
       <c r="K18" s="24" t="n">
         <v>0.1002252478096075</v>
@@ -2782,7 +2782,7 @@
         <v>-0.1188034318451188</v>
       </c>
       <c r="G19" s="24" t="n">
-        <v>-0.0427112219541819</v>
+        <v>-0.042711221954182</v>
       </c>
       <c r="H19" s="24" t="n">
         <v>-0.2797685248578938</v>
@@ -2819,13 +2819,13 @@
         </is>
       </c>
       <c r="E20" s="24" t="n">
-        <v>-0.1274762778640684</v>
+        <v>-0.1274762778640682</v>
       </c>
       <c r="F20" s="24" t="n">
-        <v>-0.0029527296674942</v>
+        <v>-0.0029527296674941</v>
       </c>
       <c r="G20" s="24" t="n">
-        <v>0.2016607055424879</v>
+        <v>0.2016607055424881</v>
       </c>
       <c r="H20" s="24" t="n">
         <v>-0.3414386978886042</v>
@@ -2872,7 +2872,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-24 01:23</t>
+          <t>Son Güncelleme: 2026-06-24 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2991,7 +2991,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-24 01:23</t>
+          <t>Son Güncelleme: 2026-06-24 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3242,7 +3242,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-24 01:23</t>
+          <t>Son Güncelleme: 2026-06-24 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14729.7001953125</v>
+        <v>14539.599609375</v>
       </c>
     </row>
     <row r="5">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>12472.33203125</v>
+        <v>12490.64252929687</v>
       </c>
     </row>
     <row r="6">
@@ -3367,7 +3367,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-24 01:23</t>
+          <t>Son Güncelleme: 2026-06-24 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3444,7 +3444,7 @@
         <v>837.2925543086967</v>
       </c>
       <c r="G4" s="25" t="n">
-        <v>2277611.882914566</v>
+        <v>2311235.193725377</v>
       </c>
       <c r="H4" s="26" t="n">
         <v>0.0748467743222782</v>
@@ -3474,7 +3474,7 @@
         <v>-988.1583320280206</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>2277611.882914566</v>
+        <v>2311235.193725377</v>
       </c>
       <c r="H5" s="26" t="n">
         <v>0.0748467743222782</v>
@@ -3504,7 +3504,7 @@
         <v>1673.436127495303</v>
       </c>
       <c r="G6" s="25" t="n">
-        <v>2277611.882914566</v>
+        <v>2311235.193725377</v>
       </c>
       <c r="H6" s="26" t="n">
         <v>0.0748467743222782</v>
@@ -3534,7 +3534,7 @@
         <v>-86.53860825758602</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>2277611.882914566</v>
+        <v>2311235.193725377</v>
       </c>
       <c r="H7" s="26" t="n">
         <v>0.0748467743222782</v>
@@ -3564,7 +3564,7 @@
         <v>545.7748465300665</v>
       </c>
       <c r="G8" s="25" t="n">
-        <v>2277611.882914566</v>
+        <v>2311235.193725377</v>
       </c>
       <c r="H8" s="26" t="n">
         <v>0.0748467743222782</v>
@@ -3594,7 +3594,7 @@
         <v>540.6591394445386</v>
       </c>
       <c r="G9" s="25" t="n">
-        <v>2277611.882914566</v>
+        <v>2311235.193725377</v>
       </c>
       <c r="H9" s="26" t="n">
         <v>0.0748467743222782</v>
@@ -3624,7 +3624,7 @@
         <v>626.2626262626254</v>
       </c>
       <c r="G10" s="25" t="n">
-        <v>2277611.882914566</v>
+        <v>2311235.193725377</v>
       </c>
       <c r="H10" s="26" t="n">
         <v>0.0748467743222782</v>
@@ -3654,7 +3654,7 @@
         <v>839.84375</v>
       </c>
       <c r="G11" s="25" t="n">
-        <v>2277611.882914566</v>
+        <v>2311235.193725377</v>
       </c>
       <c r="H11" s="26" t="n">
         <v>0.0748467743222782</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="25" t="n">
-        <v>2277611.882914566</v>
+        <v>2311235.193725377</v>
       </c>
       <c r="H12" s="26" t="n">
         <v>0.0748467743222782</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="25" t="n">
-        <v>2277611.882914566</v>
+        <v>2311235.193725377</v>
       </c>
       <c r="H13" s="26" t="n">
         <v>0.0748467743222782</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="25" t="n">
-        <v>2277611.882914566</v>
+        <v>2311235.193725377</v>
       </c>
       <c r="H14" s="26" t="n">
         <v>0.0748467743222782</v>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -629,7 +629,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-27 05:44</t>
+          <t>Son Güncelleme: 2026-06-28 06:05</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -960,25 +960,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1286261716247234</v>
+        <v>0.1286261716247233</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>12862.61716247234</v>
+        <v>12862.61716247233</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.1111298169216609</v>
+        <v>0.1111298169216608</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1429.420290398965</v>
+        <v>1429.420290398962</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>361.1171904995398</v>
+        <v>361.1171904995397</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>306.9595859379225</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>2.002015606474425</v>
+        <v>2.002015606474419</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.09876010286701303</v>
+        <v>0.09876010286701312</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>9876.010286701303</v>
+        <v>9876.010286701312</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0576923532547533</v>
+        <v>0.0576923532547535</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>569.770274207949</v>
+        <v>569.7702742079515</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>43.00577092194722</v>
+        <v>43.00577092194723</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>38.16395266206861</v>
+        <v>38.16395266206862</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.9397943629868905</v>
+        <v>0.939794362986896</v>
       </c>
       <c r="K21" s="10" t="inlineStr">
         <is>
@@ -1044,25 +1044,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.09418198775809977</v>
+        <v>0.09418198775809983</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>9418.198775809977</v>
+        <v>9418.198775809982</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>0.0768720835510508</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>723.9965631944689</v>
+        <v>723.9965631944693</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>389.2892582037049</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>338.6494229435847</v>
+        <v>338.6494229435848</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>1.216129384176888</v>
+        <v>1.216129384176894</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
@@ -1085,16 +1085,16 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.09292983765935728</v>
+        <v>0.09292983765935721</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>9292.983765935727</v>
+        <v>9292.983765935722</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.0426715939840771</v>
+        <v>0.0426715939840769</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>396.5464301606291</v>
+        <v>396.546430160627</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>144.3057422434339</v>
@@ -1103,7 +1103,7 @@
         <v>131.2317517386179</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.8238767911137752</v>
+        <v>0.8238767911137712</v>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>0.4999999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>49999.99999999999</v>
+        <v>50000</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>0</v>
@@ -1243,7 +1243,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-27 05:44</t>
+          <t>Son Güncelleme: 2026-06-28 06:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1443,7 +1443,7 @@
         <v>0.1012146812708825</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.1111298169216609</v>
+        <v>0.1111298169216608</v>
       </c>
       <c r="G8" s="16" t="n">
         <v>0.1296241549962105</v>
@@ -1452,7 +1452,7 @@
         <v>357.8947714130368</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>361.1171904995398</v>
+        <v>361.1171904995397</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>367.1278503737684</v>
@@ -1557,7 +1557,7 @@
         <v>-0.0037105180381591</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>0.0219942686510214</v>
+        <v>0.0219942686510217</v>
       </c>
       <c r="G10" s="19" t="n">
         <v>0.0938733706755232</v>
@@ -1611,25 +1611,25 @@
         <v>40.65999984741211</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>-0.0234457107155366</v>
+        <v>-0.0234457107155365</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>0.0576923532547533</v>
+        <v>0.0576923532547535</v>
       </c>
       <c r="G11" s="16" t="n">
         <v>0.2257407445924774</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>39.70669725329592</v>
+        <v>39.70669725329593</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>43.00577092194722</v>
+        <v>43.00577092194723</v>
       </c>
       <c r="J11" s="15" t="n">
         <v>49.83861848809694</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>38.16395266206861</v>
+        <v>38.16395266206862</v>
       </c>
       <c r="L11" s="14" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>-0.0557185041218549</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>0.003753763602968</v>
+        <v>0.0037537636029683</v>
       </c>
       <c r="G12" s="19" t="n">
         <v>0.0731182729479942</v>
@@ -1680,7 +1680,7 @@
         <v>312.3211047616965</v>
       </c>
       <c r="I12" s="18" t="n">
-        <v>331.9915573116817</v>
+        <v>331.9915573116818</v>
       </c>
       <c r="J12" s="18" t="n">
         <v>354.9338687775491</v>
@@ -1728,10 +1728,10 @@
         <v>-0.0082889988742848</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>0.0426715939840771</v>
+        <v>0.0426715939840769</v>
       </c>
       <c r="G13" s="16" t="n">
-        <v>0.1593907013593682</v>
+        <v>0.159390701359368</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>137.2527965028754</v>
@@ -1857,7 +1857,7 @@
         <v>425.1313564101224</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>338.6494229435847</v>
+        <v>338.6494229435848</v>
       </c>
       <c r="L15" s="14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-27 05:44</t>
+          <t>Son Güncelleme: 2026-06-28 06:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2137,7 +2137,7 @@
         <v>0.1926605504587155</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>0.4041814534285399</v>
+        <v>0.4041814534285401</v>
       </c>
       <c r="H4" s="16" t="n">
         <v>0.0254876783377191</v>
@@ -2151,7 +2151,7 @@
         <v>0.0277544831724269</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.1111298169216609</v>
+        <v>0.1111298169216608</v>
       </c>
     </row>
     <row r="5">
@@ -2237,7 +2237,7 @@
         <v>0.0199787850023338</v>
       </c>
       <c r="K6" s="19" t="n">
-        <v>0.0219942686510214</v>
+        <v>0.0219942686510217</v>
       </c>
     </row>
     <row r="7">
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="J7" s="16" t="n">
-        <v>0.0306941366786843</v>
+        <v>0.0306941366786842</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>0.0576923532547533</v>
+        <v>0.0576923532547535</v>
       </c>
     </row>
     <row r="8">
@@ -2323,7 +2323,7 @@
         <v>0.0225893046698586</v>
       </c>
       <c r="K8" s="19" t="n">
-        <v>0.003753763602968</v>
+        <v>0.0037537636029683</v>
       </c>
     </row>
     <row r="9">
@@ -2366,7 +2366,7 @@
         <v>0.0258968297470734</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>0.0426715939840771</v>
+        <v>0.0426715939840769</v>
       </c>
     </row>
     <row r="10">
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="J11" s="16" t="n">
-        <v>0.0316052241444195</v>
+        <v>0.0316052241444194</v>
       </c>
       <c r="K11" s="16" t="n">
         <v>0.0768720835510508</v>
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="J12" s="22" t="n">
-        <v>0.023328758071726</v>
+        <v>0.0233287580717261</v>
       </c>
       <c r="K12" s="22" t="n">
         <v>-0.0144632354250776</v>
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="E13" s="19" t="n">
-        <v>0.0481226364410856</v>
+        <v>0.0481226364410858</v>
       </c>
       <c r="F13" s="19" t="n">
         <v>0.0470152865980195</v>
@@ -2561,13 +2561,13 @@
         </is>
       </c>
       <c r="E14" s="24" t="n">
-        <v>0.0592390972635019</v>
+        <v>0.0592390972635021</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>0.1007848660939432</v>
+        <v>0.1007848660939434</v>
       </c>
       <c r="G14" s="24" t="n">
-        <v>0.1703970939841539</v>
+        <v>0.1703970939841541</v>
       </c>
       <c r="H14" s="24" t="n">
         <v>-0.09047421021702989</v>
@@ -2581,7 +2581,7 @@
         <v>0.0257353684650022</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.06255951557298681</v>
+        <v>0.0625595155729869</v>
       </c>
     </row>
     <row r="15">
@@ -2607,7 +2607,7 @@
         <v>0.0249554181347848</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>-0.1601752428145885</v>
+        <v>-0.1601752428145886</v>
       </c>
       <c r="G15" s="24" t="n">
         <v>-0.0619335174456089</v>
@@ -2664,7 +2664,7 @@
         </is>
       </c>
       <c r="J16" s="24" t="n">
-        <v>0.021857194251186</v>
+        <v>0.0218571942511859</v>
       </c>
       <c r="K16" s="24" t="n">
         <v>0.0477932433117227</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="J17" s="24" t="n">
-        <v>0.0268138653389995</v>
+        <v>0.0268138653389994</v>
       </c>
       <c r="K17" s="24" t="n">
         <v>0.0236686907772818</v>
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="E18" s="24" t="n">
-        <v>0.0038572954450379</v>
+        <v>0.0038572954450377</v>
       </c>
       <c r="F18" s="24" t="n">
-        <v>-0.064690066309239</v>
+        <v>-0.0646900663092389</v>
       </c>
       <c r="G18" s="24" t="n">
-        <v>-0.0378927780939064</v>
+        <v>-0.0378927780939065</v>
       </c>
       <c r="H18" s="24" t="n">
         <v>-0.1473805790456531</v>
@@ -2776,13 +2776,13 @@
         </is>
       </c>
       <c r="E19" s="24" t="n">
-        <v>-0.1140271680663239</v>
+        <v>-0.114027168066324</v>
       </c>
       <c r="F19" s="24" t="n">
-        <v>0.0213875767230238</v>
+        <v>0.0213875767230236</v>
       </c>
       <c r="G19" s="24" t="n">
-        <v>0.1773903133981555</v>
+        <v>0.1773903133981553</v>
       </c>
       <c r="H19" s="24" t="n">
         <v>-0.2178459598945363</v>
@@ -2836,7 +2836,7 @@
         </is>
       </c>
       <c r="J20" s="24" t="n">
-        <v>0.0223518238238337</v>
+        <v>0.0223518238238338</v>
       </c>
       <c r="K20" s="24" t="n">
         <v>0.0999999916062814</v>
@@ -2872,7 +2872,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-27 05:44</t>
+          <t>Son Güncelleme: 2026-06-28 06:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2991,7 +2991,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-27 05:44</t>
+          <t>Son Güncelleme: 2026-06-28 06:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3242,7 +3242,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-27 05:44</t>
+          <t>Son Güncelleme: 2026-06-28 06:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3367,7 +3367,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-27 05:44</t>
+          <t>Son Güncelleme: 2026-06-28 06:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3675,13 +3675,13 @@
         <v>101.5</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>97.44999694824219</v>
+        <v>97.4499969482422</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>-0.03990150789909175</v>
+        <v>-0.03990150789909164</v>
       </c>
       <c r="F12" s="25" t="n">
-        <v>-28378.26246333471</v>
+        <v>-28378.2624633346</v>
       </c>
       <c r="G12" s="25" t="n">
         <v>2256106.809120123</v>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -629,7 +629,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-28 06:05</t>
+          <t>Son Güncelleme: 2026-06-29 06:26</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1243,7 +1243,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-28 06:05</t>
+          <t>Son Güncelleme: 2026-06-29 06:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2040,7 +2040,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-28 06:05</t>
+          <t>Son Güncelleme: 2026-06-29 06:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2872,7 +2872,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-28 06:05</t>
+          <t>Son Güncelleme: 2026-06-29 06:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2991,7 +2991,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-28 06:05</t>
+          <t>Son Güncelleme: 2026-06-29 06:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3242,7 +3242,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-28 06:05</t>
+          <t>Son Güncelleme: 2026-06-29 06:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14259.7998046875</v>
+        <v>14274</v>
       </c>
     </row>
     <row r="5">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>12525.76452636719</v>
+        <v>12543.48702636719</v>
       </c>
     </row>
     <row r="6">
@@ -3367,7 +3367,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-06-28 06:05</t>
+          <t>Son Güncelleme: 2026-06-29 06:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3447,7 +3447,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H4" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
     <row r="5">
@@ -3477,7 +3477,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H5" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
     <row r="6">
@@ -3507,7 +3507,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H6" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
     <row r="7">
@@ -3537,7 +3537,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H7" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
     <row r="8">
@@ -3567,7 +3567,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H8" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
     <row r="9">
@@ -3597,7 +3597,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H9" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
     <row r="10">
@@ -3627,7 +3627,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H10" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
     <row r="11">
@@ -3657,7 +3657,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H11" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
     <row r="12">
@@ -3687,7 +3687,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H12" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
     <row r="13">
@@ -3717,7 +3717,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H13" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
     <row r="14">
@@ -3747,7 +3747,7 @@
         <v>2256106.809120123</v>
       </c>
       <c r="H14" s="26" t="n">
-        <v>0.0405574872072023</v>
+        <v>0.0415936952714535</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-04 05:34</t>
+          <t>Son Güncelleme: 2026-07-05 05:51</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1023,19 +1023,19 @@
         <v>12757.11168923382</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.1259383002873109</v>
+        <v>0.1259383002873111</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>1606.608962717493</v>
+        <v>1606.608962717495</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>449.8123509647807</v>
+        <v>449.8123509647808</v>
       </c>
       <c r="I21" s="8" t="n">
         <v>373.1666787300279</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>1.910596481506183</v>
+        <v>1.910596481506187</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1058567831986978</v>
+        <v>0.1058567831986977</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>10585.67831986978</v>
+        <v>10585.67831986977</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>0.1047501473143974</v>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.06951830094919656</v>
+        <v>0.06951830094919655</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>6951.830094919656</v>
+        <v>6951.830094919655</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>0.0319463736658787</v>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.05901418175367707</v>
+        <v>0.05901418175367706</v>
       </c>
       <c r="E24" s="8" t="n">
         <v>5901.418175367707</v>
@@ -1155,7 +1155,7 @@
         <v>40.80921186599804</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>36.51765369294939</v>
+        <v>36.51765369294938</v>
       </c>
       <c r="J24" s="6" t="n">
         <v>0.1979746325938461</v>
@@ -1257,7 +1257,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-04 05:34</t>
+          <t>Son Güncelleme: 2026-07-05 05:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1457,19 +1457,19 @@
         <v>0.0618301731244848</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.1259383002873109</v>
+        <v>0.1259383002873111</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.2830390713974848</v>
+        <v>0.2830390713974846</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>424.2011541632316</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>449.8123509647807</v>
+        <v>449.8123509647808</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>512.5741090232953</v>
+        <v>512.5741090232951</v>
       </c>
       <c r="K8" s="15" t="n">
         <v>373.1666787300279</v>
@@ -1682,7 +1682,7 @@
         <v>73.75</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>-0.1195457879117688</v>
+        <v>-0.1195457879117687</v>
       </c>
       <c r="F12" s="19" t="n">
         <v>-0.0525384894872815</v>
@@ -1691,7 +1691,7 @@
         <v>0.05159344410234</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>64.93349814150704</v>
+        <v>64.93349814150706</v>
       </c>
       <c r="I12" s="18" t="n">
         <v>69.87528640031299</v>
@@ -1700,7 +1700,7 @@
         <v>77.55501650254757</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>64.93349814150704</v>
+        <v>64.93349814150706</v>
       </c>
       <c r="L12" s="17" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>0.004366982061861</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.1062296048253292</v>
+        <v>0.1062296048253293</v>
       </c>
       <c r="H13" s="21" t="n">
         <v>36.01196952636552</v>
@@ -1859,7 +1859,7 @@
         <v>-0.0056061959533879</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>0.1633018392220255</v>
+        <v>0.1633018392220254</v>
       </c>
       <c r="H15" s="18" t="n">
         <v>181.012467304781</v>
@@ -1868,7 +1868,7 @@
         <v>188.5370713165358</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>220.562035816727</v>
+        <v>220.5620358167269</v>
       </c>
       <c r="K15" s="18" t="n">
         <v>180.1200057983398</v>
@@ -1919,7 +1919,7 @@
         <v>0.0827585226318214</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>36.51765369294939</v>
+        <v>36.51765369294938</v>
       </c>
       <c r="I16" s="15" t="n">
         <v>40.80921186599804</v>
@@ -1928,7 +1928,7 @@
         <v>43.41861510537765</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>36.51765369294939</v>
+        <v>36.51765369294938</v>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
@@ -1976,13 +1976,13 @@
         <v>0.0625387106897197</v>
       </c>
       <c r="H17" s="21" t="n">
-        <v>103.3044372525922</v>
+        <v>103.3044372525923</v>
       </c>
       <c r="I17" s="21" t="n">
         <v>108.9707404116317</v>
       </c>
       <c r="J17" s="21" t="n">
-        <v>113.9041465433271</v>
+        <v>113.9041465433272</v>
       </c>
       <c r="K17" s="21" t="n">
         <v>101.8399971008301</v>
@@ -2168,7 +2168,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-04 05:34</t>
+          <t>Son Güncelleme: 2026-07-05 05:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2279,7 +2279,7 @@
         <v>0.0329578488985884</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.1259383002873109</v>
+        <v>0.1259383002873111</v>
       </c>
     </row>
     <row r="5">
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="J5" s="16" t="n">
-        <v>0.0224280868678006</v>
+        <v>0.0224280868678007</v>
       </c>
       <c r="K5" s="16" t="n">
         <v>0.211966460056985</v>
@@ -2520,7 +2520,7 @@
         <v>0.0308880308880308</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>0.057843565416608</v>
+        <v>0.0578435654166078</v>
       </c>
       <c r="G10" s="16" t="n">
         <v>-0.07217851387470781</v>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="E11" s="19" t="n">
-        <v>-0.0083681530871555</v>
+        <v>-0.0083681530871556</v>
       </c>
       <c r="F11" s="19" t="n">
         <v>-0.0181253230935878</v>
@@ -2606,10 +2606,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>0.4413204787850318</v>
+        <v>0.4413204787850315</v>
       </c>
       <c r="G12" s="16" t="n">
-        <v>0.6781684227851839</v>
+        <v>0.6781684227851834</v>
       </c>
       <c r="H12" s="16" t="n">
         <v>-0.2000140581789575</v>
@@ -2646,13 +2646,13 @@
         </is>
       </c>
       <c r="E13" s="22" t="n">
-        <v>-0.0064875307482625</v>
+        <v>-0.0064875307482624</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>0.0028063182233972</v>
+        <v>0.0028063182233974</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.1166666348775227</v>
+        <v>0.1166666348775229</v>
       </c>
       <c r="H13" s="22" t="n">
         <v>-0.0013946075335394</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="J16" s="27" t="n">
-        <v>0.0262733290323232</v>
+        <v>0.0262733290323233</v>
       </c>
       <c r="K16" s="27" t="n">
         <v>0.0121672257670984</v>
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="J17" s="27" t="n">
-        <v>0.0218716122937669</v>
+        <v>0.0218716122937668</v>
       </c>
       <c r="K17" s="27" t="n">
         <v>0.0270714525721503</v>
@@ -2861,13 +2861,13 @@
         </is>
       </c>
       <c r="E18" s="27" t="n">
-        <v>-0.0502369957512588</v>
+        <v>-0.0502369957512587</v>
       </c>
       <c r="F18" s="27" t="n">
-        <v>-0.0956679224870062</v>
+        <v>-0.09566792248700599</v>
       </c>
       <c r="G18" s="27" t="n">
-        <v>-0.044804618772834</v>
+        <v>-0.0448046187728339</v>
       </c>
       <c r="H18" s="27" t="n">
         <v>-0.0867375485681951</v>
@@ -2921,7 +2921,7 @@
         </is>
       </c>
       <c r="J19" s="27" t="n">
-        <v>0.027371838733298</v>
+        <v>0.0273718387332981</v>
       </c>
       <c r="K19" s="27" t="n">
         <v>0.09098899757469089</v>
@@ -2950,7 +2950,7 @@
         <v>-0.0547403900411772</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>-0.1683217225612643</v>
+        <v>-0.1683217225612644</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>-0.09388789028605229</v>
@@ -2964,7 +2964,7 @@
         </is>
       </c>
       <c r="J20" s="27" t="n">
-        <v>0.0217198916869541</v>
+        <v>0.021719891686954</v>
       </c>
       <c r="K20" s="27" t="n">
         <v>0.09098899757469089</v>
@@ -3000,7 +3000,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-04 05:34</t>
+          <t>Son Güncelleme: 2026-07-05 05:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3119,7 +3119,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-04 05:34</t>
+          <t>Son Güncelleme: 2026-07-05 05:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3370,7 +3370,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-04 05:34</t>
+          <t>Son Güncelleme: 2026-07-05 05:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3495,7 +3495,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-04 05:34</t>
+          <t>Son Güncelleme: 2026-07-05 05:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3572,7 +3572,7 @@
         <v>338.4805471272794</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>2153877.312550157</v>
+        <v>2858357.055049356</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3602,7 +3602,7 @@
         <v>844.8417266280685</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>2153877.312550157</v>
+        <v>2858357.055049356</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3632,7 +3632,7 @@
         <v>-170.1874413355963</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>2153877.312550157</v>
+        <v>2858357.055049356</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3662,7 +3662,7 @@
         <v>-764.8350642277655</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>2153877.312550157</v>
+        <v>2858357.055049356</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3692,7 +3692,7 @@
         <v>-94416.71969714283</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>2153877.312550157</v>
+        <v>2858357.055049356</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3716,13 +3716,13 @@
         <v>40.09999847412109</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>-0.005949471431804132</v>
+        <v>-0.005949471431804354</v>
       </c>
       <c r="F9" s="28" t="n">
-        <v>-4231.310311300098</v>
+        <v>-4231.310311300214</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>2153877.312550157</v>
+        <v>2858357.055049356</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3752,7 +3752,7 @@
         <v>74.00308946839505</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>2153877.312550157</v>
+        <v>2858357.055049356</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3782,7 +3782,7 @@
         <v>-456.3221797124534</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>2153877.312550157</v>
+        <v>2858357.055049356</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3812,7 +3812,7 @@
         <v>-1.164153218269348e-10</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>2153877.312550157</v>
+        <v>2858357.055049356</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0.0520943075470665</v>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-05 05:51</t>
+          <t>Son Güncelleme: 2026-07-06 06:14</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1257,7 +1257,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-05 05:51</t>
+          <t>Son Güncelleme: 2026-07-06 06:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2168,7 +2168,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-05 05:51</t>
+          <t>Son Güncelleme: 2026-07-06 06:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3000,7 +3000,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-05 05:51</t>
+          <t>Son Güncelleme: 2026-07-06 06:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3119,7 +3119,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-05 05:51</t>
+          <t>Son Güncelleme: 2026-07-06 06:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3370,7 +3370,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-05 05:51</t>
+          <t>Son Güncelleme: 2026-07-06 06:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3495,7 +3495,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-05 05:51</t>
+          <t>Son Güncelleme: 2026-07-06 06:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3572,7 +3572,7 @@
         <v>338.4805471272794</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>2858357.055049356</v>
+        <v>3562836.797548554</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3602,7 +3602,7 @@
         <v>844.8417266280685</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>2858357.055049356</v>
+        <v>3562836.797548554</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3632,7 +3632,7 @@
         <v>-170.1874413355963</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>2858357.055049356</v>
+        <v>3562836.797548554</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3662,7 +3662,7 @@
         <v>-764.8350642277655</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>2858357.055049356</v>
+        <v>3562836.797548554</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3692,7 +3692,7 @@
         <v>-94416.71969714283</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>2858357.055049356</v>
+        <v>3562836.797548554</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3722,7 +3722,7 @@
         <v>-4231.310311300214</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>2858357.055049356</v>
+        <v>3562836.797548554</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3752,7 +3752,7 @@
         <v>74.00308946839505</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>2858357.055049356</v>
+        <v>3562836.797548554</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3782,7 +3782,7 @@
         <v>-456.3221797124534</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>2858357.055049356</v>
+        <v>3562836.797548554</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3812,7 +3812,7 @@
         <v>-1.164153218269348e-10</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>2858357.055049356</v>
+        <v>3562836.797548554</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0.0520943075470665</v>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-06 06:14</t>
+          <t>Son Güncelleme: 2026-07-07 05:56</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -974,25 +974,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1380396172060904</v>
+        <v>0.1380396116533548</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>13803.96172060904</v>
+        <v>13803.96116533548</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.211966460056985</v>
+        <v>0.2119663640262494</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>2925.976900679626</v>
+        <v>2925.97545737571</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>404.796797659033</v>
+        <v>404.7967655847673</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>317.3</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>4.239329201139705</v>
+        <v>4.239327280524994</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1017,19 +1017,19 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1275711168923382</v>
+        <v>0.1275711214916294</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>12757.11168923382</v>
+        <v>12757.11214916294</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.1259383002873111</v>
+        <v>0.1259383002873109</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>1606.608962717495</v>
+        <v>1606.609020640185</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>449.8123509647808</v>
+        <v>449.8123509647807</v>
       </c>
       <c r="I21" s="8" t="n">
         <v>373.1666787300279</v>
@@ -1058,25 +1058,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1058567831986977</v>
+        <v>0.1058567503448248</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>10585.67831986977</v>
+        <v>10585.67503448248</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.1047501473143974</v>
+        <v>0.1047500099709655</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>1108.851363429182</v>
+        <v>1108.84956541144</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>333.6345444889481</v>
+        <v>333.6345030112316</v>
       </c>
       <c r="I22" s="8" t="n">
         <v>285.1645786331716</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>1.879046790671904</v>
+        <v>1.879044326954746</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
@@ -1099,16 +1099,16 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.06951830094919655</v>
+        <v>0.06951830345552337</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>6951.830094919655</v>
+        <v>6951.830345552337</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>0.0319463736658787</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>222.0857618740043</v>
+        <v>222.0857698808096</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>137.7648408843948</v>
@@ -1117,7 +1117,7 @@
         <v>126.5130091330145</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.6103973750054179</v>
+        <v>0.6103973750054204</v>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.05901418175367706</v>
+        <v>0.05901421305466755</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>5901.418175367707</v>
+        <v>5901.421305466755</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0176861201711677</v>
+        <v>0.0176862670340702</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>104.3731910298665</v>
+        <v>104.3741130890362</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>40.80921186599804</v>
+        <v>40.80921775520021</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>36.51765369294938</v>
+        <v>36.51765090818546</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.1979746325938461</v>
+        <v>0.1979761226473516</v>
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-06 06:14</t>
+          <t>Son Güncelleme: 2026-07-07 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1457,19 +1457,19 @@
         <v>0.0618301731244848</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.1259383002873111</v>
+        <v>0.1259383002873109</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.2830390713974846</v>
+        <v>0.2830390713974848</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>424.2011541632316</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>449.8123509647808</v>
+        <v>449.8123509647807</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>512.5741090232951</v>
+        <v>512.5741090232953</v>
       </c>
       <c r="K8" s="15" t="n">
         <v>373.1666787300279</v>
@@ -1511,22 +1511,22 @@
         <v>334</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>0.0457252883240006</v>
+        <v>0.0457252439987692</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>0.211966460056985</v>
+        <v>0.2119663640262494</v>
       </c>
       <c r="G9" s="16" t="n">
-        <v>0.3728564655733453</v>
+        <v>0.3728564122007715</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>349.2722463002162</v>
+        <v>349.2722314955889</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>404.796797659033</v>
+        <v>404.7967655847673</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>458.5340595014973</v>
+        <v>458.5340416750577</v>
       </c>
       <c r="K9" s="15" t="n">
         <v>317.3</v>
@@ -1571,19 +1571,19 @@
         <v>-0.0194805194805194</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>0.1047501473143974</v>
+        <v>0.1047500099709655</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>0.1307691594971161</v>
+        <v>0.1307690576798095</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>296.1168831168831</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>333.6345444889481</v>
+        <v>333.6345030112316</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>341.4922861681291</v>
+        <v>341.4922554193025</v>
       </c>
       <c r="K10" s="15" t="n">
         <v>285.1645786331716</v>
@@ -1628,19 +1628,19 @@
         <v>-0.0174048288175393</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>-0.0036970289786339</v>
+        <v>-0.0036968005684216</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>0.1185391429973565</v>
+        <v>0.1185386588107133</v>
       </c>
       <c r="H11" s="18" t="n">
         <v>350.7864761121385</v>
       </c>
       <c r="I11" s="18" t="n">
-        <v>355.6801606546277</v>
+        <v>355.6802421970735</v>
       </c>
       <c r="J11" s="18" t="n">
-        <v>399.3184740500563</v>
+        <v>399.3183011954247</v>
       </c>
       <c r="K11" s="18" t="n">
         <v>339.15</v>
@@ -1682,25 +1682,25 @@
         <v>73.75</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>-0.1195457879117687</v>
+        <v>-0.1195457879117688</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>-0.0525384894872815</v>
+        <v>-0.0525383720373842</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>0.05159344410234</v>
+        <v>0.0515933378844173</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>64.93349814150706</v>
+        <v>64.93349814150704</v>
       </c>
       <c r="I12" s="18" t="n">
-        <v>69.87528640031299</v>
+        <v>69.87529506224291</v>
       </c>
       <c r="J12" s="18" t="n">
-        <v>77.55501650254757</v>
+        <v>77.55500866897577</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>64.93349814150706</v>
+        <v>64.93349814150704</v>
       </c>
       <c r="L12" s="17" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>0.004366982061861</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.1062296048253293</v>
+        <v>0.1062296237000928</v>
       </c>
       <c r="H13" s="21" t="n">
         <v>36.01196952636552</v>
@@ -1754,7 +1754,7 @@
         <v>38.18603311775468</v>
       </c>
       <c r="J13" s="21" t="n">
-        <v>42.05885008185074</v>
+        <v>42.05885079946926</v>
       </c>
       <c r="K13" s="21" t="n">
         <v>35.62858599261265</v>
@@ -1796,22 +1796,22 @@
         <v>133.5</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>-0.0374467634999697</v>
+        <v>-0.0374466031122178</v>
       </c>
       <c r="F14" s="16" t="n">
         <v>0.0319463736658787</v>
       </c>
       <c r="G14" s="16" t="n">
-        <v>0.10818310737263</v>
+        <v>0.1081830165120092</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>128.5008570727541</v>
+        <v>128.5008784845189</v>
       </c>
       <c r="I14" s="15" t="n">
         <v>137.7648408843948</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>147.9424448342461</v>
+        <v>147.9424327043532</v>
       </c>
       <c r="K14" s="15" t="n">
         <v>126.5130091330145</v>
@@ -1853,22 +1853,22 @@
         <v>189.6000061035156</v>
       </c>
       <c r="E15" s="19" t="n">
-        <v>-0.0452929246956146</v>
+        <v>-0.0452929265798762</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>-0.0056061959533879</v>
+        <v>-0.005606274347556</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>0.1633018392220254</v>
+        <v>0.1633017563777966</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>181.012467304781</v>
+        <v>181.012466947525</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>188.5370713165358</v>
+        <v>188.537056453001</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>220.5620358167269</v>
+        <v>220.5620201094607</v>
       </c>
       <c r="K15" s="18" t="n">
         <v>180.1200057983398</v>
@@ -1910,25 +1910,25 @@
         <v>40.09999847412109</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>-0.08933528472534991</v>
+        <v>-0.089335354170837</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>0.0176861201711677</v>
+        <v>0.0176862670340702</v>
       </c>
       <c r="G16" s="16" t="n">
-        <v>0.0827585226318214</v>
+        <v>0.0827586281845227</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>36.51765369294938</v>
+        <v>36.51765090818546</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>40.80921186599804</v>
+        <v>40.80921775520021</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>43.41861510537765</v>
+        <v>43.41861933804081</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>36.51765369294938</v>
+        <v>36.51765090818546</v>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
@@ -1970,19 +1970,19 @@
         <v>-0.036339177299891</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>0.0165181297928999</v>
+        <v>0.0165180940172871</v>
       </c>
       <c r="G17" s="22" t="n">
         <v>0.0625387106897197</v>
       </c>
       <c r="H17" s="21" t="n">
-        <v>103.3044372525923</v>
+        <v>103.3044372525922</v>
       </c>
       <c r="I17" s="21" t="n">
-        <v>108.9707404116317</v>
+        <v>108.9707365764861</v>
       </c>
       <c r="J17" s="21" t="n">
-        <v>113.9041465433272</v>
+        <v>113.9041465433271</v>
       </c>
       <c r="K17" s="21" t="n">
         <v>101.8399971008301</v>
@@ -2024,25 +2024,25 @@
         <v>248.1999969482422</v>
       </c>
       <c r="E18" s="25" t="n">
-        <v>-0.0501087082729111</v>
+        <v>-0.0501087049018857</v>
       </c>
       <c r="F18" s="25" t="n">
-        <v>-0.0049330944485646</v>
+        <v>-0.004933032871861</v>
       </c>
       <c r="G18" s="25" t="n">
-        <v>0.0825054415792305</v>
+        <v>0.082505387163645</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>235.7630157078253</v>
+        <v>235.7630165445138</v>
       </c>
       <c r="I18" s="24" t="n">
-        <v>246.9756029211631</v>
+        <v>246.9756182045007</v>
       </c>
       <c r="J18" s="24" t="n">
-        <v>268.6778472964206</v>
+        <v>268.6778337904724</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>235.7630157078253</v>
+        <v>235.7630165445138</v>
       </c>
       <c r="L18" s="23" t="inlineStr">
         <is>
@@ -2081,25 +2081,25 @@
         <v>94.5</v>
       </c>
       <c r="E19" s="25" t="n">
-        <v>-0.1036949211912278</v>
+        <v>-0.1036948476951217</v>
       </c>
       <c r="F19" s="25" t="n">
-        <v>-0.0265262577132464</v>
+        <v>-0.0265261865666126</v>
       </c>
       <c r="G19" s="25" t="n">
-        <v>0.0283369659971981</v>
+        <v>0.0283370297099155</v>
       </c>
       <c r="H19" s="24" t="n">
-        <v>84.70082994742897</v>
+        <v>84.700836892811</v>
       </c>
       <c r="I19" s="24" t="n">
-        <v>91.99326864609822</v>
+        <v>91.99327536945511</v>
       </c>
       <c r="J19" s="24" t="n">
-        <v>97.17784328673523</v>
+        <v>97.17784930758701</v>
       </c>
       <c r="K19" s="24" t="n">
-        <v>84.70082994742897</v>
+        <v>84.700836892811</v>
       </c>
       <c r="L19" s="23" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-06 06:14</t>
+          <t>Son Güncelleme: 2026-07-07 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="J4" s="16" t="n">
-        <v>0.0329578488985884</v>
+        <v>0.0329578488985883</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.1259383002873111</v>
+        <v>0.1259383002873109</v>
       </c>
     </row>
     <row r="5">
@@ -2322,7 +2322,7 @@
         <v>0.0224280868678007</v>
       </c>
       <c r="K5" s="16" t="n">
-        <v>0.211966460056985</v>
+        <v>0.2119663640262494</v>
       </c>
     </row>
     <row r="6">
@@ -2365,7 +2365,7 @@
         <v>0.0278732141834907</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>0.1047501473143974</v>
+        <v>0.1047500099709655</v>
       </c>
     </row>
     <row r="7">
@@ -2408,7 +2408,7 @@
         <v>0.0199673156767437</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>-0.0036970289786339</v>
+        <v>-0.0036968005684216</v>
       </c>
     </row>
     <row r="8">
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="J8" s="19" t="n">
-        <v>0.0317317702632586</v>
+        <v>0.0317317702632585</v>
       </c>
       <c r="K8" s="19" t="n">
-        <v>-0.0525384894872815</v>
+        <v>-0.0525383720373842</v>
       </c>
     </row>
     <row r="9">
@@ -2520,7 +2520,7 @@
         <v>0.0308880308880308</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>0.0578435654166078</v>
+        <v>0.057843565416608</v>
       </c>
       <c r="G10" s="16" t="n">
         <v>-0.07217851387470781</v>
@@ -2534,7 +2534,7 @@
         </is>
       </c>
       <c r="J10" s="16" t="n">
-        <v>0.026168505119796</v>
+        <v>0.0261685051197959</v>
       </c>
       <c r="K10" s="16" t="n">
         <v>0.0319463736658787</v>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="E11" s="19" t="n">
-        <v>-0.0083681530871556</v>
+        <v>-0.0083681530871555</v>
       </c>
       <c r="F11" s="19" t="n">
         <v>-0.0181253230935878</v>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="J11" s="19" t="n">
-        <v>0.0216342637490465</v>
+        <v>0.0216342637490466</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>-0.0056061959533879</v>
+        <v>-0.005606274347556</v>
       </c>
     </row>
     <row r="12">
@@ -2606,10 +2606,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>0.4413204787850315</v>
+        <v>0.4413204787850318</v>
       </c>
       <c r="G12" s="16" t="n">
-        <v>0.6781684227851834</v>
+        <v>0.6781684227851839</v>
       </c>
       <c r="H12" s="16" t="n">
         <v>-0.2000140581789575</v>
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="J12" s="16" t="n">
-        <v>0.0276553695056337</v>
+        <v>0.0276553695056338</v>
       </c>
       <c r="K12" s="16" t="n">
-        <v>0.0176861201711677</v>
+        <v>0.0176862670340702</v>
       </c>
     </row>
     <row r="13">
@@ -2646,13 +2646,13 @@
         </is>
       </c>
       <c r="E13" s="22" t="n">
-        <v>-0.0064875307482624</v>
+        <v>-0.0064875307482625</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>0.0028063182233974</v>
+        <v>0.0028063182233972</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.1166666348775229</v>
+        <v>0.1166666348775227</v>
       </c>
       <c r="H13" s="22" t="n">
         <v>-0.0013946075335394</v>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="J13" s="22" t="n">
-        <v>0.0234179516127443</v>
+        <v>0.0234179516127442</v>
       </c>
       <c r="K13" s="22" t="n">
-        <v>0.0165181297928999</v>
+        <v>0.0165180940172871</v>
       </c>
     </row>
     <row r="14">
@@ -2709,7 +2709,7 @@
         <v>0.0227948736710902</v>
       </c>
       <c r="K14" s="25" t="n">
-        <v>-0.0049330944485646</v>
+        <v>-0.004933032871861</v>
       </c>
     </row>
     <row r="15">
@@ -2752,7 +2752,7 @@
         <v>0.0257945186668304</v>
       </c>
       <c r="K15" s="25" t="n">
-        <v>-0.0265262577132464</v>
+        <v>-0.0265261865666126</v>
       </c>
     </row>
     <row r="16">
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="J16" s="27" t="n">
-        <v>0.0262733290323233</v>
+        <v>0.0262733290323232</v>
       </c>
       <c r="K16" s="27" t="n">
-        <v>0.0121672257670984</v>
+        <v>0.0121672262735507</v>
       </c>
     </row>
     <row r="17">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="J17" s="27" t="n">
-        <v>0.0218716122937668</v>
+        <v>0.0218716122937669</v>
       </c>
       <c r="K17" s="27" t="n">
         <v>0.0270714525721503</v>
@@ -2861,13 +2861,13 @@
         </is>
       </c>
       <c r="E18" s="27" t="n">
-        <v>-0.0502369957512587</v>
+        <v>-0.0502369957512588</v>
       </c>
       <c r="F18" s="27" t="n">
-        <v>-0.09566792248700599</v>
+        <v>-0.0956679224870062</v>
       </c>
       <c r="G18" s="27" t="n">
-        <v>-0.0448046187728339</v>
+        <v>-0.044804618772834</v>
       </c>
       <c r="H18" s="27" t="n">
         <v>-0.0867375485681951</v>
@@ -2881,7 +2881,7 @@
         <v>0.0183815906397974</v>
       </c>
       <c r="K18" s="27" t="n">
-        <v>0.0759494774088542</v>
+        <v>0.0759492964836558</v>
       </c>
     </row>
     <row r="19">
@@ -2921,7 +2921,7 @@
         </is>
       </c>
       <c r="J19" s="27" t="n">
-        <v>0.0273718387332981</v>
+        <v>0.027371838733298</v>
       </c>
       <c r="K19" s="27" t="n">
         <v>0.09098899757469089</v>
@@ -2950,7 +2950,7 @@
         <v>-0.0547403900411772</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>-0.1683217225612644</v>
+        <v>-0.1683217225612643</v>
       </c>
       <c r="G20" s="27" t="n">
         <v>-0.09388789028605229</v>
@@ -2964,7 +2964,7 @@
         </is>
       </c>
       <c r="J20" s="27" t="n">
-        <v>0.021719891686954</v>
+        <v>0.0217198916869541</v>
       </c>
       <c r="K20" s="27" t="n">
         <v>0.09098899757469089</v>
@@ -3000,7 +3000,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-06 06:14</t>
+          <t>Son Güncelleme: 2026-07-07 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3119,7 +3119,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-06 06:14</t>
+          <t>Son Güncelleme: 2026-07-07 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3370,7 +3370,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-06 06:14</t>
+          <t>Son Güncelleme: 2026-07-07 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3394,7 +3394,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14417.900390625</v>
+        <v>14424.5</v>
       </c>
     </row>
     <row r="5">
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>12639.74602539062</v>
+        <v>12656.86702636719</v>
       </c>
     </row>
     <row r="6">
@@ -3495,7 +3495,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-06 06:14</t>
+          <t>Son Güncelleme: 2026-07-07 05:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3572,7 +3572,7 @@
         <v>338.4805471272794</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>3562836.797548554</v>
+        <v>4267316.540047753</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3602,7 +3602,7 @@
         <v>844.8417266280685</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>3562836.797548554</v>
+        <v>4267316.540047753</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3632,7 +3632,7 @@
         <v>-170.1874413355963</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>3562836.797548554</v>
+        <v>4267316.540047753</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3662,7 +3662,7 @@
         <v>-764.8350642277655</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>3562836.797548554</v>
+        <v>4267316.540047753</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3692,7 +3692,7 @@
         <v>-94416.71969714283</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>3562836.797548554</v>
+        <v>4267316.540047753</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3716,13 +3716,13 @@
         <v>40.09999847412109</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>-0.005949471431804354</v>
+        <v>-0.005949471431804132</v>
       </c>
       <c r="F9" s="28" t="n">
-        <v>-4231.310311300214</v>
+        <v>-4231.310311300098</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>3562836.797548554</v>
+        <v>4267316.540047753</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3752,7 +3752,7 @@
         <v>74.00308946839505</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>3562836.797548554</v>
+        <v>4267316.540047753</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3782,7 +3782,7 @@
         <v>-456.3221797124534</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>3562836.797548554</v>
+        <v>4267316.540047753</v>
       </c>
       <c r="H11" s="29" t="n">
         <v>0.0520943075470665</v>
@@ -3812,7 +3812,7 @@
         <v>-1.164153218269348e-10</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>3562836.797548554</v>
+        <v>4267316.540047753</v>
       </c>
       <c r="H12" s="29" t="n">
         <v>0.0520943075470665</v>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -637,7 +637,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-11 04:51</t>
+          <t>Son Güncelleme: 2026-07-12 05:12</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1134,25 +1134,25 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.0737479211520321</v>
+        <v>0.07374792115203216</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>7374.79211520321</v>
+        <v>7374.792115203216</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0233118283326481</v>
+        <v>0.0233118283326483</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>171.919887778584</v>
+        <v>171.9198877785856</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>133.1328751118772</v>
+        <v>133.1328751118773</v>
       </c>
       <c r="I24" s="8" t="n">
         <v>122.850931549045</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.4183801650227493</v>
+        <v>0.4183801650227533</v>
       </c>
       <c r="K24" s="11" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-11 04:51</t>
+          <t>Son Güncelleme: 2026-07-12 05:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1790,13 +1790,13 @@
         <v>185.1000061035156</v>
       </c>
       <c r="E14" s="23" t="n">
-        <v>-0.0245806465802865</v>
+        <v>-0.0245806465802866</v>
       </c>
       <c r="F14" s="23" t="n">
         <v>0.0143885670157133</v>
       </c>
       <c r="G14" s="23" t="n">
-        <v>0.0729758361499268</v>
+        <v>0.0729758361499266</v>
       </c>
       <c r="H14" s="22" t="n">
         <v>180.5501282714762</v>
@@ -1805,7 +1805,7 @@
         <v>187.763329945945</v>
       </c>
       <c r="J14" s="22" t="n">
-        <v>198.6078338202763</v>
+        <v>198.6078338202762</v>
       </c>
       <c r="K14" s="22" t="n">
         <v>175.8450057983398</v>
@@ -1850,7 +1850,7 @@
         <v>-0.0557192483811474</v>
       </c>
       <c r="F15" s="20" t="n">
-        <v>0.0233118283326481</v>
+        <v>0.0233118283326483</v>
       </c>
       <c r="G15" s="20" t="n">
         <v>0.1272216922975995</v>
@@ -1859,7 +1859,7 @@
         <v>122.850931549045</v>
       </c>
       <c r="I15" s="19" t="n">
-        <v>133.1328751118772</v>
+        <v>133.1328751118773</v>
       </c>
       <c r="J15" s="19" t="n">
         <v>146.6515490479329</v>
@@ -1907,7 +1907,7 @@
         <v>-0.1065088329994344</v>
       </c>
       <c r="F16" s="17" t="n">
-        <v>-0.0199168792367259</v>
+        <v>-0.0199168792367256</v>
       </c>
       <c r="G16" s="17" t="n">
         <v>0.1064815305875086</v>
@@ -1916,7 +1916,7 @@
         <v>32.04059379398402</v>
       </c>
       <c r="I16" s="16" t="n">
-        <v>35.14578130876627</v>
+        <v>35.14578130876628</v>
       </c>
       <c r="J16" s="16" t="n">
         <v>39.67842836221079</v>
@@ -1964,10 +1964,10 @@
         <v>-0.0388692288111882</v>
       </c>
       <c r="F17" s="23" t="n">
-        <v>0.0138761110298257</v>
+        <v>0.0138761110298255</v>
       </c>
       <c r="G17" s="23" t="n">
-        <v>0.0600558756766196</v>
+        <v>0.0600558756766194</v>
       </c>
       <c r="H17" s="22" t="n">
         <v>100.8226193642755</v>
@@ -2048,7 +2048,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-11 04:51</t>
+          <t>Son Güncelleme: 2026-07-12 05:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2156,7 +2156,7 @@
         </is>
       </c>
       <c r="J4" s="17" t="n">
-        <v>0.0210892198914123</v>
+        <v>0.0210892198914124</v>
       </c>
       <c r="K4" s="17" t="n">
         <v>-0.0478684433228991</v>
@@ -2228,7 +2228,7 @@
         <v>-0.0357396440926404</v>
       </c>
       <c r="F6" s="20" t="n">
-        <v>-0.0228999651161745</v>
+        <v>-0.0228999651161747</v>
       </c>
       <c r="G6" s="20" t="n">
         <v>0.1854638270743971</v>
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="J8" s="17" t="n">
-        <v>0.0232520955933264</v>
+        <v>0.0232520955933265</v>
       </c>
       <c r="K8" s="17" t="n">
         <v>-0.008302551330894799</v>
@@ -2357,7 +2357,7 @@
         <v>0.0367495343186519</v>
       </c>
       <c r="F9" s="20" t="n">
-        <v>0.3727078620629436</v>
+        <v>0.3727078620629434</v>
       </c>
       <c r="G9" s="20" t="n">
         <v>0.6425849369727854</v>
@@ -2400,10 +2400,10 @@
         <v>0.0005405735325167</v>
       </c>
       <c r="F10" s="23" t="n">
-        <v>-0.08093340758166361</v>
+        <v>-0.08093340758166399</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>0.0492942938098481</v>
+        <v>0.0492942938098479</v>
       </c>
       <c r="H10" s="23" t="n">
         <v>0.1097622211770279</v>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="J10" s="23" t="n">
-        <v>0.0202677224988554</v>
+        <v>0.0202677224988553</v>
       </c>
       <c r="K10" s="23" t="n">
         <v>0.0143885670157133</v>
@@ -2460,7 +2460,7 @@
         <v>0.0239053454337624</v>
       </c>
       <c r="K11" s="20" t="n">
-        <v>0.0233118283326481</v>
+        <v>0.0233118283326483</v>
       </c>
     </row>
     <row r="12">
@@ -2503,7 +2503,7 @@
         <v>0.0293932688107371</v>
       </c>
       <c r="K12" s="17" t="n">
-        <v>-0.0199168792367259</v>
+        <v>-0.0199168792367256</v>
       </c>
     </row>
     <row r="13">
@@ -2529,7 +2529,7 @@
         <v>0.002868098050996</v>
       </c>
       <c r="F13" s="23" t="n">
-        <v>-0.0566546366480171</v>
+        <v>-0.0566546366480172</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>0.0526843945771198</v>
@@ -2546,7 +2546,7 @@
         <v>0.021978629617714</v>
       </c>
       <c r="K13" s="23" t="n">
-        <v>0.0138761110298257</v>
+        <v>0.0138761110298255</v>
       </c>
     </row>
     <row r="14">
@@ -2618,7 +2618,7 @@
         <v>-0.1005376180013021</v>
       </c>
       <c r="G15" s="25" t="n">
-        <v>-0.1894379457411047</v>
+        <v>-0.1894379457411048</v>
       </c>
       <c r="H15" s="25" t="n">
         <v>0.0238790800857664</v>
@@ -2758,10 +2758,10 @@
         </is>
       </c>
       <c r="J18" s="25" t="n">
-        <v>0.0235486104790141</v>
+        <v>0.0235486104790142</v>
       </c>
       <c r="K18" s="25" t="n">
-        <v>0.0296295530137169</v>
+        <v>0.0296295530137167</v>
       </c>
     </row>
     <row r="19">
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="J19" s="25" t="n">
-        <v>0.0170044822584004</v>
+        <v>0.0170044822584005</v>
       </c>
       <c r="K19" s="25" t="n">
         <v>0.0999999076690971</v>
@@ -2830,7 +2830,7 @@
         <v>-0.0754716832983692</v>
       </c>
       <c r="F20" s="25" t="n">
-        <v>-0.2057957165972301</v>
+        <v>-0.20579571659723</v>
       </c>
       <c r="G20" s="25" t="n">
         <v>-0.1475556752513833</v>
@@ -2878,7 +2878,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-11 04:51</t>
+          <t>Son Güncelleme: 2026-07-12 05:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2997,7 +2997,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-11 04:51</t>
+          <t>Son Güncelleme: 2026-07-12 05:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3248,7 +3248,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-11 04:51</t>
+          <t>Son Güncelleme: 2026-07-12 05:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3373,7 +3373,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-11 04:51</t>
+          <t>Son Güncelleme: 2026-07-12 05:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3450,7 +3450,7 @@
         <v>-65.32012378828949</v>
       </c>
       <c r="G4" s="26" t="n">
-        <v>4138744.760793019</v>
+        <v>4172120.154143265</v>
       </c>
       <c r="H4" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3480,7 +3480,7 @@
         <v>568.6440061870599</v>
       </c>
       <c r="G5" s="26" t="n">
-        <v>4138744.760793019</v>
+        <v>4172120.154143265</v>
       </c>
       <c r="H5" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3510,7 +3510,7 @@
         <v>-2162.636557778162</v>
       </c>
       <c r="G6" s="26" t="n">
-        <v>4138744.760793019</v>
+        <v>4172120.154143265</v>
       </c>
       <c r="H6" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3540,7 +3540,7 @@
         <v>-4936.472651186981</v>
       </c>
       <c r="G7" s="26" t="n">
-        <v>4138744.760793019</v>
+        <v>4172120.154143265</v>
       </c>
       <c r="H7" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3570,7 +3570,7 @@
         <v>-1207.911652180035</v>
       </c>
       <c r="G8" s="26" t="n">
-        <v>4138744.760793019</v>
+        <v>4172120.154143265</v>
       </c>
       <c r="H8" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3600,7 +3600,7 @@
         <v>-71858.69713852904</v>
       </c>
       <c r="G9" s="26" t="n">
-        <v>4138744.760793019</v>
+        <v>4172120.154143265</v>
       </c>
       <c r="H9" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3630,7 +3630,7 @@
         <v>-44007.74369329773</v>
       </c>
       <c r="G10" s="26" t="n">
-        <v>4138744.760793019</v>
+        <v>4172120.154143265</v>
       </c>
       <c r="H10" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3660,7 +3660,7 @@
         <v>-59.77284158069051</v>
       </c>
       <c r="G11" s="26" t="n">
-        <v>4138744.760793019</v>
+        <v>4172120.154143265</v>
       </c>
       <c r="H11" s="27" t="n">
         <v>0.0292907465429801</v>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -637,7 +637,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-12 05:12</t>
+          <t>Son Güncelleme: 2026-07-13 05:21</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1251,7 +1251,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-12 05:12</t>
+          <t>Son Güncelleme: 2026-07-13 05:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2048,7 +2048,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-12 05:12</t>
+          <t>Son Güncelleme: 2026-07-13 05:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2878,7 +2878,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-12 05:12</t>
+          <t>Son Güncelleme: 2026-07-13 05:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2997,7 +2997,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-12 05:12</t>
+          <t>Son Güncelleme: 2026-07-13 05:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3248,7 +3248,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-12 05:12</t>
+          <t>Son Güncelleme: 2026-07-13 05:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3373,7 +3373,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-12 05:12</t>
+          <t>Son Güncelleme: 2026-07-13 05:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3450,7 +3450,7 @@
         <v>-65.32012378828949</v>
       </c>
       <c r="G4" s="26" t="n">
-        <v>4172120.154143265</v>
+        <v>4205495.547493511</v>
       </c>
       <c r="H4" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3480,7 +3480,7 @@
         <v>568.6440061870599</v>
       </c>
       <c r="G5" s="26" t="n">
-        <v>4172120.154143265</v>
+        <v>4205495.547493511</v>
       </c>
       <c r="H5" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3510,7 +3510,7 @@
         <v>-2162.636557778162</v>
       </c>
       <c r="G6" s="26" t="n">
-        <v>4172120.154143265</v>
+        <v>4205495.547493511</v>
       </c>
       <c r="H6" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3540,7 +3540,7 @@
         <v>-4936.472651186981</v>
       </c>
       <c r="G7" s="26" t="n">
-        <v>4172120.154143265</v>
+        <v>4205495.547493511</v>
       </c>
       <c r="H7" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3570,7 +3570,7 @@
         <v>-1207.911652180035</v>
       </c>
       <c r="G8" s="26" t="n">
-        <v>4172120.154143265</v>
+        <v>4205495.547493511</v>
       </c>
       <c r="H8" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3600,7 +3600,7 @@
         <v>-71858.69713852904</v>
       </c>
       <c r="G9" s="26" t="n">
-        <v>4172120.154143265</v>
+        <v>4205495.547493511</v>
       </c>
       <c r="H9" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3630,7 +3630,7 @@
         <v>-44007.74369329773</v>
       </c>
       <c r="G10" s="26" t="n">
-        <v>4172120.154143265</v>
+        <v>4205495.547493511</v>
       </c>
       <c r="H10" s="27" t="n">
         <v>0.0292907465429801</v>
@@ -3660,7 +3660,7 @@
         <v>-59.77284158069051</v>
       </c>
       <c r="G11" s="26" t="n">
-        <v>4172120.154143265</v>
+        <v>4205495.547493511</v>
       </c>
       <c r="H11" s="27" t="n">
         <v>0.0292907465429801</v>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -646,7 +646,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-16 04:47</t>
+          <t>Son Güncelleme: 2026-07-17 04:51</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1411907502446492</v>
+        <v>0.1411907281111466</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>14119.07502446492</v>
+        <v>14119.07281111465</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>0.211966460056985</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>2992.770352214818</v>
+        <v>2992.769883058797</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>395.1010659785771</v>
@@ -1020,25 +1020,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1158182162300614</v>
+        <v>0.1158181990764193</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>11581.82162300614</v>
+        <v>11581.81990764193</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.1111299260656438</v>
+        <v>0.1111299294937776</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>1287.086980670147</v>
+        <v>1287.086829745878</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>327.7833281893649</v>
+        <v>327.7833292006644</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>280.1065641480559</v>
+        <v>280.1065641480558</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>2.201193097097575</v>
+        <v>2.201193164999927</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1061,25 +1061,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1004959051851134</v>
+        <v>0.1004959604649992</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>10049.59051851134</v>
+        <v>10049.59604649992</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0285884964496119</v>
+        <v>0.0285888522422834</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>287.3026828585149</v>
+        <v>287.3064164680217</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>395.4922768848758</v>
+        <v>395.492413687158</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>347.0838567671177</v>
+        <v>347.0838242840497</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.2937843383926182</v>
+        <v>0.2937877395757468</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
@@ -1102,25 +1102,25 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.08834742378690429</v>
+        <v>0.08834739475178791</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>8834.742378690429</v>
+        <v>8834.739475178791</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.0768722084891164</v>
+        <v>0.07687214851712661</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>679.1461580823228</v>
+        <v>679.1454050460652</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>375.2899646584571</v>
+        <v>375.2899437582186</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>325.9832118727351</v>
+        <v>325.983211872735</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>1.189777356656739</v>
+        <v>1.189776428449815</v>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
@@ -1143,25 +1143,25 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.05414770455327169</v>
+        <v>0.05414771759564697</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>5414.770455327169</v>
+        <v>5414.771759564697</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.029998132625555</v>
+        <v>0.0299982063440521</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>162.4330022558412</v>
+        <v>162.4334405493678</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>44.90791701082177</v>
+        <v>44.90792022494814</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>41.39471417403306</v>
+        <v>41.39471417403307</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.5930838652632977</v>
+        <v>0.593085322729063</v>
       </c>
       <c r="K24" s="11" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-16 04:47</t>
+          <t>Son Güncelleme: 2026-07-17 04:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1457,25 +1457,25 @@
         <v>384.5</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>-0.0973111657552205</v>
+        <v>-0.09731125023654159</v>
       </c>
       <c r="F8" s="17" t="n">
-        <v>0.0285884964496119</v>
+        <v>0.0285888522422834</v>
       </c>
       <c r="G8" s="17" t="n">
-        <v>0.0474812210724069</v>
+        <v>0.0474812157001536</v>
       </c>
       <c r="H8" s="16" t="n">
-        <v>347.0838567671177</v>
+        <v>347.0838242840497</v>
       </c>
       <c r="I8" s="16" t="n">
-        <v>395.4922768848758</v>
+        <v>395.492413687158</v>
       </c>
       <c r="J8" s="16" t="n">
-        <v>402.7565295023405</v>
+        <v>402.7565274367091</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>347.0838567671177</v>
+        <v>347.0838242840497</v>
       </c>
       <c r="L8" s="15" t="inlineStr">
         <is>
@@ -1571,25 +1571,25 @@
         <v>270.75</v>
       </c>
       <c r="E10" s="20" t="n">
-        <v>-0.1075472304912292</v>
+        <v>-0.1075471744334234</v>
       </c>
       <c r="F10" s="20" t="n">
-        <v>-0.0035847527809796</v>
+        <v>-0.0035848577601887</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>0.08512142993789459</v>
+        <v>0.0851215718148548</v>
       </c>
       <c r="H10" s="19" t="n">
-        <v>241.6315873444997</v>
+        <v>241.6316025221506</v>
       </c>
       <c r="I10" s="19" t="n">
-        <v>269.7794281845498</v>
+        <v>269.7793997614289</v>
       </c>
       <c r="J10" s="19" t="n">
-        <v>293.796627155685</v>
+        <v>293.796665568872</v>
       </c>
       <c r="K10" s="19" t="n">
-        <v>241.6315873444997</v>
+        <v>241.6316025221506</v>
       </c>
       <c r="L10" s="18" t="inlineStr">
         <is>
@@ -1631,22 +1631,22 @@
         <v>0.0081607762661732</v>
       </c>
       <c r="F11" s="17" t="n">
-        <v>0.1111299260656438</v>
+        <v>0.1111299294937776</v>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.1437536984966724</v>
+        <v>0.1437538499105514</v>
       </c>
       <c r="H11" s="16" t="n">
         <v>297.4074289985211</v>
       </c>
       <c r="I11" s="16" t="n">
-        <v>327.7833281893649</v>
+        <v>327.7833292006644</v>
       </c>
       <c r="J11" s="16" t="n">
-        <v>337.4073410565183</v>
+        <v>337.4073857236127</v>
       </c>
       <c r="K11" s="16" t="n">
-        <v>280.1065641480559</v>
+        <v>280.1065641480558</v>
       </c>
       <c r="L11" s="15" t="inlineStr">
         <is>
@@ -1685,22 +1685,22 @@
         <v>191.1000061035156</v>
       </c>
       <c r="E12" s="23" t="n">
-        <v>-0.0031018111585281</v>
+        <v>-0.0031017381985415</v>
       </c>
       <c r="F12" s="23" t="n">
-        <v>0.0259674251026877</v>
+        <v>0.025967427052516</v>
       </c>
       <c r="G12" s="23" t="n">
-        <v>0.0466708728798923</v>
+        <v>0.0466707608184535</v>
       </c>
       <c r="H12" s="22" t="n">
-        <v>190.5072499721889</v>
+        <v>190.5072639148428</v>
       </c>
       <c r="I12" s="22" t="n">
-        <v>196.0623811991318</v>
+        <v>196.0623815717441</v>
       </c>
       <c r="J12" s="22" t="n">
-        <v>200.0188101957195</v>
+        <v>200.0187887807778</v>
       </c>
       <c r="K12" s="22" t="n">
         <v>181.5450057983398</v>
@@ -1745,7 +1745,7 @@
         <v>-0.0615866518007279</v>
       </c>
       <c r="F13" s="20" t="n">
-        <v>-0.0157859170736172</v>
+        <v>-0.0157857473464384</v>
       </c>
       <c r="G13" s="20" t="n">
         <v>0.0100401434839101</v>
@@ -1754,7 +1754,7 @@
         <v>103.4131481077495</v>
       </c>
       <c r="I13" s="19" t="n">
-        <v>108.4603889349044</v>
+        <v>108.4604076388389</v>
       </c>
       <c r="J13" s="19" t="n">
         <v>111.306420729529</v>
@@ -1802,7 +1802,7 @@
         <v>-0.0161982288834289</v>
       </c>
       <c r="F14" s="17" t="n">
-        <v>0.0768722084891164</v>
+        <v>0.07687214851712661</v>
       </c>
       <c r="G14" s="17" t="n">
         <v>0.2234482270298656</v>
@@ -1811,13 +1811,13 @@
         <v>342.854917234125</v>
       </c>
       <c r="I14" s="16" t="n">
-        <v>375.2899646584571</v>
+        <v>375.2899437582186</v>
       </c>
       <c r="J14" s="16" t="n">
         <v>426.3717071199082</v>
       </c>
       <c r="K14" s="16" t="n">
-        <v>325.9832118727351</v>
+        <v>325.983211872735</v>
       </c>
       <c r="L14" s="15" t="inlineStr">
         <is>
@@ -1859,19 +1859,19 @@
         <v>-0.0609999645366716</v>
       </c>
       <c r="F15" s="20" t="n">
-        <v>-0.0254998112759489</v>
+        <v>-0.0254997257062651</v>
       </c>
       <c r="G15" s="20" t="n">
-        <v>0.082112718269422</v>
+        <v>0.08211272221694969</v>
       </c>
       <c r="H15" s="19" t="n">
         <v>39.32532248816444</v>
       </c>
       <c r="I15" s="19" t="n">
-        <v>40.81206894464176</v>
+        <v>40.81207252830021</v>
       </c>
       <c r="J15" s="19" t="n">
-        <v>45.31888179694447</v>
+        <v>45.31888196226694</v>
       </c>
       <c r="K15" s="19" t="n">
         <v>39.32532248816444</v>
@@ -1973,7 +1973,7 @@
         <v>-0.0338140537472411</v>
       </c>
       <c r="F17" s="17" t="n">
-        <v>0.029998132625555</v>
+        <v>0.0299982063440521</v>
       </c>
       <c r="G17" s="17" t="n">
         <v>0.111591751941328</v>
@@ -1982,13 +1982,13 @@
         <v>42.12570578233753</v>
       </c>
       <c r="I17" s="16" t="n">
-        <v>44.90791701082177</v>
+        <v>44.90792022494814</v>
       </c>
       <c r="J17" s="16" t="n">
         <v>48.4653986884875</v>
       </c>
       <c r="K17" s="16" t="n">
-        <v>41.39471417403306</v>
+        <v>41.39471417403307</v>
       </c>
       <c r="L17" s="15" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-16 04:47</t>
+          <t>Son Güncelleme: 2026-07-17 04:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="J4" s="17" t="n">
-        <v>0.0196644721393515</v>
+        <v>0.0196644721393516</v>
       </c>
       <c r="K4" s="17" t="n">
-        <v>0.0285884964496119</v>
+        <v>0.0285888522422834</v>
       </c>
     </row>
     <row r="5">
@@ -2311,7 +2311,7 @@
         <v>0.0227658524144454</v>
       </c>
       <c r="K6" s="20" t="n">
-        <v>-0.0035847527809796</v>
+        <v>-0.0035848577601887</v>
       </c>
     </row>
     <row r="7">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="J7" s="17" t="n">
-        <v>0.0252431116134646</v>
+        <v>0.0252431116134647</v>
       </c>
       <c r="K7" s="17" t="n">
-        <v>0.1111299260656438</v>
+        <v>0.1111299294937776</v>
       </c>
     </row>
     <row r="8">
@@ -2397,7 +2397,7 @@
         <v>0.0207599110986449</v>
       </c>
       <c r="K8" s="23" t="n">
-        <v>0.0259674251026877</v>
+        <v>0.025967427052516</v>
       </c>
     </row>
     <row r="9">
@@ -2440,7 +2440,7 @@
         <v>0.0216927332752226</v>
       </c>
       <c r="K9" s="20" t="n">
-        <v>-0.0157859170736172</v>
+        <v>-0.0157857473464384</v>
       </c>
     </row>
     <row r="10">
@@ -2480,10 +2480,10 @@
         </is>
       </c>
       <c r="J10" s="17" t="n">
-        <v>0.0323052914307962</v>
+        <v>0.0323052914307963</v>
       </c>
       <c r="K10" s="17" t="n">
-        <v>0.0768722084891164</v>
+        <v>0.07687214851712661</v>
       </c>
     </row>
     <row r="11">
@@ -2526,7 +2526,7 @@
         <v>0.0268438090323615</v>
       </c>
       <c r="K11" s="20" t="n">
-        <v>-0.0254998112759489</v>
+        <v>-0.0254997257062651</v>
       </c>
     </row>
     <row r="12">
@@ -2609,10 +2609,10 @@
         </is>
       </c>
       <c r="J13" s="17" t="n">
-        <v>0.0252899584548952</v>
+        <v>0.0252899584548951</v>
       </c>
       <c r="K13" s="17" t="n">
-        <v>0.029998132625555</v>
+        <v>0.0299982063440521</v>
       </c>
     </row>
     <row r="14">
@@ -2698,7 +2698,7 @@
         <v>0.0238212180877457</v>
       </c>
       <c r="K15" s="28" t="n">
-        <v>0.0044790800861671</v>
+        <v>0.0044791569432763</v>
       </c>
     </row>
     <row r="16">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="J16" s="28" t="n">
-        <v>0.0294479348541073</v>
+        <v>0.0294479348541072</v>
       </c>
       <c r="K16" s="28" t="n">
-        <v>0.0024287491670588</v>
+        <v>0.0024286871265271</v>
       </c>
     </row>
     <row r="17">
@@ -2784,7 +2784,7 @@
         <v>0.0226186848606233</v>
       </c>
       <c r="K17" s="28" t="n">
-        <v>0.0283622708857007</v>
+        <v>0.0283623502202803</v>
       </c>
     </row>
     <row r="18">
@@ -2827,7 +2827,7 @@
         <v>0.0165054412771882</v>
       </c>
       <c r="K18" s="28" t="n">
-        <v>0.0423503831348128</v>
+        <v>0.0423504428390855</v>
       </c>
     </row>
     <row r="19">
@@ -2867,7 +2867,7 @@
         </is>
       </c>
       <c r="J19" s="28" t="n">
-        <v>0.0294480866932792</v>
+        <v>0.0294480866932793</v>
       </c>
       <c r="K19" s="28" t="n">
         <v>0.06673212298112791</v>
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="J20" s="28" t="n">
-        <v>0.0200612149228342</v>
+        <v>0.0200612149228341</v>
       </c>
       <c r="K20" s="28" t="inlineStr"/>
     </row>
@@ -2944,7 +2944,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-16 04:47</t>
+          <t>Son Güncelleme: 2026-07-17 04:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3063,7 +3063,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-16 04:47</t>
+          <t>Son Güncelleme: 2026-07-17 04:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3314,7 +3314,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-16 04:47</t>
+          <t>Son Güncelleme: 2026-07-17 04:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14080</v>
+        <v>14251.2998046875</v>
       </c>
     </row>
     <row r="5">
@@ -3348,7 +3348,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>12745.84003417969</v>
+        <v>12760.26203125</v>
       </c>
     </row>
     <row r="6">
@@ -3439,7 +3439,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-16 04:47</t>
+          <t>Son Güncelleme: 2026-07-17 04:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -637,7 +637,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-18 04:36</t>
+          <t>Son Güncelleme: 2026-07-19 04:57</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -977,7 +977,7 @@
         <v>0.1047501547505572</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1361.849145534137</v>
+        <v>1361.849145534138</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>336.9487971989199</v>
@@ -1020,7 +1020,7 @@
         <v>0.0436044762683809</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>480.7314187874006</v>
+        <v>480.7314187874007</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>344.3894771685657</v>
@@ -1052,16 +1052,16 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.09676731342591428</v>
+        <v>0.09676731342591423</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>9676.731342591429</v>
+        <v>9676.731342591424</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>0.07687214851712661</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>743.8711289280222</v>
+        <v>743.8711289280219</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>379.5974323522872</v>
@@ -1070,7 +1070,7 @@
         <v>329.6993168810639</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>1.188448267577676</v>
+        <v>1.188448267577674</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
@@ -1093,16 +1093,16 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.09533883249165311</v>
+        <v>0.09533883249165313</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>9533.88324916531</v>
+        <v>9533.883249165314</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>0.025967427052516</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>247.5704177999044</v>
+        <v>247.5704177999045</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>202.1155831293457</v>
@@ -1134,25 +1134,25 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.06763640027756311</v>
+        <v>0.06763640027756314</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>6763.640027756311</v>
+        <v>6763.640027756313</v>
       </c>
       <c r="F24" s="7" t="n">
         <v>0.0333833966972141</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>225.7932781637451</v>
+        <v>225.7932781637452</v>
       </c>
       <c r="H24" s="8" t="n">
         <v>46.50225285137464</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>42.69473037002698</v>
+        <v>42.69473037002699</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.6516603662506142</v>
+        <v>0.6516603662506162</v>
       </c>
       <c r="K24" s="11" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-18 04:36</t>
+          <t>Son Güncelleme: 2026-07-19 04:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1676,7 +1676,7 @@
         <v>197</v>
       </c>
       <c r="E12" s="20" t="n">
-        <v>-0.0031018113855404</v>
+        <v>-0.0031018113855402</v>
       </c>
       <c r="F12" s="20" t="n">
         <v>0.025967427052516</v>
@@ -1685,7 +1685,7 @@
         <v>0.0466708728798923</v>
       </c>
       <c r="H12" s="19" t="n">
-        <v>196.3889431570485</v>
+        <v>196.3889431570486</v>
       </c>
       <c r="I12" s="19" t="n">
         <v>202.1155831293457</v>
@@ -1739,7 +1739,7 @@
         <v>-0.0157858315348814</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.0139753607082788</v>
+        <v>0.013975360708279</v>
       </c>
       <c r="H13" s="16" t="n">
         <v>105.2899748041481</v>
@@ -1967,7 +1967,7 @@
         <v>0.0333833966972141</v>
       </c>
       <c r="G17" s="20" t="n">
-        <v>0.1048109348623858</v>
+        <v>0.1048109348623857</v>
       </c>
       <c r="H17" s="19" t="n">
         <v>43.47836758137415</v>
@@ -1979,7 +1979,7 @@
         <v>49.71649206880736</v>
       </c>
       <c r="K17" s="19" t="n">
-        <v>42.69473037002698</v>
+        <v>42.69473037002699</v>
       </c>
       <c r="L17" s="18" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="D18" s="22" t="n">
-        <v>90.30000305175781</v>
+        <v>90.3000030517578</v>
       </c>
       <c r="E18" s="23" t="n">
         <v>-0.1036950453198939</v>
@@ -2027,16 +2027,16 @@
         <v>0.0283370511511488</v>
       </c>
       <c r="H18" s="22" t="n">
-        <v>80.93634014291922</v>
+        <v>80.93634014291921</v>
       </c>
       <c r="I18" s="22" t="n">
-        <v>87.90467175975154</v>
+        <v>87.90467175975152</v>
       </c>
       <c r="J18" s="22" t="n">
-        <v>92.85883885718435</v>
+        <v>92.85883885718434</v>
       </c>
       <c r="K18" s="22" t="n">
-        <v>80.93634014291922</v>
+        <v>80.93634014291921</v>
       </c>
       <c r="L18" s="21" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>-0.0361423551605843</v>
       </c>
       <c r="F19" s="23" t="n">
-        <v>-0.0007077205736818</v>
+        <v>-0.0007077205736817</v>
       </c>
       <c r="G19" s="23" t="n">
         <v>0.1552276165943749</v>
@@ -2087,7 +2087,7 @@
         <v>161.6389240981099</v>
       </c>
       <c r="I19" s="22" t="n">
-        <v>167.5813122101955</v>
+        <v>167.5813122101956</v>
       </c>
       <c r="J19" s="22" t="n">
         <v>193.7316677774018</v>
@@ -2162,7 +2162,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-18 04:36</t>
+          <t>Son Güncelleme: 2026-07-19 04:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2296,13 +2296,13 @@
         </is>
       </c>
       <c r="E5" s="17" t="n">
-        <v>0.2699645419310046</v>
+        <v>0.2699645419310044</v>
       </c>
       <c r="F5" s="17" t="n">
         <v>0.0700934579439251</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.3637918713419257</v>
+        <v>0.3637918713419255</v>
       </c>
       <c r="H5" s="17" t="n">
         <v>0.021181247850716</v>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="J5" s="17" t="n">
-        <v>0.0238092956020326</v>
+        <v>0.0238092956020327</v>
       </c>
       <c r="K5" s="17" t="n">
         <v>-0.0267075881338385</v>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="J7" s="20" t="n">
-        <v>0.0248090483605681</v>
+        <v>0.024809048360568</v>
       </c>
       <c r="K7" s="20" t="n">
         <v>0.1047501547505572</v>
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="E8" s="20" t="n">
-        <v>-0.0154922839028397</v>
+        <v>-0.0154922839028396</v>
       </c>
       <c r="F8" s="20" t="n">
         <v>-0.0450799947367163</v>
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="J8" s="20" t="n">
-        <v>0.0210928877011063</v>
+        <v>0.0210928877011062</v>
       </c>
       <c r="K8" s="20" t="n">
         <v>0.025967427052516</v>
@@ -2471,7 +2471,7 @@
         <v>-0.0260416673565352</v>
       </c>
       <c r="F9" s="17" t="n">
-        <v>-0.035253705897935</v>
+        <v>-0.0352537058979348</v>
       </c>
       <c r="G9" s="17" t="n">
         <v>0.1032448408562265</v>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="J9" s="17" t="n">
-        <v>0.0218090949713451</v>
+        <v>0.0218090949713452</v>
       </c>
       <c r="K9" s="17" t="n">
         <v>-0.0157858315348814</v>
@@ -2517,7 +2517,7 @@
         <v>0.4195514021586155</v>
       </c>
       <c r="G10" s="17" t="n">
-        <v>0.7472256708514629</v>
+        <v>0.7472256708514631</v>
       </c>
       <c r="H10" s="17" t="n">
         <v>-0.0966077990495649</v>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="J11" s="20" t="n">
-        <v>0.0323413944949448</v>
+        <v>0.0323413944949449</v>
       </c>
       <c r="K11" s="20" t="n">
         <v>0.07687214851712661</v>
@@ -2640,13 +2640,13 @@
         </is>
       </c>
       <c r="E13" s="20" t="n">
-        <v>-0.0204614422030583</v>
+        <v>-0.0204614422030581</v>
       </c>
       <c r="F13" s="20" t="n">
-        <v>-0.0518956693664893</v>
+        <v>-0.0518956693664892</v>
       </c>
       <c r="G13" s="20" t="n">
-        <v>0.1846376939669889</v>
+        <v>0.1846376939669887</v>
       </c>
       <c r="H13" s="20" t="n">
         <v>-0.08927798507305711</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="J13" s="20" t="n">
-        <v>0.0256141069997002</v>
+        <v>0.0256141069997001</v>
       </c>
       <c r="K13" s="20" t="n">
         <v>0.0333833966972141</v>
@@ -2700,10 +2700,10 @@
         </is>
       </c>
       <c r="J14" s="25" t="n">
-        <v>0.0294643191802923</v>
+        <v>0.0294643191802922</v>
       </c>
       <c r="K14" s="25" t="n">
-        <v>0.0558806111879733</v>
+        <v>0.0558806111879734</v>
       </c>
     </row>
     <row r="15">
@@ -2729,10 +2729,10 @@
         <v>-0.1041666635129818</v>
       </c>
       <c r="F15" s="23" t="n">
-        <v>-0.1014925069476834</v>
+        <v>-0.1014925069476836</v>
       </c>
       <c r="G15" s="23" t="n">
-        <v>-0.0176581311770364</v>
+        <v>-0.0176581311770365</v>
       </c>
       <c r="H15" s="23" t="n">
         <v>-0.0323755999692956</v>
@@ -2815,10 +2815,10 @@
         <v>-0.0885869731073794</v>
       </c>
       <c r="F17" s="23" t="n">
-        <v>-0.1036879130006019</v>
+        <v>-0.1036879130006018</v>
       </c>
       <c r="G17" s="23" t="n">
-        <v>-0.1491629033224522</v>
+        <v>-0.149162903322452</v>
       </c>
       <c r="H17" s="23" t="n">
         <v>-0.0486293813820859</v>
@@ -2832,7 +2832,7 @@
         <v>0.0209242476671809</v>
       </c>
       <c r="K17" s="23" t="n">
-        <v>-0.0007077205736818</v>
+        <v>-0.0007077205736817</v>
       </c>
     </row>
     <row r="18">
@@ -2858,7 +2858,7 @@
         <v>-0.0630331898187573</v>
       </c>
       <c r="F18" s="25" t="n">
-        <v>-0.1608659090552879</v>
+        <v>-0.1608659090552878</v>
       </c>
       <c r="G18" s="25" t="n">
         <v>-0.1134529284832188</v>
@@ -2872,7 +2872,7 @@
         </is>
       </c>
       <c r="J18" s="25" t="n">
-        <v>0.0165367731826493</v>
+        <v>0.0165367731826494</v>
       </c>
       <c r="K18" s="25" t="n">
         <v>0.0531914626506075</v>
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="J19" s="25" t="n">
-        <v>0.0293944691265913</v>
+        <v>0.0293944691265912</v>
       </c>
       <c r="K19" s="25" t="n">
         <v>0.0999999916062814</v>
@@ -2941,13 +2941,13 @@
         </is>
       </c>
       <c r="E20" s="25" t="n">
-        <v>-0.0755750415689177</v>
+        <v>-0.07557504156891739</v>
       </c>
       <c r="F20" s="25" t="n">
         <v>-0.2045240081085867</v>
       </c>
       <c r="G20" s="25" t="n">
-        <v>-0.1407812215898962</v>
+        <v>-0.1407812215898961</v>
       </c>
       <c r="H20" s="25" t="n">
         <v>-0.1771614345863863</v>
@@ -2994,7 +2994,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-18 04:36</t>
+          <t>Son Güncelleme: 2026-07-19 04:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3113,7 +3113,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-18 04:36</t>
+          <t>Son Güncelleme: 2026-07-19 04:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3364,7 +3364,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-18 04:36</t>
+          <t>Son Güncelleme: 2026-07-19 04:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3489,7 +3489,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-18 04:36</t>
+          <t>Son Güncelleme: 2026-07-19 04:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3566,7 +3566,7 @@
         <v>454.9145851775429</v>
       </c>
       <c r="G4" s="26" t="n">
-        <v>4429896.600449844</v>
+        <v>7336241.340194726</v>
       </c>
       <c r="H4" s="27" t="n">
         <v>0.039937230347891</v>
@@ -3596,7 +3596,7 @@
         <v>-329.6703296703308</v>
       </c>
       <c r="G5" s="26" t="n">
-        <v>4429896.600449844</v>
+        <v>7336241.340194726</v>
       </c>
       <c r="H5" s="27" t="n">
         <v>0.039937230347891</v>
@@ -3626,7 +3626,7 @@
         <v>-134.212405797778</v>
       </c>
       <c r="G6" s="26" t="n">
-        <v>4429896.600449844</v>
+        <v>7336241.340194726</v>
       </c>
       <c r="H6" s="27" t="n">
         <v>0.039937230347891</v>
@@ -3656,7 +3656,7 @@
         <v>-82879.96970578819</v>
       </c>
       <c r="G7" s="26" t="n">
-        <v>4429896.600449844</v>
+        <v>7336241.340194726</v>
       </c>
       <c r="H7" s="27" t="n">
         <v>0.039937230347891</v>
@@ -3686,7 +3686,7 @@
         <v>-2751.438172919472</v>
       </c>
       <c r="G8" s="26" t="n">
-        <v>4429896.600449844</v>
+        <v>7336241.340194726</v>
       </c>
       <c r="H8" s="27" t="n">
         <v>0.039937230347891</v>
@@ -3716,7 +3716,7 @@
         <v>-8189.448336457834</v>
       </c>
       <c r="G9" s="26" t="n">
-        <v>4429896.600449844</v>
+        <v>7336241.340194726</v>
       </c>
       <c r="H9" s="27" t="n">
         <v>0.039937230347891</v>
@@ -3746,7 +3746,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="26" t="n">
-        <v>4429896.600449844</v>
+        <v>7336241.340194726</v>
       </c>
       <c r="H10" s="27" t="n">
         <v>0.039937230347891</v>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -637,7 +637,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-19 04:57</t>
+          <t>Son Güncelleme: 2026-07-20 05:26</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1251,7 +1251,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-19 04:57</t>
+          <t>Son Güncelleme: 2026-07-20 05:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2162,7 +2162,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-19 04:57</t>
+          <t>Son Güncelleme: 2026-07-20 05:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2994,7 +2994,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-19 04:57</t>
+          <t>Son Güncelleme: 2026-07-20 05:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3113,7 +3113,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-19 04:57</t>
+          <t>Son Güncelleme: 2026-07-20 05:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3364,7 +3364,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-19 04:57</t>
+          <t>Son Güncelleme: 2026-07-20 05:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3489,7 +3489,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-19 04:57</t>
+          <t>Son Güncelleme: 2026-07-20 05:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3566,7 +3566,7 @@
         <v>454.9145851775429</v>
       </c>
       <c r="G4" s="26" t="n">
-        <v>7336241.340194726</v>
+        <v>10242586.07993961</v>
       </c>
       <c r="H4" s="27" t="n">
         <v>0.039937230347891</v>
@@ -3596,7 +3596,7 @@
         <v>-329.6703296703308</v>
       </c>
       <c r="G5" s="26" t="n">
-        <v>7336241.340194726</v>
+        <v>10242586.07993961</v>
       </c>
       <c r="H5" s="27" t="n">
         <v>0.039937230347891</v>
@@ -3626,7 +3626,7 @@
         <v>-134.212405797778</v>
       </c>
       <c r="G6" s="26" t="n">
-        <v>7336241.340194726</v>
+        <v>10242586.07993961</v>
       </c>
       <c r="H6" s="27" t="n">
         <v>0.039937230347891</v>
@@ -3656,7 +3656,7 @@
         <v>-82879.96970578819</v>
       </c>
       <c r="G7" s="26" t="n">
-        <v>7336241.340194726</v>
+        <v>10242586.07993961</v>
       </c>
       <c r="H7" s="27" t="n">
         <v>0.039937230347891</v>
@@ -3686,7 +3686,7 @@
         <v>-2751.438172919472</v>
       </c>
       <c r="G8" s="26" t="n">
-        <v>7336241.340194726</v>
+        <v>10242586.07993961</v>
       </c>
       <c r="H8" s="27" t="n">
         <v>0.039937230347891</v>
@@ -3716,7 +3716,7 @@
         <v>-8189.448336457834</v>
       </c>
       <c r="G9" s="26" t="n">
-        <v>7336241.340194726</v>
+        <v>10242586.07993961</v>
       </c>
       <c r="H9" s="27" t="n">
         <v>0.039937230347891</v>
@@ -3746,7 +3746,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="26" t="n">
-        <v>7336241.340194726</v>
+        <v>10242586.07993961</v>
       </c>
       <c r="H10" s="27" t="n">
         <v>0.039937230347891</v>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -630,7 +630,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-25 04:53</t>
+          <t>Son Güncelleme: 2026-07-26 05:17</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1004,16 +1004,16 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1061157987449863</v>
+        <v>0.1061157987449862</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>10611.57987449863</v>
+        <v>10611.57987449862</v>
       </c>
       <c r="F21" s="7" t="n">
         <v>0.0439164979259993</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>466.0234255499948</v>
+        <v>466.0234255499947</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>392.7735823446573</v>
@@ -1054,7 +1054,7 @@
         <v>0.0343566853834971</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>349.6367099705449</v>
+        <v>349.6367099705448</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>205.009491886403</v>
@@ -1086,16 +1086,16 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.09680149841362548</v>
+        <v>0.09680149841362547</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>9680.149841362549</v>
+        <v>9680.149841362547</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>0.0532805395405533</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>515.763606381198</v>
+        <v>515.7636063811979</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>301.5015544434834</v>
@@ -1127,16 +1127,16 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.07961307892339649</v>
+        <v>0.07961307892339654</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>7961.307892339649</v>
+        <v>7961.307892339654</v>
       </c>
       <c r="F24" s="7" t="n">
         <v>0.0662461449400904</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>527.405956548618</v>
+        <v>527.4059565486184</v>
       </c>
       <c r="H24" s="8" t="n">
         <v>35.46334499104866</v>
@@ -1145,7 +1145,7 @@
         <v>31.34528912709862</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>1.150747422073201</v>
+        <v>1.150747422073205</v>
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-25 04:53</t>
+          <t>Son Güncelleme: 2026-07-26 05:17</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1498,7 +1498,7 @@
         <v>314.5</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>-0.09857152200522271</v>
+        <v>-0.0985715220052225</v>
       </c>
       <c r="F9" s="18" t="n">
         <v>-0.0267076945339092</v>
@@ -1612,7 +1612,7 @@
         <v>22.55999946594238</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>-0.0480530189205196</v>
+        <v>-0.0480530189205198</v>
       </c>
       <c r="F11" s="18" t="n">
         <v>-0.0151488195452038</v>
@@ -1732,7 +1732,7 @@
         <v>0.0089213306645721</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>0.1846002415757828</v>
+        <v>0.184600241575783</v>
       </c>
       <c r="H13" s="20" t="n">
         <v>296.6181496934038</v>
@@ -1786,7 +1786,7 @@
         <v>-0.0609999645366716</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>-0.0154052729933271</v>
+        <v>-0.015405272993327</v>
       </c>
       <c r="G14" s="18" t="n">
         <v>0.0525822108985147</v>
@@ -1840,7 +1840,7 @@
         <v>286.25</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>0.0192863783331422</v>
+        <v>0.019286378333142</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0.0532805395405533</v>
@@ -1849,7 +1849,7 @@
         <v>0.084836584704717</v>
       </c>
       <c r="H15" s="14" t="n">
-        <v>291.770725797862</v>
+        <v>291.7707257978619</v>
       </c>
       <c r="I15" s="14" t="n">
         <v>301.5015544434834</v>
@@ -2014,7 +2014,7 @@
         <v>-0.0462686718992926</v>
       </c>
       <c r="F18" s="24" t="n">
-        <v>-0.0007077205736818</v>
+        <v>-0.0007077205736817</v>
       </c>
       <c r="G18" s="24" t="n">
         <v>0.1518716549814833</v>
@@ -2155,7 +2155,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-25 04:53</t>
+          <t>Son Güncelleme: 2026-07-26 05:17</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2289,7 +2289,7 @@
         </is>
       </c>
       <c r="E5" s="18" t="n">
-        <v>0.4269510377015333</v>
+        <v>0.4269510377015331</v>
       </c>
       <c r="F5" s="18" t="n">
         <v>0.2406311637080866</v>
@@ -2524,7 +2524,7 @@
         <v>0.0280762215956702</v>
       </c>
       <c r="K10" s="18" t="n">
-        <v>-0.0154052729933271</v>
+        <v>-0.015405272993327</v>
       </c>
     </row>
     <row r="11">
@@ -2593,7 +2593,7 @@
         <v>-0.054054054054054</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>-0.08933220103328331</v>
+        <v>-0.0893322010332832</v>
       </c>
       <c r="G12" s="18" t="n">
         <v>-0.004739336492891</v>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="J12" s="18" t="n">
-        <v>0.0227482826335469</v>
+        <v>0.022748282633547</v>
       </c>
       <c r="K12" s="18" t="n">
         <v>-0.0223463826050375</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="J13" s="15" t="n">
-        <v>0.0287839640868978</v>
+        <v>0.0287839640868977</v>
       </c>
       <c r="K13" s="15" t="n">
         <v>0.0662461449400904</v>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="J17" s="24" t="n">
-        <v>0.019334221948612</v>
+        <v>0.0193342219486119</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>-0.0007077205736818</v>
+        <v>-0.0007077205736817</v>
       </c>
     </row>
     <row r="18">
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="J18" s="26" t="n">
-        <v>0.0159758845365429</v>
+        <v>0.015975884536543</v>
       </c>
       <c r="K18" s="26" t="n">
         <v>0.0384313523279102</v>
@@ -2908,7 +2908,7 @@
         </is>
       </c>
       <c r="J19" s="26" t="n">
-        <v>0.0280471682847775</v>
+        <v>0.0280471682847774</v>
       </c>
       <c r="K19" s="26" t="n">
         <v>0.06497451176343599</v>
@@ -2987,7 +2987,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-25 04:53</t>
+          <t>Son Güncelleme: 2026-07-26 05:17</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-25 04:53</t>
+          <t>Son Güncelleme: 2026-07-26 05:17</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3357,7 +3357,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-25 04:53</t>
+          <t>Son Güncelleme: 2026-07-26 05:17</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3482,7 +3482,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-25 04:53</t>
+          <t>Son Güncelleme: 2026-07-26 05:17</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -630,7 +630,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-26 05:17</t>
+          <t>Son Güncelleme: 2026-07-27 05:35</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1244,7 +1244,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-26 05:17</t>
+          <t>Son Güncelleme: 2026-07-27 05:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2155,7 +2155,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-26 05:17</t>
+          <t>Son Güncelleme: 2026-07-27 05:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2987,7 +2987,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-26 05:17</t>
+          <t>Son Güncelleme: 2026-07-27 05:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-26 05:17</t>
+          <t>Son Güncelleme: 2026-07-27 05:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3357,7 +3357,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-26 05:17</t>
+          <t>Son Güncelleme: 2026-07-27 05:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3482,7 +3482,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-26 05:17</t>
+          <t>Son Güncelleme: 2026-07-27 05:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-01 05:14</t>
+          <t>Son Güncelleme: 2026-08-02 05:13</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -978,7 +978,7 @@
         <v>0.057165502871556</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>739.8365501968819</v>
+        <v>739.8365501968822</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>304.4636648270081</v>
@@ -1012,25 +1012,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1090027888193446</v>
+        <v>0.1090027888193445</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>10900.27888193446</v>
+        <v>10900.27888193445</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0184997945881833</v>
+        <v>0.0184997945881831</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>201.6529202696998</v>
+        <v>201.6529202696975</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>390.0854213272742</v>
+        <v>390.0854213272741</v>
       </c>
       <c r="I21" s="8" t="n">
         <v>361.816597715633</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.334479855131823</v>
+        <v>0.3344798551318176</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>0.0535513188368701</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>558.9610131012665</v>
+        <v>558.9610131012668</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>355.5735701074437</v>
@@ -1094,10 +1094,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.08855294943930817</v>
+        <v>0.08855294943930818</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>8855.294943930816</v>
+        <v>8855.294943930818</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>0.0185280737323094</v>
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.06864558375910687</v>
+        <v>0.0686455837591069</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>6864.558375910687</v>
+        <v>6864.55837591069</v>
       </c>
       <c r="F24" s="7" t="n">
         <v>0.0238096245652548</v>
@@ -1153,7 +1153,7 @@
         <v>28.2992428565673</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.273293125713912</v>
+        <v>0.2732931257139113</v>
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-01 05:14</t>
+          <t>Son Güncelleme: 2026-08-02 05:13</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1509,7 +1509,7 @@
         <v>-0.0553091443456059</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>0.0184997945881833</v>
+        <v>0.0184997945881831</v>
       </c>
       <c r="G9" s="16" t="n">
         <v>0.0814958906985057</v>
@@ -1518,7 +1518,7 @@
         <v>361.816597715633</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>390.0854213272742</v>
+        <v>390.0854213272741</v>
       </c>
       <c r="J9" s="15" t="n">
         <v>414.2129261375277</v>
@@ -1563,10 +1563,10 @@
         <v>308.25</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>-0.0557183387298561</v>
+        <v>-0.0557183387298559</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>0.0063375475858378</v>
+        <v>0.0063375475858379</v>
       </c>
       <c r="G10" s="19" t="n">
         <v>0.1846001644787691</v>
@@ -1626,7 +1626,7 @@
         <v>0.0535513188368701</v>
       </c>
       <c r="G11" s="16" t="n">
-        <v>0.1516948423836668</v>
+        <v>0.151694842383667</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>315.5624893475263</v>
@@ -1677,7 +1677,7 @@
         <v>42.40000152587891</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>-0.0603687366609073</v>
+        <v>-0.0603687366609074</v>
       </c>
       <c r="F12" s="22" t="n">
         <v>-0.0181817200022263</v>
@@ -1686,7 +1686,7 @@
         <v>0.0613532271160165</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>39.84036699934106</v>
+        <v>39.84036699934105</v>
       </c>
       <c r="I12" s="21" t="n">
         <v>41.62909657004141</v>
@@ -1695,7 +1695,7 @@
         <v>45.0013784492156</v>
       </c>
       <c r="K12" s="21" t="n">
-        <v>39.84036699934106</v>
+        <v>39.84036699934105</v>
       </c>
       <c r="L12" s="20" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>191.5</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>-0.0083587415184747</v>
+        <v>-0.008358741518474801</v>
       </c>
       <c r="F13" s="16" t="n">
         <v>0.0185280737323094</v>
@@ -1791,16 +1791,16 @@
         <v>101.5</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>-0.0616850558301536</v>
+        <v>-0.0616850558301534</v>
       </c>
       <c r="F14" s="22" t="n">
         <v>-0.0232804071164443</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>0.0289375192237391</v>
+        <v>0.0289375192237388</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>95.2389668332394</v>
+        <v>95.23896683323943</v>
       </c>
       <c r="I14" s="21" t="n">
         <v>99.13703867768091</v>
@@ -1809,7 +1809,7 @@
         <v>104.4371582012095</v>
       </c>
       <c r="K14" s="21" t="n">
-        <v>95.2389668332394</v>
+        <v>95.23896683323943</v>
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>19.01000022888184</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>20.07129459190576</v>
+        <v>20.07129459190577</v>
       </c>
       <c r="K15" s="18" t="n">
         <v>17.84444362991376</v>
@@ -1962,13 +1962,13 @@
         <v>31</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>-0.0871211981752482</v>
+        <v>-0.0871211981752484</v>
       </c>
       <c r="F17" s="16" t="n">
         <v>0.0238096245652548</v>
       </c>
       <c r="G17" s="16" t="n">
-        <v>0.0792951206779122</v>
+        <v>0.079295120677912</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>28.2992428565673</v>
@@ -1977,7 +1977,7 @@
         <v>31.7380983615229</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>33.45814874101528</v>
+        <v>33.45814874101527</v>
       </c>
       <c r="K17" s="15" t="n">
         <v>28.2992428565673</v>
@@ -2106,7 +2106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-01 05:14</t>
+          <t>Son Güncelleme: 2026-08-02 05:13</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2260,7 +2260,7 @@
         <v>0.020736118110066</v>
       </c>
       <c r="K5" s="16" t="n">
-        <v>0.0184997945881833</v>
+        <v>0.0184997945881831</v>
       </c>
     </row>
     <row r="6">
@@ -2303,7 +2303,7 @@
         <v>0.0216824464777646</v>
       </c>
       <c r="K6" s="19" t="n">
-        <v>0.0063375475858378</v>
+        <v>0.0063375475858379</v>
       </c>
     </row>
     <row r="7">
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="J10" s="22" t="n">
-        <v>0.0224080999198344</v>
+        <v>0.0224080999198345</v>
       </c>
       <c r="K10" s="22" t="n">
         <v>-0.0232804071164443</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="E11" s="19" t="n">
-        <v>-0.0052328821703729</v>
+        <v>-0.0052328821703726</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>-0.2340853963488951</v>
+        <v>-0.2340853963488949</v>
       </c>
       <c r="G11" s="19" t="n">
         <v>0.0439319706002252</v>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="J12" s="19" t="n">
-        <v>0.0261229653188725</v>
+        <v>0.0261229653188726</v>
       </c>
       <c r="K12" s="19" t="n">
         <v>0.0050933786078097</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="J13" s="16" t="n">
-        <v>0.0290376821986274</v>
+        <v>0.0290376821986273</v>
       </c>
       <c r="K13" s="16" t="n">
         <v>0.0238096245652548</v>
@@ -2676,7 +2676,7 @@
         <v>-0.1440457436747242</v>
       </c>
       <c r="G15" s="25" t="n">
-        <v>-0.2066204726021715</v>
+        <v>-0.2066204726021714</v>
       </c>
       <c r="H15" s="25" t="n">
         <v>0.1007071692957457</v>
@@ -2716,7 +2716,7 @@
         <v>-0.0668171362404083</v>
       </c>
       <c r="F16" s="27" t="n">
-        <v>-0.08724310524054101</v>
+        <v>-0.0872431052405412</v>
       </c>
       <c r="G16" s="27" t="n">
         <v>0.0061819138307206</v>
@@ -2730,7 +2730,7 @@
         </is>
       </c>
       <c r="J16" s="27" t="n">
-        <v>0.0253707760054063</v>
+        <v>0.0253707760054064</v>
       </c>
       <c r="K16" s="27" t="n">
         <v>0.0287515535773972</v>
@@ -2759,7 +2759,7 @@
         <v>-0.02466026155884</v>
       </c>
       <c r="F17" s="27" t="n">
-        <v>-0.1371326901815062</v>
+        <v>-0.1371326901815061</v>
       </c>
       <c r="G17" s="27" t="n">
         <v>-0.1499999866150972</v>
@@ -2805,7 +2805,7 @@
         <v>-0.1697376221065171</v>
       </c>
       <c r="G18" s="27" t="n">
-        <v>-0.2523881271427706</v>
+        <v>-0.2523881271427707</v>
       </c>
       <c r="H18" s="27" t="n">
         <v>0.0354464643980367</v>
@@ -2819,7 +2819,7 @@
         <v>0.0198916910720305</v>
       </c>
       <c r="K18" s="27" t="n">
-        <v>0.009701613552635499</v>
+        <v>0.0097016135526356</v>
       </c>
     </row>
     <row r="19">
@@ -2842,10 +2842,10 @@
         </is>
       </c>
       <c r="E19" s="27" t="n">
-        <v>-0.2000000198166092</v>
+        <v>-0.2000000198166093</v>
       </c>
       <c r="F19" s="27" t="n">
-        <v>-0.1641790905719934</v>
+        <v>-0.1641790905719935</v>
       </c>
       <c r="G19" s="27" t="n">
         <v>-0.250744843998032</v>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="J19" s="27" t="n">
-        <v>0.0282262795302659</v>
+        <v>0.0282262795302658</v>
       </c>
       <c r="K19" s="27" t="n">
         <v>0.0759492964836558</v>
@@ -2888,10 +2888,10 @@
         <v>-0.0928445395644775</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>-0.2177461034064992</v>
+        <v>-0.2177461034064991</v>
       </c>
       <c r="G20" s="27" t="n">
-        <v>-0.2807583314076235</v>
+        <v>-0.2807583314076234</v>
       </c>
       <c r="H20" s="27" t="n">
         <v>-0.1020340293017442</v>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="J20" s="27" t="n">
-        <v>0.0194542362354065</v>
+        <v>0.0194542362354064</v>
       </c>
       <c r="K20" s="27" t="n">
         <v>0.1002252939750626</v>
@@ -2938,7 +2938,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-01 05:14</t>
+          <t>Son Güncelleme: 2026-08-02 05:13</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3057,7 +3057,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-01 05:14</t>
+          <t>Son Güncelleme: 2026-08-02 05:13</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3308,7 +3308,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-01 05:14</t>
+          <t>Son Güncelleme: 2026-08-02 05:13</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3433,7 +3433,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-01 05:14</t>
+          <t>Son Güncelleme: 2026-08-02 05:13</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-02 05:13</t>
+          <t>Son Güncelleme: 2026-08-03 05:26</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-02 05:13</t>
+          <t>Son Güncelleme: 2026-08-03 05:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2106,7 +2106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-02 05:13</t>
+          <t>Son Güncelleme: 2026-08-03 05:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2938,7 +2938,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-02 05:13</t>
+          <t>Son Güncelleme: 2026-08-03 05:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3057,7 +3057,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-02 05:13</t>
+          <t>Son Güncelleme: 2026-08-03 05:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3308,7 +3308,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-02 05:13</t>
+          <t>Son Güncelleme: 2026-08-03 05:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3433,7 +3433,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-02 05:13</t>
+          <t>Son Güncelleme: 2026-08-03 05:26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-03 05:26</t>
+          <t>Son Güncelleme: 2026-08-04 04:52</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -969,25 +969,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1294201070633815</v>
+        <v>0.1294201302157204</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>12942.01070633815</v>
+        <v>12942.01302157204</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.057165502871556</v>
+        <v>0.0571655276246191</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>739.8365501968822</v>
+        <v>739.8370029028566</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>304.4636648270081</v>
+        <v>304.4636719558903</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>269.3710133334368</v>
+        <v>269.3710282642439</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.8837659890840134</v>
+        <v>0.8837670800847366</v>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
@@ -1012,25 +1012,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1090027888193445</v>
+        <v>0.1090028071327864</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>10900.27888193445</v>
+        <v>10900.28071327864</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0184997945881831</v>
+        <v>0.0184998271357302</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>201.6529202696975</v>
+        <v>201.6533089265887</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>390.0854213272741</v>
+        <v>390.0854337929846</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>361.816597715633</v>
+        <v>361.8166023514825</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.3344798551318176</v>
+        <v>0.3344805167966291</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1053,16 +1053,16 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1043785709188588</v>
+        <v>0.1043785775170885</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>10437.85709188588</v>
+        <v>10437.85775170885</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>0.0535513188368701</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>558.9610131012668</v>
+        <v>558.9610484356566</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>355.5735701074437</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.08855294943930818</v>
+        <v>0.08855291398532347</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>8855.294943930818</v>
+        <v>8855.291398532347</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.0185280737323094</v>
+        <v>0.0185279555776163</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>164.0715576424968</v>
+        <v>164.070445658855</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>195.0481261197373</v>
+        <v>195.0481034931135</v>
       </c>
       <c r="I23" s="8" t="n">
         <v>181.925</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.37056147464619</v>
+        <v>0.3705591115523262</v>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.0686455837591069</v>
+        <v>0.06864557114908122</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>6864.55837591069</v>
+        <v>6864.557114908122</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0238096245652548</v>
+        <v>0.0238095584443063</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>163.4425577367087</v>
+        <v>163.4420738216836</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>31.7380983615229</v>
+        <v>31.7380963117735</v>
       </c>
       <c r="I24" s="8" t="n">
         <v>28.2992428565673</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.2732931257139113</v>
+        <v>0.2732923667602955</v>
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-03 05:26</t>
+          <t>Son Güncelleme: 2026-08-04 04:52</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1449,25 +1449,25 @@
         <v>288</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.0646839814811222</v>
+        <v>-0.064683929638042</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.057165502871556</v>
+        <v>0.0571655276246191</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.1505434775960539</v>
+        <v>0.1505434643863876</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>269.3710133334368</v>
+        <v>269.3710282642439</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>304.4636648270081</v>
+        <v>304.4636719558903</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>331.3565215476635</v>
+        <v>331.3565177432797</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>269.3710133334368</v>
+        <v>269.3710282642439</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
@@ -1506,25 +1506,25 @@
         <v>383</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>-0.0553091443456059</v>
+        <v>-0.0553091322415601</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>0.0184997945881831</v>
+        <v>0.0184998271357302</v>
       </c>
       <c r="G9" s="16" t="n">
-        <v>0.0814958906985057</v>
+        <v>0.0814962596984995</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>361.816597715633</v>
+        <v>361.8166023514825</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>390.0854213272741</v>
+        <v>390.0854337929846</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>414.2129261375277</v>
+        <v>414.2130674645254</v>
       </c>
       <c r="K9" s="15" t="n">
-        <v>361.816597715633</v>
+        <v>361.8166023514825</v>
       </c>
       <c r="L9" s="14" t="inlineStr">
         <is>
@@ -1563,25 +1563,25 @@
         <v>308.25</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>-0.0557183387298559</v>
+        <v>-0.0557185041218549</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>0.0063375475858379</v>
+        <v>0.00633754713377</v>
       </c>
       <c r="G10" s="19" t="n">
-        <v>0.1846001644787691</v>
+        <v>0.1846002415757828</v>
       </c>
       <c r="H10" s="18" t="n">
-        <v>291.0748220865219</v>
+        <v>291.0747711044382</v>
       </c>
       <c r="I10" s="18" t="n">
-        <v>310.2035490433345</v>
+        <v>310.2035489039847</v>
       </c>
       <c r="J10" s="18" t="n">
-        <v>365.1530007005806</v>
+        <v>365.153024465735</v>
       </c>
       <c r="K10" s="18" t="n">
-        <v>291.0748220865219</v>
+        <v>291.0747711044382</v>
       </c>
       <c r="L10" s="17" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>0.0535513188368701</v>
       </c>
       <c r="G11" s="16" t="n">
-        <v>0.151694842383667</v>
+        <v>0.1516950211453938</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>315.5624893475263</v>
@@ -1635,7 +1635,7 @@
         <v>355.5735701074437</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>388.6970093044876</v>
+        <v>388.6970696365704</v>
       </c>
       <c r="K11" s="15" t="n">
         <v>315.5624893475263</v>
@@ -1677,25 +1677,25 @@
         <v>42.40000152587891</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>-0.0603687366609074</v>
+        <v>-0.0603687118615568</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>-0.0181817200022263</v>
+        <v>-0.0181818861523047</v>
       </c>
       <c r="G12" s="22" t="n">
-        <v>0.0613532271160165</v>
+        <v>0.0613531469582715</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>39.84036699934105</v>
+        <v>39.84036805083355</v>
       </c>
       <c r="I12" s="21" t="n">
-        <v>41.62909657004141</v>
+        <v>41.62908952527783</v>
       </c>
       <c r="J12" s="21" t="n">
-        <v>45.0013784492156</v>
+        <v>45.00137505052709</v>
       </c>
       <c r="K12" s="21" t="n">
-        <v>39.84036699934105</v>
+        <v>39.84036805083355</v>
       </c>
       <c r="L12" s="20" t="inlineStr">
         <is>
@@ -1734,22 +1734,22 @@
         <v>191.5</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>-0.008358741518474801</v>
+        <v>-0.0083587023213938</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>0.0185280737323094</v>
+        <v>0.0185279555776163</v>
       </c>
       <c r="G13" s="16" t="n">
-        <v>0.0757753717076345</v>
+        <v>0.0757754432413195</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>189.8993009992121</v>
+        <v>189.8993085054531</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>195.0481261197373</v>
+        <v>195.0481034931135</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>206.010983682012</v>
+        <v>206.0109973807127</v>
       </c>
       <c r="K13" s="15" t="n">
         <v>181.925</v>
@@ -1791,25 +1791,25 @@
         <v>101.5</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>-0.0616850558301534</v>
+        <v>-0.0616850558301536</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>-0.0232804071164443</v>
+        <v>-0.0232805184548855</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>0.0289375192237388</v>
+        <v>0.0289374356535263</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>95.23896683323943</v>
+        <v>95.2389668332394</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>99.13703867768091</v>
+        <v>99.13702737682912</v>
       </c>
       <c r="J14" s="21" t="n">
-        <v>104.4371582012095</v>
+        <v>104.4371497188329</v>
       </c>
       <c r="K14" s="21" t="n">
-        <v>95.23896683323943</v>
+        <v>95.2389668332394</v>
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>19.01000022888184</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>20.07129459190577</v>
+        <v>20.07129459190576</v>
       </c>
       <c r="K15" s="18" t="n">
         <v>17.84444362991376</v>
@@ -1905,25 +1905,25 @@
         <v>260.5</v>
       </c>
       <c r="E16" s="19" t="n">
-        <v>-0.0713413812853959</v>
+        <v>-0.0713413679291167</v>
       </c>
       <c r="F16" s="19" t="n">
         <v>0.0050933786078097</v>
       </c>
       <c r="G16" s="19" t="n">
-        <v>0.1023868619897293</v>
+        <v>0.1023869095225903</v>
       </c>
       <c r="H16" s="18" t="n">
-        <v>241.9155701751544</v>
+        <v>241.9155736544651</v>
       </c>
       <c r="I16" s="18" t="n">
         <v>261.8268251273345</v>
       </c>
       <c r="J16" s="18" t="n">
-        <v>287.1717775483245</v>
+        <v>287.1717899306348</v>
       </c>
       <c r="K16" s="18" t="n">
-        <v>241.9155701751544</v>
+        <v>241.9155736544651</v>
       </c>
       <c r="L16" s="17" t="inlineStr">
         <is>
@@ -1962,22 +1962,22 @@
         <v>31</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>-0.0871211981752484</v>
+        <v>-0.0871211981752482</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>0.0238096245652548</v>
+        <v>0.0238095584443063</v>
       </c>
       <c r="G17" s="16" t="n">
-        <v>0.079295120677912</v>
+        <v>0.0792953142437882</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>28.2992428565673</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>31.7380983615229</v>
+        <v>31.7380963117735</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>33.45814874101527</v>
+        <v>33.45815474155744</v>
       </c>
       <c r="K17" s="15" t="n">
         <v>28.2992428565673</v>
@@ -2106,7 +2106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-03 05:26</t>
+          <t>Son Güncelleme: 2026-08-04 04:52</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2217,7 +2217,7 @@
         <v>0.0240855922651444</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.057165502871556</v>
+        <v>0.0571655276246191</v>
       </c>
     </row>
     <row r="5">
@@ -2260,7 +2260,7 @@
         <v>0.020736118110066</v>
       </c>
       <c r="K5" s="16" t="n">
-        <v>0.0184997945881831</v>
+        <v>0.0184998271357302</v>
       </c>
     </row>
     <row r="6">
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="J6" s="19" t="n">
-        <v>0.0216824464777646</v>
+        <v>0.0216824464777645</v>
       </c>
       <c r="K6" s="19" t="n">
-        <v>0.0063375475858379</v>
+        <v>0.00633754713377</v>
       </c>
     </row>
     <row r="7">
@@ -2389,7 +2389,7 @@
         <v>0.0278304305933973</v>
       </c>
       <c r="K8" s="22" t="n">
-        <v>-0.0181817200022263</v>
+        <v>-0.0181818861523047</v>
       </c>
     </row>
     <row r="9">
@@ -2432,7 +2432,7 @@
         <v>0.0208004752934908</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>0.0185280737323094</v>
+        <v>0.0185279555776163</v>
       </c>
     </row>
     <row r="10">
@@ -2475,7 +2475,7 @@
         <v>0.0224080999198345</v>
       </c>
       <c r="K10" s="22" t="n">
-        <v>-0.0232804071164443</v>
+        <v>-0.0232805184548855</v>
       </c>
     </row>
     <row r="11">
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="E11" s="19" t="n">
-        <v>-0.0052328821703726</v>
+        <v>-0.0052328821703729</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>-0.2340853963488949</v>
+        <v>-0.2340853963488951</v>
       </c>
       <c r="G11" s="19" t="n">
         <v>0.0439319706002252</v>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="J12" s="19" t="n">
-        <v>0.0261229653188726</v>
+        <v>0.0261229653188725</v>
       </c>
       <c r="K12" s="19" t="n">
         <v>0.0050933786078097</v>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="J13" s="16" t="n">
-        <v>0.0290376821986273</v>
+        <v>0.0290376821986274</v>
       </c>
       <c r="K13" s="16" t="n">
-        <v>0.0238096245652548</v>
+        <v>0.0238095584443063</v>
       </c>
     </row>
     <row r="14">
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="J14" s="27" t="n">
-        <v>0.0221556678262782</v>
+        <v>0.0221556678262783</v>
       </c>
       <c r="K14" s="27" t="n">
-        <v>0.0156794711232165</v>
+        <v>0.0156795465450354</v>
       </c>
     </row>
     <row r="15">
@@ -2676,7 +2676,7 @@
         <v>-0.1440457436747242</v>
       </c>
       <c r="G15" s="25" t="n">
-        <v>-0.2066204726021714</v>
+        <v>-0.2066204726021715</v>
       </c>
       <c r="H15" s="25" t="n">
         <v>0.1007071692957457</v>
@@ -2716,7 +2716,7 @@
         <v>-0.0668171362404083</v>
       </c>
       <c r="F16" s="27" t="n">
-        <v>-0.0872431052405412</v>
+        <v>-0.08724310524054101</v>
       </c>
       <c r="G16" s="27" t="n">
         <v>0.0061819138307206</v>
@@ -2730,7 +2730,7 @@
         </is>
       </c>
       <c r="J16" s="27" t="n">
-        <v>0.0253707760054064</v>
+        <v>0.0253707760054063</v>
       </c>
       <c r="K16" s="27" t="n">
         <v>0.0287515535773972</v>
@@ -2759,7 +2759,7 @@
         <v>-0.02466026155884</v>
       </c>
       <c r="F17" s="27" t="n">
-        <v>-0.1371326901815061</v>
+        <v>-0.1371326901815062</v>
       </c>
       <c r="G17" s="27" t="n">
         <v>-0.1499999866150972</v>
@@ -2776,7 +2776,7 @@
         <v>0.015715253363987</v>
       </c>
       <c r="K17" s="27" t="n">
-        <v>0.1196572591075438</v>
+        <v>0.1196572855882683</v>
       </c>
     </row>
     <row r="18">
@@ -2805,7 +2805,7 @@
         <v>-0.1697376221065171</v>
       </c>
       <c r="G18" s="27" t="n">
-        <v>-0.2523881271427707</v>
+        <v>-0.2523881271427706</v>
       </c>
       <c r="H18" s="27" t="n">
         <v>0.0354464643980367</v>
@@ -2819,7 +2819,7 @@
         <v>0.0198916910720305</v>
       </c>
       <c r="K18" s="27" t="n">
-        <v>0.0097016135526356</v>
+        <v>0.009701613552635499</v>
       </c>
     </row>
     <row r="19">
@@ -2842,10 +2842,10 @@
         </is>
       </c>
       <c r="E19" s="27" t="n">
-        <v>-0.2000000198166093</v>
+        <v>-0.2000000198166092</v>
       </c>
       <c r="F19" s="27" t="n">
-        <v>-0.1641790905719935</v>
+        <v>-0.1641790905719934</v>
       </c>
       <c r="G19" s="27" t="n">
         <v>-0.250744843998032</v>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="J19" s="27" t="n">
-        <v>0.0282262795302658</v>
+        <v>0.0282262795302659</v>
       </c>
       <c r="K19" s="27" t="n">
         <v>0.0759492964836558</v>
@@ -2888,10 +2888,10 @@
         <v>-0.0928445395644775</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>-0.2177461034064991</v>
+        <v>-0.2177461034064992</v>
       </c>
       <c r="G20" s="27" t="n">
-        <v>-0.2807583314076234</v>
+        <v>-0.2807583314076235</v>
       </c>
       <c r="H20" s="27" t="n">
         <v>-0.1020340293017442</v>
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="J20" s="27" t="n">
-        <v>0.0194542362354064</v>
+        <v>0.0194542362354065</v>
       </c>
       <c r="K20" s="27" t="n">
-        <v>0.1002252939750626</v>
+        <v>0.1002252058410154</v>
       </c>
     </row>
   </sheetData>
@@ -2938,7 +2938,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-03 05:26</t>
+          <t>Son Güncelleme: 2026-08-04 04:52</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3057,7 +3057,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-03 05:26</t>
+          <t>Son Güncelleme: 2026-08-04 04:52</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3308,7 +3308,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-03 05:26</t>
+          <t>Son Güncelleme: 2026-08-04 04:52</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3433,7 +3433,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-03 05:26</t>
+          <t>Son Güncelleme: 2026-08-04 04:52</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-08 03:15</t>
+          <t>Son Güncelleme: 2026-08-09 03:23</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -978,7 +978,7 @@
         <v>0.0493707647628267</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>636.773828896617</v>
+        <v>636.7738288966171</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>337.3727008712488</v>
@@ -1027,7 +1027,7 @@
         <v>205.0428176087989</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>186.1049942016601</v>
+        <v>186.1049942016602</v>
       </c>
       <c r="J21" s="6" t="n">
         <v>0.9334174575978448</v>
@@ -1056,22 +1056,22 @@
         <v>0.1019676292204013</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>10196.76292204013</v>
+        <v>10196.76292204012</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0485935360435065</v>
+        <v>0.0485935360435063</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>495.4967665792475</v>
+        <v>495.4967665792454</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>400.8248791526304</v>
+        <v>400.8248791526303</v>
       </c>
       <c r="I22" s="8" t="n">
         <v>363.1375</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.9718707208701309</v>
+        <v>0.9718707208701279</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.09651783980938428</v>
+        <v>0.0965178398093843</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>9651.783980938428</v>
+        <v>9651.78398093843</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>0.0535513188368701</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>516.8657613078291</v>
+        <v>516.8657613078292</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>382.4391287377838</v>
@@ -1147,13 +1147,13 @@
         <v>69.67315506435257</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>129.2054889307282</v>
+        <v>129.2054889307281</v>
       </c>
       <c r="I24" s="8" t="n">
         <v>117.0125159007824</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.1302885333071543</v>
+        <v>0.130288533307153</v>
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>0.5000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>50000.00000000001</v>
+        <v>50000</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-08 03:15</t>
+          <t>Son Güncelleme: 2026-08-09 03:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1506,7 +1506,7 @@
         <v>195.8999938964844</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>-0.0031018113855404</v>
+        <v>-0.0031018113855402</v>
       </c>
       <c r="F9" s="16" t="n">
         <v>0.0466708728798923</v>
@@ -1521,10 +1521,10 @@
         <v>205.0428176087989</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>212.4432543504554</v>
+        <v>212.4432543504555</v>
       </c>
       <c r="K9" s="15" t="n">
-        <v>186.1049942016601</v>
+        <v>186.1049942016602</v>
       </c>
       <c r="L9" s="14" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>-0.009829009969016899</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>0.0485935360435065</v>
+        <v>0.0485935360435063</v>
       </c>
       <c r="G10" s="16" t="n">
         <v>0.1486668544898615</v>
@@ -1575,7 +1575,7 @@
         <v>378.4928609393433</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>400.8248791526304</v>
+        <v>400.8248791526303</v>
       </c>
       <c r="J10" s="15" t="n">
         <v>439.0779051287495</v>
@@ -1734,25 +1734,25 @@
         <v>105.3000030517578</v>
       </c>
       <c r="E13" s="19" t="n">
-        <v>-0.0616850558301536</v>
+        <v>-0.0616850558301534</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>-0.0093592552096705</v>
+        <v>-0.009359255209670601</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>0.0535268260817061</v>
+        <v>0.0535268260817058</v>
       </c>
       <c r="H13" s="18" t="n">
-        <v>98.80456648459479</v>
+        <v>98.8045664845948</v>
       </c>
       <c r="I13" s="18" t="n">
         <v>104.3144734496173</v>
       </c>
       <c r="J13" s="18" t="n">
-        <v>110.9363780015124</v>
+        <v>110.9363780015123</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>98.80456648459479</v>
+        <v>98.8045664845948</v>
       </c>
       <c r="L13" s="17" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>19.05999946594238</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>-0.0432524986932348</v>
+        <v>-0.0432524986932347</v>
       </c>
       <c r="F14" s="22" t="n">
         <v>0.002557432846991</v>
@@ -1800,7 +1800,7 @@
         <v>0.06315792247529731</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>18.23560686394865</v>
+        <v>18.23560686394866</v>
       </c>
       <c r="I14" s="21" t="n">
         <v>19.10874413464022</v>
@@ -1854,7 +1854,7 @@
         <v>-0.0341997901255592</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>0.1273843626077347</v>
+        <v>0.1273843626077345</v>
       </c>
       <c r="H15" s="18" t="n">
         <v>289.0519869030868</v>
@@ -1974,7 +1974,7 @@
         <v>117.0125159007824</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>129.2054889307282</v>
+        <v>129.2054889307281</v>
       </c>
       <c r="J17" s="15" t="n">
         <v>135.0575066694285</v>
@@ -2019,7 +2019,7 @@
         <v>67.09999847412109</v>
       </c>
       <c r="E18" s="25" t="n">
-        <v>-0.0666066214119836</v>
+        <v>-0.0666066214119837</v>
       </c>
       <c r="F18" s="25" t="n">
         <v>-0.0216543725047507</v>
@@ -2106,7 +2106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-08 03:15</t>
+          <t>Son Güncelleme: 2026-08-09 03:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2203,7 +2203,7 @@
         <v>0.2401157184185149</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>0.4602270876535832</v>
+        <v>0.4602270876535834</v>
       </c>
       <c r="H4" s="16" t="n">
         <v>0.2304124079553751</v>
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="E5" s="16" t="n">
-        <v>0.0354122465978423</v>
+        <v>0.0354122465978425</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>-0.07375889410645679</v>
+        <v>-0.0737588941064567</v>
       </c>
       <c r="G5" s="16" t="n">
-        <v>-0.0229583630481745</v>
+        <v>-0.0229583630481744</v>
       </c>
       <c r="H5" s="16" t="n">
         <v>0.1578562564107331</v>
@@ -2303,7 +2303,7 @@
         <v>0.0202481395738857</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>0.0485935360435065</v>
+        <v>0.0485935360435063</v>
       </c>
     </row>
     <row r="7">
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="E9" s="19" t="n">
-        <v>-0.0268021624609804</v>
+        <v>-0.0268021624609806</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>-0.1121416154593406</v>
+        <v>-0.1121416154593408</v>
       </c>
       <c r="G9" s="19" t="n">
         <v>-0.1098901070553001</v>
@@ -2432,7 +2432,7 @@
         <v>0.0229823679178929</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>-0.0093592552096705</v>
+        <v>-0.009359255209670601</v>
       </c>
     </row>
     <row r="10">
@@ -2458,10 +2458,10 @@
         <v>-0.0052192266318432</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>-0.1978114780161616</v>
+        <v>-0.1978114780161617</v>
       </c>
       <c r="G10" s="22" t="n">
-        <v>0.0381262980566652</v>
+        <v>0.0381262980566654</v>
       </c>
       <c r="H10" s="22" t="n">
         <v>0.2620627924084371</v>
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="E12" s="19" t="n">
-        <v>-0.0946807899751375</v>
+        <v>-0.09468078997513719</v>
       </c>
       <c r="F12" s="19" t="n">
         <v>-0.1195033354919691</v>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="J12" s="19" t="n">
-        <v>0.0295235758046596</v>
+        <v>0.0295235758046595</v>
       </c>
       <c r="K12" s="19" t="n">
         <v>-0.0089743807627755</v>
@@ -2584,13 +2584,13 @@
         </is>
       </c>
       <c r="E13" s="16" t="n">
-        <v>-0.0491070769676516</v>
+        <v>-0.0491070769676517</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>-0.07122094925188691</v>
+        <v>-0.071220949251887</v>
       </c>
       <c r="G13" s="16" t="n">
-        <v>-0.1771997464649704</v>
+        <v>-0.1771997464649705</v>
       </c>
       <c r="H13" s="16" t="n">
         <v>0.09552174833303501</v>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="E14" s="27" t="n">
-        <v>-0.0506465993865901</v>
+        <v>-0.05064659938659</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>-0.1190000152587891</v>
@@ -2647,7 +2647,7 @@
         <v>0.0210311854786991</v>
       </c>
       <c r="K14" s="27" t="n">
-        <v>0.0394097287801945</v>
+        <v>0.0394097287801946</v>
       </c>
     </row>
     <row r="15">
@@ -2730,7 +2730,7 @@
         </is>
       </c>
       <c r="J16" s="27" t="n">
-        <v>0.0254119805740714</v>
+        <v>0.0254119805740715</v>
       </c>
       <c r="K16" s="27" t="n">
         <v>0.0357561195683878</v>
@@ -2799,7 +2799,7 @@
         </is>
       </c>
       <c r="E18" s="27" t="n">
-        <v>-0.0080971966300317</v>
+        <v>-0.0080971966300315</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>-0.1478260869565217</v>
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="J18" s="27" t="n">
-        <v>0.0152928955505609</v>
+        <v>0.015292895550561</v>
       </c>
       <c r="K18" s="27" t="n">
         <v>0.1120622093111625</v>
@@ -2891,7 +2891,7 @@
         <v>-0.2052578638883636</v>
       </c>
       <c r="G20" s="27" t="n">
-        <v>-0.2979484965286054</v>
+        <v>-0.2979484965286055</v>
       </c>
       <c r="H20" s="27" t="n">
         <v>-0.07856065964472959</v>
@@ -2938,7 +2938,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-08 03:15</t>
+          <t>Son Güncelleme: 2026-08-09 03:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3057,7 +3057,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-08 03:15</t>
+          <t>Son Güncelleme: 2026-08-09 03:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3308,7 +3308,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-08 03:15</t>
+          <t>Son Güncelleme: 2026-08-09 03:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3411,8 +3411,8 @@
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -3433,7 +3433,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-08 03:15</t>
+          <t>Son Güncelleme: 2026-08-09 03:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3510,7 +3510,7 @@
         <v>-2386.812482561385</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>10100525.50440948</v>
+        <v>10158339.7140869</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0.006917674013974</v>
@@ -3540,7 +3540,7 @@
         <v>-64364.23179279291</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>10100525.50440948</v>
+        <v>10158339.7140869</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0.006917674013974</v>
@@ -3564,13 +3564,13 @@
         <v>195.8999938964844</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>-0.00558378732749043</v>
+        <v>-0.005583787327490319</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>-16228.41092710616</v>
+        <v>-16228.4109271057</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>10100525.50440948</v>
+        <v>10158339.7140869</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0.006917674013974</v>
@@ -3600,7 +3600,7 @@
         <v>-62904.35692547169</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>10100525.50440948</v>
+        <v>10158339.7140869</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0.006917674013974</v>
@@ -3630,7 +3630,7 @@
         <v>197115.9711043495</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>10100525.50440948</v>
+        <v>10158339.7140869</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0.006917674013974</v>
@@ -3654,13 +3654,13 @@
         <v>127.8000030517578</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="F9" s="28" t="n">
-        <v>0</v>
+        <v>-7.275957614183426e-12</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>10100525.50440948</v>
+        <v>10158339.7140869</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0.006917674013974</v>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-09 03:23</t>
+          <t>Son Güncelleme: 2026-08-10 03:42</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-09 03:23</t>
+          <t>Son Güncelleme: 2026-08-10 03:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2106,7 +2106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-09 03:23</t>
+          <t>Son Güncelleme: 2026-08-10 03:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2938,7 +2938,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-09 03:23</t>
+          <t>Son Güncelleme: 2026-08-10 03:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3057,7 +3057,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-09 03:23</t>
+          <t>Son Güncelleme: 2026-08-10 03:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3308,7 +3308,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-09 03:23</t>
+          <t>Son Güncelleme: 2026-08-10 03:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3412,7 +3412,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -3433,7 +3433,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-09 03:23</t>
+          <t>Son Güncelleme: 2026-08-10 03:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3510,7 +3510,7 @@
         <v>-2386.812482561385</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>10158339.7140869</v>
+        <v>10216153.92376433</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0.006917674013974</v>
@@ -3540,7 +3540,7 @@
         <v>-64364.23179279291</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>10158339.7140869</v>
+        <v>10216153.92376433</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0.006917674013974</v>
@@ -3570,7 +3570,7 @@
         <v>-16228.4109271057</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>10158339.7140869</v>
+        <v>10216153.92376433</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0.006917674013974</v>
@@ -3600,7 +3600,7 @@
         <v>-62904.35692547169</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>10158339.7140869</v>
+        <v>10216153.92376433</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0.006917674013974</v>
@@ -3630,7 +3630,7 @@
         <v>197115.9711043495</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>10158339.7140869</v>
+        <v>10216153.92376433</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0.006917674013974</v>
@@ -3660,7 +3660,7 @@
         <v>-7.275957614183426e-12</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>10158339.7140869</v>
+        <v>10216153.92376433</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0.006917674013974</v>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -637,7 +637,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-15 02:43</t>
+          <t>Son Güncelleme: 2026-08-16 02:50</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1251,7 +1251,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-15 02:43</t>
+          <t>Son Güncelleme: 2026-08-16 02:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1568,7 +1568,7 @@
         <v>0.0439164979259993</v>
       </c>
       <c r="G10" s="17" t="n">
-        <v>0.1382006157766129</v>
+        <v>0.138200615776613</v>
       </c>
       <c r="H10" s="16" t="n">
         <v>370.0262375089882</v>
@@ -1682,7 +1682,7 @@
         <v>0.0060687804495014</v>
       </c>
       <c r="G12" s="20" t="n">
-        <v>0.07305447787943251</v>
+        <v>0.0730544778794326</v>
       </c>
       <c r="H12" s="19" t="n">
         <v>365.9026706205821</v>
@@ -1691,7 +1691,7 @@
         <v>378.7848958392373</v>
       </c>
       <c r="J12" s="19" t="n">
-        <v>404.0050109216063</v>
+        <v>404.0050109216064</v>
       </c>
       <c r="K12" s="19" t="n">
         <v>357.675</v>
@@ -1736,7 +1736,7 @@
         <v>-0.0789866180022725</v>
       </c>
       <c r="F13" s="23" t="n">
-        <v>-0.0105208185445254</v>
+        <v>-0.0105208185445256</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>0.0584958172872285</v>
@@ -1745,7 +1745,7 @@
         <v>17.32426122350304</v>
       </c>
       <c r="I13" s="22" t="n">
-        <v>18.61210287473859</v>
+        <v>18.61210287473858</v>
       </c>
       <c r="J13" s="22" t="n">
         <v>19.91030575787502</v>
@@ -1961,22 +1961,22 @@
         <v>69.05000305175781</v>
       </c>
       <c r="E17" s="17" t="n">
-        <v>0.0306243693277838</v>
+        <v>0.0306243693277841</v>
       </c>
       <c r="F17" s="17" t="n">
         <v>0.1086638342048738</v>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.1743487455946222</v>
+        <v>0.1743487455946224</v>
       </c>
       <c r="H17" s="16" t="n">
-        <v>71.16461584729944</v>
+        <v>71.16461584729946</v>
       </c>
       <c r="I17" s="16" t="n">
         <v>76.55324113522005</v>
       </c>
       <c r="J17" s="16" t="n">
-        <v>81.08878446713662</v>
+        <v>81.08878446713663</v>
       </c>
       <c r="K17" s="16" t="n">
         <v>65.05111663722695</v>
@@ -2048,7 +2048,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-15 02:43</t>
+          <t>Son Güncelleme: 2026-08-16 02:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2182,13 +2182,13 @@
         </is>
       </c>
       <c r="E5" s="20" t="n">
-        <v>0.0591312790793305</v>
+        <v>0.0591312790793308</v>
       </c>
       <c r="F5" s="20" t="n">
-        <v>-0.0102689785012989</v>
+        <v>-0.0102689785012987</v>
       </c>
       <c r="G5" s="20" t="n">
-        <v>0.0123804463255767</v>
+        <v>0.0123804463255772</v>
       </c>
       <c r="H5" s="20" t="n">
         <v>0.2481088749818165</v>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="J5" s="20" t="n">
-        <v>0.0217091481717317</v>
+        <v>0.0217091481717316</v>
       </c>
       <c r="K5" s="20" t="n">
         <v>0.0371204201966619</v>
@@ -2374,7 +2374,7 @@
         <v>0.0270933955942019</v>
       </c>
       <c r="K9" s="23" t="n">
-        <v>-0.0105208185445254</v>
+        <v>-0.0105208185445256</v>
       </c>
     </row>
     <row r="10">
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="J10" s="20" t="n">
-        <v>0.0217785131066505</v>
+        <v>0.0217785131066506</v>
       </c>
       <c r="K10" s="20" t="n">
         <v>0.0292262535427767</v>
@@ -2572,7 +2572,7 @@
         <v>-0.0187844966656595</v>
       </c>
       <c r="F14" s="25" t="n">
-        <v>-0.0672268287987855</v>
+        <v>-0.0672268287987856</v>
       </c>
       <c r="G14" s="25" t="n">
         <v>-0.1447712328733906</v>
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="E16" s="25" t="n">
-        <v>-0.0644283000974651</v>
+        <v>-0.0644283000974652</v>
       </c>
       <c r="F16" s="25" t="n">
         <v>-0.09956333210374591</v>
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="E17" s="25" t="n">
-        <v>-0.0449541090153023</v>
+        <v>-0.0449541090153021</v>
       </c>
       <c r="F17" s="25" t="n">
         <v>-0.1395106937258488</v>
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="J17" s="25" t="n">
-        <v>0.0218911391981522</v>
+        <v>0.0218911391981521</v>
       </c>
       <c r="K17" s="25" t="n">
         <v>0.0236686907772818</v>
@@ -2830,10 +2830,10 @@
         <v>-0.0429726990336588</v>
       </c>
       <c r="F20" s="25" t="n">
-        <v>-0.1748038008354153</v>
+        <v>-0.1748038008354154</v>
       </c>
       <c r="G20" s="25" t="n">
-        <v>-0.2409783172235023</v>
+        <v>-0.2409783172235025</v>
       </c>
       <c r="H20" s="25" t="n">
         <v>-0.1458254589228474</v>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="J20" s="25" t="n">
-        <v>0.0152227377417771</v>
+        <v>0.0152227377417772</v>
       </c>
       <c r="K20" s="25" t="n">
         <v>0.0649744697948437</v>
@@ -2880,7 +2880,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-15 02:43</t>
+          <t>Son Güncelleme: 2026-08-16 02:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2999,7 +2999,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-15 02:43</t>
+          <t>Son Güncelleme: 2026-08-16 02:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3250,7 +3250,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-15 02:43</t>
+          <t>Son Güncelleme: 2026-08-16 02:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3375,7 +3375,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-15 02:43</t>
+          <t>Son Güncelleme: 2026-08-16 02:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3506,7 +3506,7 @@
         <v>202.3999938964844</v>
       </c>
       <c r="E6" s="27" t="n">
-        <v>0.02741113653037752</v>
+        <v>0.02741113653037774</v>
       </c>
       <c r="F6" s="26" t="n">
         <v>79666.21246549161</v>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -637,7 +637,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-16 02:50</t>
+          <t>Son Güncelleme: 2026-08-17 02:50</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1251,7 +1251,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-16 02:50</t>
+          <t>Son Güncelleme: 2026-08-17 02:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2048,7 +2048,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-16 02:50</t>
+          <t>Son Güncelleme: 2026-08-17 02:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2880,7 +2880,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-16 02:50</t>
+          <t>Son Güncelleme: 2026-08-17 02:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2999,7 +2999,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-16 02:50</t>
+          <t>Son Güncelleme: 2026-08-17 02:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3250,7 +3250,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-16 02:50</t>
+          <t>Son Güncelleme: 2026-08-17 02:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3375,7 +3375,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-16 02:50</t>
+          <t>Son Güncelleme: 2026-08-17 02:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-22 02:45</t>
+          <t>Son Güncelleme: 2026-08-23 02:52</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -952,25 +952,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1343465767065309</v>
+        <v>0.134346576706531</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>13434.65767065309</v>
+        <v>13434.6576706531</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>0.0493707647628267</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>663.279323526919</v>
+        <v>663.2793235269194</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>414.7637947725073</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>374.126078049435</v>
+        <v>374.1260780494351</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.9237770721826276</v>
+        <v>0.9237770721826325</v>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
@@ -995,16 +995,16 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.0929986952954848</v>
+        <v>0.09299869529548477</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>9299.869529548479</v>
+        <v>9299.869529548478</v>
       </c>
       <c r="F21" s="7" t="n">
         <v>0.0716181384209222</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>666.0393432637196</v>
+        <v>666.0393432637195</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>290.4085155120699</v>
@@ -1036,22 +1036,22 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.09214758429668768</v>
+        <v>0.09214758429668765</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>9214.758429668767</v>
+        <v>9214.758429668766</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>0.0417778692166073</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>384.9729725373314</v>
+        <v>384.9729725373313</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>39.69173522752586</v>
+        <v>39.69173522752585</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>35.84806158069362</v>
+        <v>35.84806158069361</v>
       </c>
       <c r="J22" s="6" t="n">
         <v>0.7068300883787749</v>
@@ -1077,16 +1077,16 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.09106343946398338</v>
+        <v>0.09106343946398336</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>9106.343946398338</v>
+        <v>9106.343946398336</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>0.0377359140906252</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>343.6362128409725</v>
+        <v>343.6362128409724</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>93.5518942387292</v>
@@ -1118,16 +1118,16 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.08944370423731328</v>
+        <v>0.08944370423731327</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>8944.370423731329</v>
+        <v>8944.370423731327</v>
       </c>
       <c r="F24" s="7" t="n">
         <v>0.0536684495919916</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>480.0304932181254</v>
+        <v>480.0304932181253</v>
       </c>
       <c r="H24" s="8" t="n">
         <v>423.8381338483787</v>
@@ -1235,7 +1235,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-22 02:45</t>
+          <t>Son Güncelleme: 2026-08-23 02:52</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1450,7 +1450,7 @@
         <v>482.1635646835106</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>374.126078049435</v>
+        <v>374.1260780494351</v>
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
@@ -1489,10 +1489,10 @@
         <v>218</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>-0.07714115080299661</v>
+        <v>-0.0771411508029967</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>0.0299893661512347</v>
+        <v>0.0299893661512346</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>0.1156037188174166</v>
@@ -1555,16 +1555,16 @@
         <v>0.1107634622150022</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>35.84806158069362</v>
+        <v>35.84806158069361</v>
       </c>
       <c r="I10" s="14" t="n">
-        <v>39.69173522752586</v>
+        <v>39.69173522752585</v>
       </c>
       <c r="J10" s="14" t="n">
-        <v>42.32008621550105</v>
+        <v>42.32008621550104</v>
       </c>
       <c r="K10" s="14" t="n">
-        <v>35.84806158069362</v>
+        <v>35.84806158069361</v>
       </c>
       <c r="L10" s="13" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>0.0177083448864976</v>
       </c>
       <c r="G11" s="18" t="n">
-        <v>0.1124000923734837</v>
+        <v>0.1124000923734836</v>
       </c>
       <c r="H11" s="17" t="n">
         <v>33.11816269310333</v>
@@ -1723,7 +1723,7 @@
         <v>0.0536684495919916</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0.1760204477177214</v>
+        <v>0.1760204477177211</v>
       </c>
       <c r="H13" s="14" t="n">
         <v>390.9189903803491</v>
@@ -1732,7 +1732,7 @@
         <v>423.8381338483787</v>
       </c>
       <c r="J13" s="14" t="n">
-        <v>473.0542250944534</v>
+        <v>473.0542250944533</v>
       </c>
       <c r="K13" s="14" t="n">
         <v>375.5149467979344</v>
@@ -1774,7 +1774,7 @@
         <v>411</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>-0.0281470913039894</v>
+        <v>-0.0281470913039895</v>
       </c>
       <c r="F14" s="18" t="n">
         <v>0.0052710954697796</v>
@@ -2002,7 +2002,7 @@
         <v>40</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>-0.0706307531256109</v>
+        <v>-0.0706307531256108</v>
       </c>
       <c r="F18" s="21" t="n">
         <v>-0.0160170779776641</v>
@@ -2011,7 +2011,7 @@
         <v>0.0525686146659375</v>
       </c>
       <c r="H18" s="20" t="n">
-        <v>37.17476987497556</v>
+        <v>37.17476987497557</v>
       </c>
       <c r="I18" s="20" t="n">
         <v>39.35931688089344</v>
@@ -2020,7 +2020,7 @@
         <v>42.1027445866375</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>37.17476987497556</v>
+        <v>37.17476987497557</v>
       </c>
       <c r="L18" s="19" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-22 02:45</t>
+          <t>Son Güncelleme: 2026-08-23 02:52</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2240,10 +2240,10 @@
         <v>0.2597609561752987</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>0.6258740850532789</v>
+        <v>0.6258740850532791</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>0.8525816386388203</v>
+        <v>0.8525816386388205</v>
       </c>
       <c r="H4" s="15" t="n">
         <v>0.2368085817325154</v>
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="J4" s="15" t="n">
-        <v>0.0267222289064705</v>
+        <v>0.0267222289064704</v>
       </c>
       <c r="K4" s="15" t="n">
         <v>0.0493707647628267</v>
@@ -2286,7 +2286,7 @@
         <v>0.1461619531956293</v>
       </c>
       <c r="G5" s="18" t="n">
-        <v>0.0369141594032791</v>
+        <v>0.0369141594032793</v>
       </c>
       <c r="H5" s="18" t="n">
         <v>0.2910267401040018</v>
@@ -2300,7 +2300,7 @@
         <v>0.0197309397935816</v>
       </c>
       <c r="K5" s="18" t="n">
-        <v>0.0299893661512347</v>
+        <v>0.0299893661512346</v>
       </c>
     </row>
     <row r="6">
@@ -2323,13 +2323,13 @@
         </is>
       </c>
       <c r="E6" s="15" t="n">
-        <v>-0.098011435602196</v>
+        <v>-0.0980114356021962</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>-0.0016017059272716</v>
+        <v>-0.0016017059272717</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0.3029030422072716</v>
+        <v>0.3029030422072714</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>0.1839209653969769</v>
@@ -2415,7 +2415,7 @@
         <v>0.0112170497238826</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>-0.1596484590301509</v>
+        <v>-0.1596484590301508</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>0.1576829052094781</v>
@@ -2498,10 +2498,10 @@
         <v>0.0281425891181987</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>0.05191756587349</v>
+        <v>0.0519175658734898</v>
       </c>
       <c r="G10" s="18" t="n">
-        <v>0.2080135694289591</v>
+        <v>0.2080135694289593</v>
       </c>
       <c r="H10" s="18" t="n">
         <v>0.0245572648966108</v>
@@ -2667,13 +2667,13 @@
         </is>
       </c>
       <c r="E14" s="23" t="n">
-        <v>-0.0738738463805602</v>
+        <v>-0.0738738463805603</v>
       </c>
       <c r="F14" s="23" t="n">
-        <v>-0.0347417553825557</v>
+        <v>-0.0347417553825558</v>
       </c>
       <c r="G14" s="23" t="n">
-        <v>-0.1749598369930241</v>
+        <v>-0.1749598369930242</v>
       </c>
       <c r="H14" s="23" t="n">
         <v>0.2048580599541376</v>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="E15" s="23" t="n">
-        <v>-0.0720071342738285</v>
+        <v>-0.07200713427382829</v>
       </c>
       <c r="F15" s="23" t="n">
-        <v>-0.1119723751510086</v>
+        <v>-0.1119723751510085</v>
       </c>
       <c r="G15" s="23" t="n">
         <v>0.114594639958562</v>
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="J16" s="23" t="n">
-        <v>0.018762325619922</v>
+        <v>0.0187623256199221</v>
       </c>
       <c r="K16" s="23" t="n">
         <v>0.0004400050591799</v>
@@ -2799,7 +2799,7 @@
         <v>-0.0829894319240496</v>
       </c>
       <c r="F17" s="21" t="n">
-        <v>-0.1043352838645631</v>
+        <v>-0.1043352838645629</v>
       </c>
       <c r="G17" s="21" t="n">
         <v>-0.1255961526017237</v>
@@ -2813,7 +2813,7 @@
         </is>
       </c>
       <c r="J17" s="21" t="n">
-        <v>0.0201384375410243</v>
+        <v>0.0201384375410242</v>
       </c>
       <c r="K17" s="21" t="n">
         <v>-0.0160170779776641</v>
@@ -2882,13 +2882,13 @@
         </is>
       </c>
       <c r="E19" s="23" t="n">
-        <v>-0.0618975739687389</v>
+        <v>-0.0618975739687386</v>
       </c>
       <c r="F19" s="23" t="n">
-        <v>-0.1119116397371999</v>
+        <v>-0.1119116397371998</v>
       </c>
       <c r="G19" s="23" t="n">
-        <v>-0.2771696962838884</v>
+        <v>-0.2771696962838883</v>
       </c>
       <c r="H19" s="23" t="n">
         <v>-0.0299086319404379</v>
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="J19" s="23" t="n">
-        <v>0.0129972957161291</v>
+        <v>0.0129972957161292</v>
       </c>
       <c r="K19" s="23" t="n">
         <v>0.0649744278262515</v>
@@ -2978,7 +2978,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-22 02:45</t>
+          <t>Son Güncelleme: 2026-08-23 02:52</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3097,7 +3097,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-22 02:45</t>
+          <t>Son Güncelleme: 2026-08-23 02:52</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3348,7 +3348,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-22 02:45</t>
+          <t>Son Güncelleme: 2026-08-23 02:52</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3452,7 +3452,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -3473,7 +3473,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-22 02:45</t>
+          <t>Son Güncelleme: 2026-08-23 02:52</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3550,7 +3550,7 @@
         <v>4849.359929593862</v>
       </c>
       <c r="G4" s="24" t="n">
-        <v>11450673.0954523</v>
+        <v>11477046.72182592</v>
       </c>
       <c r="H4" s="25" t="n">
         <v>0.0505326911850554</v>
@@ -3580,7 +3580,7 @@
         <v>309813.3986530076</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>11450673.0954523</v>
+        <v>11477046.72182592</v>
       </c>
       <c r="H5" s="25" t="n">
         <v>0.0505326911850554</v>
@@ -3610,7 +3610,7 @@
         <v>1016118.949636504</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>11450673.0954523</v>
+        <v>11477046.72182592</v>
       </c>
       <c r="H6" s="25" t="n">
         <v>0.0505326911850554</v>
@@ -3640,7 +3640,7 @@
         <v>678.5705199163494</v>
       </c>
       <c r="G7" s="24" t="n">
-        <v>11450673.0954523</v>
+        <v>11477046.72182592</v>
       </c>
       <c r="H7" s="25" t="n">
         <v>0.0505326911850554</v>
@@ -3664,13 +3664,13 @@
         <v>38.09999847412109</v>
       </c>
       <c r="E8" s="25" t="n">
-        <v>-0.01499487658941612</v>
+        <v>-0.01499487658941623</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>-866.9169392276599</v>
+        <v>-866.9169392276672</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>11450673.0954523</v>
+        <v>11477046.72182592</v>
       </c>
       <c r="H8" s="25" t="n">
         <v>0.0505326911850554</v>
@@ -3700,7 +3700,7 @@
         <v>845.7754880934372</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>11450673.0954523</v>
+        <v>11477046.72182592</v>
       </c>
       <c r="H9" s="25" t="n">
         <v>0.0505326911850554</v>
@@ -3730,7 +3730,7 @@
         <v>6360.157754268032</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>11450673.0954523</v>
+        <v>11477046.72182592</v>
       </c>
       <c r="H10" s="25" t="n">
         <v>0.0505326911850554</v>
@@ -3760,7 +3760,7 @@
         <v>110.3276276744764</v>
       </c>
       <c r="G11" s="24" t="n">
-        <v>11450673.0954523</v>
+        <v>11477046.72182592</v>
       </c>
       <c r="H11" s="25" t="n">
         <v>0.0505326911850554</v>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-23 02:52</t>
+          <t>Son Güncelleme: 2026-08-24 02:53</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1235,7 +1235,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-23 02:52</t>
+          <t>Son Güncelleme: 2026-08-24 02:53</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2146,7 +2146,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-23 02:52</t>
+          <t>Son Güncelleme: 2026-08-24 02:53</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2978,7 +2978,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-23 02:52</t>
+          <t>Son Güncelleme: 2026-08-24 02:53</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3097,7 +3097,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-23 02:52</t>
+          <t>Son Güncelleme: 2026-08-24 02:53</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3348,7 +3348,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-23 02:52</t>
+          <t>Son Güncelleme: 2026-08-24 02:53</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3473,7 +3473,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-23 02:52</t>
+          <t>Son Güncelleme: 2026-08-24 02:53</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3550,7 +3550,7 @@
         <v>4849.359929593862</v>
       </c>
       <c r="G4" s="24" t="n">
-        <v>11477046.72182592</v>
+        <v>11503420.34819955</v>
       </c>
       <c r="H4" s="25" t="n">
         <v>0.0505326911850554</v>
@@ -3580,7 +3580,7 @@
         <v>309813.3986530076</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>11477046.72182592</v>
+        <v>11503420.34819955</v>
       </c>
       <c r="H5" s="25" t="n">
         <v>0.0505326911850554</v>
@@ -3610,7 +3610,7 @@
         <v>1016118.949636504</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>11477046.72182592</v>
+        <v>11503420.34819955</v>
       </c>
       <c r="H6" s="25" t="n">
         <v>0.0505326911850554</v>
@@ -3640,7 +3640,7 @@
         <v>678.5705199163494</v>
       </c>
       <c r="G7" s="24" t="n">
-        <v>11477046.72182592</v>
+        <v>11503420.34819955</v>
       </c>
       <c r="H7" s="25" t="n">
         <v>0.0505326911850554</v>
@@ -3670,7 +3670,7 @@
         <v>-866.9169392276672</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>11477046.72182592</v>
+        <v>11503420.34819955</v>
       </c>
       <c r="H8" s="25" t="n">
         <v>0.0505326911850554</v>
@@ -3700,7 +3700,7 @@
         <v>845.7754880934372</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>11477046.72182592</v>
+        <v>11503420.34819955</v>
       </c>
       <c r="H9" s="25" t="n">
         <v>0.0505326911850554</v>
@@ -3730,7 +3730,7 @@
         <v>6360.157754268032</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>11477046.72182592</v>
+        <v>11503420.34819955</v>
       </c>
       <c r="H10" s="25" t="n">
         <v>0.0505326911850554</v>
@@ -3760,7 +3760,7 @@
         <v>110.3276276744764</v>
       </c>
       <c r="G11" s="24" t="n">
-        <v>11477046.72182592</v>
+        <v>11503420.34819955</v>
       </c>
       <c r="H11" s="25" t="n">
         <v>0.0505326911850554</v>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-28 13:27</t>
+          <t>Son Güncelleme: 2026-08-29 08:21</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -969,25 +969,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1301946401295221</v>
+        <v>0.1301946563809981</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>13019.46401295221</v>
+        <v>13019.46563809981</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.1079079459374078</v>
+        <v>0.1079080026692217</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1404.903618843673</v>
+        <v>1404.904532827915</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>237.313878638726</v>
+        <v>237.3138907906804</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>203.4899971008301</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>2.158158918748152</v>
+        <v>2.158160053384431</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1012,16 +1012,16 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1159312918589553</v>
+        <v>0.1159312909309919</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>11593.12918589553</v>
+        <v>11593.12909309919</v>
       </c>
       <c r="F21" s="7" t="n">
         <v>0.0493707647628267</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>572.361653901909</v>
+        <v>572.3616493204826</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>399.5479186834463</v>
@@ -1053,25 +1053,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.08903847142738525</v>
+        <v>0.08903846940928832</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>8903.847142738525</v>
+        <v>8903.846940928832</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0768721535112086</v>
+        <v>0.07687214851712661</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>684.457904396932</v>
+        <v>684.4578444168445</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>434.7871319801505</v>
+        <v>434.7871299637899</v>
       </c>
       <c r="I22" s="8" t="n">
         <v>377.4784125939908</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>1.181395379749729</v>
+        <v>1.181395302999109</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.0854623464075606</v>
+        <v>0.08546234572348362</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>8546.23464075606</v>
+        <v>8546.234572348361</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>0.0331174361060366</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>283.0293796624355</v>
+        <v>283.0293773969479</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>137.4046190021029</v>
@@ -1135,25 +1135,25 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.07937325017657668</v>
+        <v>0.07937323755523804</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>7937.325017657668</v>
+        <v>7937.323755523804</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0345253730965184</v>
+        <v>0.0345253100982498</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>274.0391076229605</v>
+        <v>274.038564009664</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>39.93267782296517</v>
+        <v>39.9326753912321</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>36.34287963504224</v>
+        <v>36.34288187878566</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.5904338423704588</v>
+        <v>0.5904333519434122</v>
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>0.5000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>50000.00000000001</v>
+        <v>50000</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-28 13:27</t>
+          <t>Son Güncelleme: 2026-08-29 08:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1449,22 +1449,22 @@
         <v>380.75</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>0.0028744012948362</v>
+        <v>0.0028744014962105</v>
       </c>
       <c r="F8" s="16" t="n">
         <v>0.0493707647628267</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.2198951866897833</v>
+        <v>0.2198952770741356</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>381.8444282930089</v>
+        <v>381.8444283696822</v>
       </c>
       <c r="I8" s="15" t="n">
         <v>399.5479186834463</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>464.475092332135</v>
+        <v>464.4751267459771</v>
       </c>
       <c r="K8" s="15" t="n">
         <v>359.396749902489</v>
@@ -1506,19 +1506,19 @@
         <v>214.1999969482422</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>0.0371203067330339</v>
+        <v>0.0371204201966619</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>0.1079079459374078</v>
+        <v>0.1079080026692217</v>
       </c>
       <c r="G9" s="16" t="n">
         <v>0.1786955851417817</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>222.1511665371759</v>
+        <v>222.1511908410847</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>237.313878638726</v>
+        <v>237.3138907906804</v>
       </c>
       <c r="J9" s="15" t="n">
         <v>252.4765907402762</v>
@@ -1569,7 +1569,7 @@
         <v>0.0331174361060366</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>0.1446542046234986</v>
+        <v>0.1446539767324788</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>131.8975631497201</v>
@@ -1578,7 +1578,7 @@
         <v>137.4046190021029</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>152.2390092149253</v>
+        <v>152.2389789054197</v>
       </c>
       <c r="K10" s="15" t="n">
         <v>126.35</v>
@@ -1620,25 +1620,25 @@
         <v>72.84999847412109</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>-0.1195457879117688</v>
+        <v>-0.1195456773982677</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>-0.0366895635349088</v>
+        <v>-0.0366894684105838</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>0.05159344410234</v>
+        <v>0.0515933324042807</v>
       </c>
       <c r="H11" s="18" t="n">
-        <v>64.14108800716113</v>
+        <v>64.14109605806952</v>
       </c>
       <c r="I11" s="18" t="n">
-        <v>70.17716382658682</v>
+        <v>70.17717075639375</v>
       </c>
       <c r="J11" s="18" t="n">
-        <v>76.60858079825121</v>
+        <v>76.60857266104777</v>
       </c>
       <c r="K11" s="18" t="n">
-        <v>64.14108800716113</v>
+        <v>64.14109605806952</v>
       </c>
       <c r="L11" s="17" t="inlineStr">
         <is>
@@ -1677,25 +1677,25 @@
         <v>93.75</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>-0.07730044685463951</v>
+        <v>-0.0773005255414696</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>0.0255523087465968</v>
+        <v>0.0255522639279874</v>
       </c>
       <c r="G12" s="22" t="n">
-        <v>0.0887438433689242</v>
+        <v>0.08874378886366099</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>86.50308310737755</v>
+        <v>86.50307573048723</v>
       </c>
       <c r="I12" s="21" t="n">
-        <v>96.14552894499344</v>
+        <v>96.14552474324883</v>
       </c>
       <c r="J12" s="21" t="n">
-        <v>102.0697353158367</v>
+        <v>102.0697302059682</v>
       </c>
       <c r="K12" s="21" t="n">
-        <v>86.50308310737755</v>
+        <v>86.50307573048723</v>
       </c>
       <c r="L12" s="20" t="inlineStr">
         <is>
@@ -1737,19 +1737,19 @@
         <v>-0.0079710144927536</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>0.0768721535112086</v>
+        <v>0.07687214851712661</v>
       </c>
       <c r="G13" s="16" t="n">
-        <v>0.1767024655720609</v>
+        <v>0.1767023253641666</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>400.5317028985507</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>434.7871319801505</v>
+        <v>434.7871299637899</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>475.0936204747196</v>
+        <v>475.0935638657823</v>
       </c>
       <c r="K13" s="15" t="n">
         <v>377.4784125939908</v>
@@ -1791,25 +1791,25 @@
         <v>38.59999847412109</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>-0.0584745836348182</v>
+        <v>-0.0584745255067481</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>0.0345253730965184</v>
+        <v>0.0345253100982498</v>
       </c>
       <c r="G14" s="16" t="n">
         <v>0.1107634622150022</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>36.34287963504224</v>
+        <v>36.34288187878566</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>39.93267782296517</v>
+        <v>39.9326753912321</v>
       </c>
       <c r="J14" s="15" t="n">
         <v>42.87546794660855</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>36.34287963504224</v>
+        <v>36.34288187878566</v>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
@@ -1848,22 +1848,22 @@
         <v>413.75</v>
       </c>
       <c r="E15" s="22" t="n">
-        <v>-0.0243525901521948</v>
+        <v>-0.0243524546491471</v>
       </c>
       <c r="F15" s="22" t="n">
         <v>0.0060687804495014</v>
       </c>
       <c r="G15" s="22" t="n">
-        <v>0.06314855114378599</v>
+        <v>0.0631485677683334</v>
       </c>
       <c r="H15" s="21" t="n">
-        <v>403.6741158245294</v>
+        <v>403.6741718889153</v>
       </c>
       <c r="I15" s="21" t="n">
         <v>416.2609579109812</v>
       </c>
       <c r="J15" s="21" t="n">
-        <v>439.8777130357414</v>
+        <v>439.877719914148</v>
       </c>
       <c r="K15" s="21" t="n">
         <v>393.0625</v>
@@ -1908,7 +1908,7 @@
         <v>-0.104751646118041</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>-0.0315931209320554</v>
+        <v>-0.0315930645677514</v>
       </c>
       <c r="G16" s="19" t="n">
         <v>0.1136891323573432</v>
@@ -1917,7 +1917,7 @@
         <v>32.99885487050524</v>
       </c>
       <c r="I16" s="18" t="n">
-        <v>35.69547815351309</v>
+        <v>35.69548023110137</v>
       </c>
       <c r="J16" s="18" t="n">
         <v>41.05058209843357</v>
@@ -1965,19 +1965,19 @@
         <v>-0.0476951848926354</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>0.0046669165044877</v>
+        <v>0.0046668155230729</v>
       </c>
       <c r="G17" s="22" t="n">
-        <v>0.0596783413325591</v>
+        <v>0.0596784074389585</v>
       </c>
       <c r="H17" s="21" t="n">
         <v>97.89693789924074</v>
       </c>
       <c r="I17" s="21" t="n">
-        <v>103.2797620826614</v>
+        <v>103.2797517017717</v>
       </c>
       <c r="J17" s="21" t="n">
-        <v>108.9349367228687</v>
+        <v>108.9349435186068</v>
       </c>
       <c r="K17" s="21" t="n">
         <v>97.66000289916991</v>
@@ -2019,25 +2019,25 @@
         <v>273.5</v>
       </c>
       <c r="E18" s="25" t="n">
-        <v>-0.1062914431538463</v>
+        <v>-0.1062913807230041</v>
       </c>
       <c r="F18" s="25" t="n">
         <v>-0.0245398668646306</v>
       </c>
       <c r="G18" s="25" t="n">
-        <v>0.0358585890694043</v>
+        <v>0.0358586773669118</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>244.429290297423</v>
+        <v>244.4293073722584</v>
       </c>
       <c r="I18" s="24" t="n">
         <v>266.7883464125235</v>
       </c>
       <c r="J18" s="24" t="n">
-        <v>283.3073241104821</v>
+        <v>283.3073482598504</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>244.429290297423</v>
+        <v>244.4293073722584</v>
       </c>
       <c r="L18" s="23" t="inlineStr">
         <is>
@@ -2076,22 +2076,22 @@
         <v>151.5</v>
       </c>
       <c r="E19" s="25" t="n">
-        <v>-0.0355162004498606</v>
+        <v>-0.035516201414184</v>
       </c>
       <c r="F19" s="25" t="n">
-        <v>-0.0011988764109042</v>
+        <v>-0.0011987972727639</v>
       </c>
       <c r="G19" s="25" t="n">
-        <v>0.0637569974381122</v>
+        <v>0.0637570370071823</v>
       </c>
       <c r="H19" s="24" t="n">
-        <v>146.1192956318461</v>
+        <v>146.1192954857511</v>
       </c>
       <c r="I19" s="24" t="n">
-        <v>151.318370223748</v>
+        <v>151.3183822131762</v>
       </c>
       <c r="J19" s="24" t="n">
-        <v>161.159185111874</v>
+        <v>161.1591911065881</v>
       </c>
       <c r="K19" s="24" t="n">
         <v>143.925</v>
@@ -2163,7 +2163,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-28 13:27</t>
+          <t>Son Güncelleme: 2026-08-29 08:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="J5" s="16" t="n">
-        <v>0.0200890131090384</v>
+        <v>0.0200890131090385</v>
       </c>
       <c r="K5" s="16" t="n">
-        <v>0.1079079459374078</v>
+        <v>0.1079080026692217</v>
       </c>
     </row>
     <row r="6">
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="J6" s="16" t="n">
-        <v>0.0189344060033612</v>
+        <v>0.018934406003361</v>
       </c>
       <c r="K6" s="16" t="n">
         <v>0.0331174361060366</v>
@@ -2400,10 +2400,10 @@
         </is>
       </c>
       <c r="J7" s="19" t="n">
-        <v>0.0252030048204396</v>
+        <v>0.0252030048204395</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>-0.0366895635349088</v>
+        <v>-0.0366894684105838</v>
       </c>
     </row>
     <row r="8">
@@ -2446,7 +2446,7 @@
         <v>0.0188918567133183</v>
       </c>
       <c r="K8" s="22" t="n">
-        <v>0.0255523087465968</v>
+        <v>0.0255522639279874</v>
       </c>
     </row>
     <row r="9">
@@ -2489,7 +2489,7 @@
         <v>0.0325344735678133</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>0.0768721535112086</v>
+        <v>0.07687214851712661</v>
       </c>
     </row>
     <row r="10">
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="J10" s="16" t="n">
-        <v>0.0224073510671082</v>
+        <v>0.0224073510671083</v>
       </c>
       <c r="K10" s="16" t="n">
-        <v>0.0345253730965184</v>
+        <v>0.0345253100982498</v>
       </c>
     </row>
     <row r="11">
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="J11" s="22" t="n">
-        <v>0.0191946226833422</v>
+        <v>0.0191946226833423</v>
       </c>
       <c r="K11" s="22" t="n">
         <v>0.0060687804495014</v>
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="J12" s="19" t="n">
-        <v>0.0268491707380297</v>
+        <v>0.0268491707380296</v>
       </c>
       <c r="K12" s="19" t="n">
-        <v>-0.0315931209320554</v>
+        <v>-0.0315930645677514</v>
       </c>
     </row>
     <row r="13">
@@ -2661,7 +2661,7 @@
         <v>0.0200829643840794</v>
       </c>
       <c r="K13" s="22" t="n">
-        <v>0.0046669165044877</v>
+        <v>0.0046668155230729</v>
       </c>
     </row>
     <row r="14">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="J16" s="25" t="n">
-        <v>0.0221671481200846</v>
+        <v>0.0221671481200847</v>
       </c>
       <c r="K16" s="25" t="n">
         <v>-0.0245398668646306</v>
@@ -2833,7 +2833,7 @@
         <v>0.0196257181094786</v>
       </c>
       <c r="K17" s="27" t="n">
-        <v>0.0258272542822017</v>
+        <v>0.0258271723736069</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="J18" s="27" t="n">
-        <v>0.0165613004791113</v>
+        <v>0.0165613004791115</v>
       </c>
       <c r="K18" s="27" t="n">
-        <v>0.0283621099664455</v>
+        <v>0.0283622708857007</v>
       </c>
     </row>
     <row r="19">
@@ -2919,7 +2919,7 @@
         <v>0.0174669176767137</v>
       </c>
       <c r="K19" s="25" t="n">
-        <v>-0.0011988764109042</v>
+        <v>-0.0011987972727639</v>
       </c>
     </row>
     <row r="20">
@@ -2962,7 +2962,7 @@
         <v>0.0130331319051929</v>
       </c>
       <c r="K20" s="27" t="n">
-        <v>0.0294396733991557</v>
+        <v>0.0294396328657622</v>
       </c>
     </row>
   </sheetData>
@@ -2995,7 +2995,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-28 13:27</t>
+          <t>Son Güncelleme: 2026-08-29 08:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3114,7 +3114,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-28 13:27</t>
+          <t>Son Güncelleme: 2026-08-29 08:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3365,7 +3365,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-28 13:27</t>
+          <t>Son Güncelleme: 2026-08-29 08:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3490,7 +3490,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-28 13:27</t>
+          <t>Son Güncelleme: 2026-08-29 08:21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3567,7 +3567,7 @@
         <v>7494.465345736011</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>11292893.23744916</v>
+        <v>11323067.84361813</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0.0635945709281962</v>
@@ -3597,7 +3597,7 @@
         <v>253751.8814931558</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>11292893.23744916</v>
+        <v>11323067.84361813</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0.0635945709281962</v>
@@ -3627,7 +3627,7 @@
         <v>855094.6352132326</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>11292893.23744916</v>
+        <v>11323067.84361813</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0.0635945709281962</v>
@@ -3657,7 +3657,7 @@
         <v>2352.37642182142</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>11292893.23744916</v>
+        <v>11323067.84361813</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0.0635945709281962</v>
@@ -3687,7 +3687,7 @@
         <v>-119.5771095832897</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>11292893.23744916</v>
+        <v>11323067.84361813</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0.0635945709281962</v>
@@ -3717,7 +3717,7 @@
         <v>-20731.00951479189</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>11292893.23744916</v>
+        <v>11323067.84361813</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0.0635945709281962</v>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-29 08:21</t>
+          <t>Son Güncelleme: 2026-08-30 07:35</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1301946563809981</v>
+        <v>0.1301946563809982</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>13019.46563809981</v>
+        <v>13019.46563809982</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>0.1079080026692217</v>
@@ -1135,22 +1135,22 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.07937323755523804</v>
+        <v>0.07937323755523805</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>7937.323755523804</v>
+        <v>7937.323755523805</v>
       </c>
       <c r="F24" s="7" t="n">
         <v>0.0345253100982498</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>274.038564009664</v>
+        <v>274.0385640096641</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>39.9326753912321</v>
+        <v>39.93267539123209</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>36.34288187878566</v>
+        <v>36.34288187878565</v>
       </c>
       <c r="J24" s="6" t="n">
         <v>0.5904333519434122</v>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-29 08:21</t>
+          <t>Son Güncelleme: 2026-08-30 07:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1620,7 +1620,7 @@
         <v>72.84999847412109</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>-0.1195456773982677</v>
+        <v>-0.1195456773982676</v>
       </c>
       <c r="F11" s="19" t="n">
         <v>-0.0366894684105838</v>
@@ -1677,25 +1677,25 @@
         <v>93.75</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>-0.0773005255414696</v>
+        <v>-0.07730052554146941</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>0.0255522639279874</v>
+        <v>0.0255522639279876</v>
       </c>
       <c r="G12" s="22" t="n">
         <v>0.08874378886366099</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>86.50307573048723</v>
+        <v>86.50307573048724</v>
       </c>
       <c r="I12" s="21" t="n">
-        <v>96.14552474324883</v>
+        <v>96.14552474324884</v>
       </c>
       <c r="J12" s="21" t="n">
         <v>102.0697302059682</v>
       </c>
       <c r="K12" s="21" t="n">
-        <v>86.50307573048723</v>
+        <v>86.50307573048724</v>
       </c>
       <c r="L12" s="20" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>0.07687214851712661</v>
       </c>
       <c r="G13" s="16" t="n">
-        <v>0.1767023253641666</v>
+        <v>0.1767023253641665</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>400.5317028985507</v>
@@ -1749,7 +1749,7 @@
         <v>434.7871299637899</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>475.0935638657823</v>
+        <v>475.0935638657822</v>
       </c>
       <c r="K13" s="15" t="n">
         <v>377.4784125939908</v>
@@ -1800,16 +1800,16 @@
         <v>0.1107634622150022</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>36.34288187878566</v>
+        <v>36.34288187878565</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>39.9326753912321</v>
+        <v>39.93267539123209</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>42.87546794660855</v>
+        <v>42.87546794660854</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>36.34288187878566</v>
+        <v>36.34288187878565</v>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>0.0060687804495014</v>
       </c>
       <c r="G15" s="22" t="n">
-        <v>0.0631485677683334</v>
+        <v>0.0631485677683335</v>
       </c>
       <c r="H15" s="21" t="n">
         <v>403.6741718889153</v>
@@ -1908,7 +1908,7 @@
         <v>-0.104751646118041</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>-0.0315930645677514</v>
+        <v>-0.0315930645677513</v>
       </c>
       <c r="G16" s="19" t="n">
         <v>0.1136891323573432</v>
@@ -1965,13 +1965,13 @@
         <v>-0.0476951848926354</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>0.0046668155230729</v>
+        <v>0.0046668155230728</v>
       </c>
       <c r="G17" s="22" t="n">
         <v>0.0596784074389585</v>
       </c>
       <c r="H17" s="21" t="n">
-        <v>97.89693789924074</v>
+        <v>97.89693789924073</v>
       </c>
       <c r="I17" s="21" t="n">
         <v>103.2797517017717</v>
@@ -2019,7 +2019,7 @@
         <v>273.5</v>
       </c>
       <c r="E18" s="25" t="n">
-        <v>-0.1062913807230041</v>
+        <v>-0.1062913807230039</v>
       </c>
       <c r="F18" s="25" t="n">
         <v>-0.0245398668646306</v>
@@ -2163,7 +2163,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-29 08:21</t>
+          <t>Son Güncelleme: 2026-08-30 07:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="E5" s="16" t="n">
-        <v>0.1064049080334841</v>
+        <v>0.1064049080334843</v>
       </c>
       <c r="F5" s="16" t="n">
         <v>0.1327339504737326</v>
@@ -2314,7 +2314,7 @@
         </is>
       </c>
       <c r="J5" s="16" t="n">
-        <v>0.0200890131090385</v>
+        <v>0.0200890131090384</v>
       </c>
       <c r="K5" s="16" t="n">
         <v>0.1079080026692217</v>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="J6" s="16" t="n">
-        <v>0.018934406003361</v>
+        <v>0.0189344060033611</v>
       </c>
       <c r="K6" s="16" t="n">
         <v>0.0331174361060366</v>
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="J7" s="19" t="n">
-        <v>0.0252030048204395</v>
+        <v>0.0252030048204396</v>
       </c>
       <c r="K7" s="19" t="n">
         <v>-0.0366894684105838</v>
@@ -2446,7 +2446,7 @@
         <v>0.0188918567133183</v>
       </c>
       <c r="K8" s="22" t="n">
-        <v>0.0255522639279874</v>
+        <v>0.0255522639279876</v>
       </c>
     </row>
     <row r="9">
@@ -2512,13 +2512,13 @@
         </is>
       </c>
       <c r="E10" s="16" t="n">
-        <v>-0.1056534149539492</v>
+        <v>-0.1056534149539493</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>-0.0014077733762175</v>
+        <v>-0.0014077733762177</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>0.2468082657762476</v>
+        <v>0.2468082657762471</v>
       </c>
       <c r="H10" s="16" t="n">
         <v>0.1982309170737504</v>
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="J10" s="16" t="n">
-        <v>0.0224073510671083</v>
+        <v>0.0224073510671082</v>
       </c>
       <c r="K10" s="16" t="n">
         <v>0.0345253100982498</v>
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="J11" s="22" t="n">
-        <v>0.0191946226833423</v>
+        <v>0.0191946226833422</v>
       </c>
       <c r="K11" s="22" t="n">
         <v>0.0060687804495014</v>
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="J12" s="19" t="n">
-        <v>0.0268491707380296</v>
+        <v>0.0268491707380297</v>
       </c>
       <c r="K12" s="19" t="n">
-        <v>-0.0315930645677514</v>
+        <v>-0.0315930645677513</v>
       </c>
     </row>
     <row r="13">
@@ -2641,13 +2641,13 @@
         </is>
       </c>
       <c r="E13" s="22" t="n">
-        <v>0.0138067209547487</v>
+        <v>0.0138067209547485</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>0.0178218123936417</v>
+        <v>0.0178218123936415</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>-0.1504131979193569</v>
+        <v>-0.150413197919357</v>
       </c>
       <c r="H13" s="22" t="n">
         <v>0.1254756146184883</v>
@@ -2661,7 +2661,7 @@
         <v>0.0200829643840794</v>
       </c>
       <c r="K13" s="22" t="n">
-        <v>0.0046668155230729</v>
+        <v>0.0046668155230728</v>
       </c>
     </row>
     <row r="14">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="J15" s="27" t="n">
-        <v>0.0184939262170705</v>
+        <v>0.0184939262170706</v>
       </c>
       <c r="K15" s="27" t="n">
         <v>0.0048076735037425</v>
@@ -2833,7 +2833,7 @@
         <v>0.0196257181094786</v>
       </c>
       <c r="K17" s="27" t="n">
-        <v>0.0258271723736069</v>
+        <v>0.0258271723736072</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="J18" s="27" t="n">
-        <v>0.0165613004791115</v>
+        <v>0.0165613004791113</v>
       </c>
       <c r="K18" s="27" t="n">
-        <v>0.0283622708857007</v>
+        <v>0.0283622708857009</v>
       </c>
     </row>
     <row r="19">
@@ -2942,13 +2942,13 @@
         </is>
       </c>
       <c r="E20" s="27" t="n">
-        <v>-0.044738196178383</v>
+        <v>-0.0447381961783829</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>-0.09402121781031809</v>
+        <v>-0.094021217810318</v>
       </c>
       <c r="G20" s="27" t="n">
-        <v>-0.2091751301781463</v>
+        <v>-0.2091751301781461</v>
       </c>
       <c r="H20" s="27" t="n">
         <v>-0.1050783758981807</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="J20" s="27" t="n">
-        <v>0.0130331319051929</v>
+        <v>0.013033131905193</v>
       </c>
       <c r="K20" s="27" t="n">
         <v>0.0294396328657622</v>
@@ -2995,7 +2995,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-29 08:21</t>
+          <t>Son Güncelleme: 2026-08-30 07:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3114,7 +3114,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-29 08:21</t>
+          <t>Son Güncelleme: 2026-08-30 07:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3365,7 +3365,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-29 08:21</t>
+          <t>Son Güncelleme: 2026-08-30 07:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14575.5</v>
+        <v>14641.599609375</v>
       </c>
     </row>
     <row r="5">
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13240.16153320312</v>
+        <v>13258.74703125</v>
       </c>
     </row>
     <row r="6">
@@ -3469,7 +3469,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -3490,7 +3490,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-29 08:21</t>
+          <t>Son Güncelleme: 2026-08-30 07:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3567,7 +3567,7 @@
         <v>7494.465345736011</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>11323067.84361813</v>
+        <v>11353242.4497871</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0.0635945709281962</v>
@@ -3597,7 +3597,7 @@
         <v>253751.8814931558</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>11323067.84361813</v>
+        <v>11353242.4497871</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0.0635945709281962</v>
@@ -3627,7 +3627,7 @@
         <v>855094.6352132326</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>11323067.84361813</v>
+        <v>11353242.4497871</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0.0635945709281962</v>
@@ -3657,7 +3657,7 @@
         <v>2352.37642182142</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>11323067.84361813</v>
+        <v>11353242.4497871</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0.0635945709281962</v>
@@ -3681,13 +3681,13 @@
         <v>38.59999847412109</v>
       </c>
       <c r="E8" s="29" t="n">
-        <v>-0.002068299649004457</v>
+        <v>-0.002068299649004679</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>-119.5771095832897</v>
+        <v>-119.5771095833043</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>11323067.84361813</v>
+        <v>11353242.4497871</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0.0635945709281962</v>
@@ -3711,13 +3711,13 @@
         <v>102.8000030517578</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>-0.006763255538571822</v>
+        <v>-0.006763255538572044</v>
       </c>
       <c r="F9" s="28" t="n">
         <v>-20731.00951479189</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>11323067.84361813</v>
+        <v>11353242.4497871</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0.0635945709281962</v>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-30 07:35</t>
+          <t>Son Güncelleme: 2026-08-31 07:46</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-30 07:35</t>
+          <t>Son Güncelleme: 2026-08-31 07:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2163,7 +2163,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-30 07:35</t>
+          <t>Son Güncelleme: 2026-08-31 07:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2995,7 +2995,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-30 07:35</t>
+          <t>Son Güncelleme: 2026-08-31 07:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3114,7 +3114,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-30 07:35</t>
+          <t>Son Güncelleme: 2026-08-31 07:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3365,7 +3365,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-30 07:35</t>
+          <t>Son Güncelleme: 2026-08-31 07:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3469,7 +3469,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -3490,7 +3490,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-30 07:35</t>
+          <t>Son Güncelleme: 2026-08-31 07:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3567,7 +3567,7 @@
         <v>7494.465345736011</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>11353242.4497871</v>
+        <v>11383417.05595607</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0.0635945709281962</v>
@@ -3597,7 +3597,7 @@
         <v>253751.8814931558</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>11353242.4497871</v>
+        <v>11383417.05595607</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0.0635945709281962</v>
@@ -3627,7 +3627,7 @@
         <v>855094.6352132326</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>11353242.4497871</v>
+        <v>11383417.05595607</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0.0635945709281962</v>
@@ -3657,7 +3657,7 @@
         <v>2352.37642182142</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>11353242.4497871</v>
+        <v>11383417.05595607</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0.0635945709281962</v>
@@ -3687,7 +3687,7 @@
         <v>-119.5771095833043</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>11353242.4497871</v>
+        <v>11383417.05595607</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0.0635945709281962</v>
@@ -3717,7 +3717,7 @@
         <v>-20731.00951479189</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>11353242.4497871</v>
+        <v>11383417.05595607</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0.0635945709281962</v>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -629,7 +629,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-05 06:24</t>
+          <t>Son Güncelleme: 2026-09-06 06:34</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1085,16 +1085,16 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.09058627837803448</v>
+        <v>0.09058627837803444</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>9058.627837803448</v>
+        <v>9058.627837803444</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>0.0919577026412617</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>833.0106050465848</v>
+        <v>833.0106050465845</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>415.2169164293397</v>
@@ -1103,7 +1103,7 @@
         <v>357.1530283216292</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>1.513917794776732</v>
+        <v>1.513917794776729</v>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-05 06:24</t>
+          <t>Son Güncelleme: 2026-09-06 06:34</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1455,7 +1455,7 @@
         <v>236.4900906566582</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>255.0697174304946</v>
+        <v>255.0697174304947</v>
       </c>
       <c r="K8" s="15" t="n">
         <v>205.5799942016602</v>
@@ -1611,10 +1611,10 @@
         <v>93</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>-0.0794520528549532</v>
+        <v>-0.0794520528549533</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>-0.002145890072864</v>
+        <v>-0.0021458900728641</v>
       </c>
       <c r="G11" s="19" t="n">
         <v>0.0870869998031074</v>
@@ -1623,7 +1623,7 @@
         <v>85.61095908448935</v>
       </c>
       <c r="I11" s="18" t="n">
-        <v>92.80043222322365</v>
+        <v>92.80043222322364</v>
       </c>
       <c r="J11" s="18" t="n">
         <v>101.099090981689</v>
@@ -1668,7 +1668,7 @@
         <v>71.55000305175781</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>-0.1195456698956569</v>
+        <v>-0.1195456698956567</v>
       </c>
       <c r="F12" s="19" t="n">
         <v>-0.0366894684105838</v>
@@ -1677,7 +1677,7 @@
         <v>0.0515933324042807</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>62.99651000589913</v>
+        <v>62.99651000589914</v>
       </c>
       <c r="I12" s="18" t="n">
         <v>68.92487147501316</v>
@@ -1686,7 +1686,7 @@
         <v>75.24150614273445</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>62.99651000589913</v>
+        <v>62.99651000589914</v>
       </c>
       <c r="L12" s="17" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>-0.0609999645366716</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>-0.0447738760747383</v>
+        <v>-0.0447738760747384</v>
       </c>
       <c r="G13" s="19" t="n">
         <v>0.0704908343640927</v>
@@ -1788,7 +1788,7 @@
         <v>0.0919577026412617</v>
       </c>
       <c r="G14" s="16" t="n">
-        <v>0.1760202809935627</v>
+        <v>0.1760202809935624</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>377.9423233695652</v>
@@ -1797,7 +1797,7 @@
         <v>415.2169164293397</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>447.1817118478022</v>
+        <v>447.1817118478021</v>
       </c>
       <c r="K14" s="15" t="n">
         <v>357.1530283216292</v>
@@ -1839,7 +1839,7 @@
         <v>131.3999938964844</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>-0.0217475887738314</v>
+        <v>-0.0217475887738313</v>
       </c>
       <c r="F15" s="16" t="n">
         <v>0.0331174361060366</v>
@@ -1899,7 +1899,7 @@
         <v>-0.0508568307647213</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>-0.0154185299195158</v>
+        <v>-0.0154185299195159</v>
       </c>
       <c r="G16" s="19" t="n">
         <v>0.06315792247529731</v>
@@ -1908,13 +1908,13 @@
         <v>19.19167423021244</v>
       </c>
       <c r="I16" s="18" t="n">
-        <v>19.90823664896895</v>
+        <v>19.90823664896894</v>
       </c>
       <c r="J16" s="18" t="n">
         <v>21.4970524624379</v>
       </c>
       <c r="K16" s="18" t="n">
-        <v>19.11551570387917</v>
+        <v>19.11551570387916</v>
       </c>
       <c r="L16" s="17" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-05 06:24</t>
+          <t>Son Güncelleme: 2026-09-06 06:34</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2134,10 +2134,10 @@
         <v>0.0504854072644873</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>0.1449735126798115</v>
+        <v>0.1449735126798117</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>0.1809107991212859</v>
+        <v>0.1809107991212861</v>
       </c>
       <c r="H4" s="16" t="n">
         <v>0.3469524036816227</v>
@@ -2180,7 +2180,7 @@
         <v>0.6237541322454139</v>
       </c>
       <c r="G5" s="16" t="n">
-        <v>0.7620523625301359</v>
+        <v>0.7620523625301361</v>
       </c>
       <c r="H5" s="16" t="n">
         <v>0.200899625699457</v>
@@ -2280,7 +2280,7 @@
         <v>0.0167392005313508</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>-0.002145890072864</v>
+        <v>-0.0021458900728641</v>
       </c>
     </row>
     <row r="8">
@@ -2352,7 +2352,7 @@
         <v>-0.06588350424950069</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>0.2847325049290004</v>
+        <v>0.2847325049290006</v>
       </c>
       <c r="H9" s="19" t="n">
         <v>0.283111231226671</v>
@@ -2363,10 +2363,10 @@
         </is>
       </c>
       <c r="J9" s="19" t="n">
-        <v>0.022420600998482</v>
+        <v>0.0224206009984821</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>-0.0447738760747383</v>
+        <v>-0.0447738760747384</v>
       </c>
     </row>
     <row r="10">
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="J10" s="16" t="n">
-        <v>0.0303707714376999</v>
+        <v>0.0303707714377</v>
       </c>
       <c r="K10" s="16" t="n">
         <v>0.0919577026412617</v>
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="E12" s="19" t="n">
-        <v>-0.0009881649204468001</v>
+        <v>-0.000988164920447</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>-0.0297505198989361</v>
+        <v>-0.0297505198989362</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>0.0830208479232221</v>
+        <v>0.0830208479232219</v>
       </c>
       <c r="H12" s="19" t="n">
         <v>-0.0151103504099816</v>
@@ -2495,7 +2495,7 @@
         <v>0.0273116628828433</v>
       </c>
       <c r="K12" s="19" t="n">
-        <v>-0.0154185299195158</v>
+        <v>-0.0154185299195159</v>
       </c>
     </row>
     <row r="13">
@@ -2581,7 +2581,7 @@
         <v>0.020767963471301</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.0163071580494242</v>
+        <v>0.0163071580494245</v>
       </c>
     </row>
     <row r="15">
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="E15" s="24" t="n">
-        <v>-0.08859562778512679</v>
+        <v>-0.0885956277851266</v>
       </c>
       <c r="F15" s="24" t="n">
         <v>-0.1366071213416904</v>
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="J15" s="24" t="n">
-        <v>0.0188806590576912</v>
+        <v>0.0188806590576913</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>0.0258272542822017</v>
+        <v>0.0258272542822022</v>
       </c>
     </row>
     <row r="16">
@@ -2667,7 +2667,7 @@
         <v>0.0184925189907912</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.1028940851473592</v>
+        <v>0.1028940851473593</v>
       </c>
     </row>
     <row r="17">
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="J17" s="24" t="n">
-        <v>0.0221933836514507</v>
+        <v>0.0221933836514506</v>
       </c>
       <c r="K17" s="24" t="n">
         <v>0.0228670835813538</v>
@@ -2779,7 +2779,7 @@
         <v>-0.09429154071230859</v>
       </c>
       <c r="F19" s="24" t="n">
-        <v>-0.1398838736761376</v>
+        <v>-0.1398838736761375</v>
       </c>
       <c r="G19" s="24" t="n">
         <v>-0.2024237230061375</v>
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="J19" s="24" t="n">
-        <v>0.0122421878126867</v>
+        <v>0.0122421878126869</v>
       </c>
       <c r="K19" s="24" t="n">
         <v>0.029948947983406</v>
@@ -2872,7 +2872,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-05 06:24</t>
+          <t>Son Güncelleme: 2026-09-06 06:34</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2991,7 +2991,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-05 06:24</t>
+          <t>Son Güncelleme: 2026-09-06 06:34</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3242,7 +3242,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-05 06:24</t>
+          <t>Son Güncelleme: 2026-09-06 06:34</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3367,7 +3367,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-05 06:24</t>
+          <t>Son Güncelleme: 2026-09-06 06:34</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3468,7 +3468,7 @@
         <v>216.3999938964844</v>
       </c>
       <c r="E5" s="26" t="n">
-        <v>0.09847712637809325</v>
+        <v>0.09847712637809347</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>286208.4782341635</v>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -629,7 +629,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-06 06:34</t>
+          <t>Son Güncelleme: 2026-09-07 06:42</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1243,7 +1243,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-06 06:34</t>
+          <t>Son Güncelleme: 2026-09-07 06:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2040,7 +2040,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-06 06:34</t>
+          <t>Son Güncelleme: 2026-09-07 06:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2872,7 +2872,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-06 06:34</t>
+          <t>Son Güncelleme: 2026-09-07 06:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2991,7 +2991,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-06 06:34</t>
+          <t>Son Güncelleme: 2026-09-07 06:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3242,7 +3242,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-06 06:34</t>
+          <t>Son Güncelleme: 2026-09-07 06:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3367,7 +3367,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-06 06:34</t>
+          <t>Son Güncelleme: 2026-09-07 06:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-08 06:37</t>
+          <t>Son Güncelleme: 2026-09-09 06:49</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -689,7 +689,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 65.78/100</t>
+          <t>Güven Puanı: 69.28/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -969,25 +969,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1181200984536789</v>
+        <v>0.1181201156992633</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>11812.00984536789</v>
+        <v>11812.01156992633</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>0.0493707647628267</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>583.1679594518513</v>
+        <v>583.1680445946204</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>407.6805421103582</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>367.6046449578748</v>
+        <v>367.6046449578747</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.9179332953036716</v>
+        <v>0.9179332953036691</v>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
@@ -1012,25 +1012,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1162103976391515</v>
+        <v>0.1162104029062462</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>11621.03976391515</v>
+        <v>11621.04029062462</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0354565735575836</v>
+        <v>0.0354565230645036</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>412.0422512048614</v>
+        <v>412.0416830980574</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>222.7267152921616</v>
+        <v>222.7267044310998</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>195.6263790882017</v>
+        <v>195.626377797947</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.3916429734763007</v>
+        <v>0.3916423897956006</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1053,25 +1053,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1035522320007947</v>
+        <v>0.103552179816356</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>10355.22320007947</v>
+        <v>10355.2179816356</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0485935360435065</v>
+        <v>0.0485933210137139</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>503.1969118116162</v>
+        <v>503.1944315486014</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>435.9527626100879</v>
+        <v>435.9526732114516</v>
       </c>
       <c r="I22" s="8" t="n">
         <v>394.9625</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.9718707208701305</v>
+        <v>0.9718664202742769</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.09631036101676975</v>
+        <v>0.0963103810806922</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>9631.036101676975</v>
+        <v>9631.03810806922</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.09195747824944769</v>
+        <v>0.0919574997942756</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>885.645792839606</v>
+        <v>885.6461848414358</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>423.9524909303481</v>
+        <v>423.9524992951275</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>364.6187335307732</v>
+        <v>364.6187335307733</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>1.510815807389788</v>
+        <v>1.510816161360639</v>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.0658069108896053</v>
+        <v>0.06580692049744219</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>6580.691088960531</v>
+        <v>6580.692049744219</v>
       </c>
       <c r="F24" s="7" t="n">
         <v>0.0349441231528639</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>229.9564798435908</v>
+        <v>229.9565134173344</v>
       </c>
       <c r="H24" s="8" t="n">
         <v>101.579767266653</v>
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>0.4999999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>49999.99999999999</v>
+        <v>50000</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-08 06:37</t>
+          <t>Son Güncelleme: 2026-09-09 06:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1449,25 +1449,25 @@
         <v>215.1000061035156</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.0905328984785914</v>
+        <v>-0.09053290447698591</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.0354565735575836</v>
+        <v>0.0354565230645036</v>
       </c>
       <c r="G8" s="16" t="n">
         <v>0.1259383002873109</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>195.6263790882017</v>
+        <v>195.626377797947</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>222.7267152921616</v>
+        <v>222.7267044310998</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>242.1893352639826</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>195.6263790882017</v>
+        <v>195.626377797947</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="M8" s="14" t="n">
-        <v>65.78</v>
+        <v>69.28</v>
       </c>
       <c r="N8" s="14" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>0.0493707647628267</v>
       </c>
       <c r="G9" s="16" t="n">
-        <v>0.2407264600600418</v>
+        <v>0.2407265379940244</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>377.0949406620862</v>
@@ -1521,10 +1521,10 @@
         <v>407.6805421103582</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>482.0222297333262</v>
+        <v>482.0222600106785</v>
       </c>
       <c r="K9" s="15" t="n">
-        <v>367.6046449578748</v>
+        <v>367.6046449578747</v>
       </c>
       <c r="L9" s="14" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="M9" s="14" t="n">
-        <v>65.78</v>
+        <v>69.28</v>
       </c>
       <c r="N9" s="14" t="inlineStr">
         <is>
@@ -1566,19 +1566,19 @@
         <v>0.0079654248712648</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>0.0485935360435065</v>
+        <v>0.0485933210137139</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>0.0892150917049894</v>
+        <v>0.0892150802528868</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>419.0616253902284</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>435.9527626100879</v>
+        <v>435.9526732114516</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>452.8411743763493</v>
+        <v>452.8411696151377</v>
       </c>
       <c r="K10" s="15" t="n">
         <v>394.9625</v>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="M10" s="14" t="n">
-        <v>65.78</v>
+        <v>69.28</v>
       </c>
       <c r="N10" s="14" t="inlineStr">
         <is>
@@ -1620,25 +1620,25 @@
         <v>92.59999847412109</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>-0.077838466384963</v>
+        <v>-0.07783841193174081</v>
       </c>
       <c r="F11" s="19" t="n">
         <v>0.0224111679198997</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>0.094045958010278</v>
+        <v>0.0940460207708569</v>
       </c>
       <c r="H11" s="18" t="n">
-        <v>85.3921566056456</v>
+        <v>85.39216164801388</v>
       </c>
       <c r="I11" s="18" t="n">
         <v>94.67527258930708</v>
       </c>
       <c r="J11" s="18" t="n">
-        <v>101.3086540423701</v>
+        <v>101.3086598539996</v>
       </c>
       <c r="K11" s="18" t="n">
-        <v>85.3921566056456</v>
+        <v>85.39216164801388</v>
       </c>
       <c r="L11" s="17" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         </is>
       </c>
       <c r="M11" s="17" t="n">
-        <v>65.78</v>
+        <v>69.28</v>
       </c>
       <c r="N11" s="17" t="inlineStr">
         <is>
@@ -1677,25 +1677,25 @@
         <v>37.20000076293945</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>-0.0609999645366716</v>
+        <v>-0.061000020827669</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>-0.0367800783516739</v>
+        <v>-0.0367800335642668</v>
       </c>
       <c r="G12" s="22" t="n">
-        <v>0.0704910572228887</v>
+        <v>0.070491024415195</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>34.93080203563599</v>
+        <v>34.93079994161084</v>
       </c>
       <c r="I12" s="21" t="n">
-        <v>35.83178182019621</v>
+        <v>35.83178348628779</v>
       </c>
       <c r="J12" s="21" t="n">
-        <v>39.82226814541132</v>
+        <v>39.82226692496509</v>
       </c>
       <c r="K12" s="21" t="n">
-        <v>34.93080203563599</v>
+        <v>34.93079994161084</v>
       </c>
       <c r="L12" s="20" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="M12" s="20" t="n">
-        <v>65.78</v>
+        <v>69.28</v>
       </c>
       <c r="N12" s="20" t="inlineStr">
         <is>
@@ -1734,25 +1734,25 @@
         <v>71.84999847412109</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>-0.1210647833847655</v>
+        <v>-0.1210647605252412</v>
       </c>
       <c r="F13" s="22" t="n">
         <v>-0.031845613590586</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.0678617521643783</v>
+        <v>0.0678617289923662</v>
       </c>
       <c r="H13" s="21" t="n">
-        <v>63.15149397265589</v>
+        <v>63.15149561511268</v>
       </c>
       <c r="I13" s="21" t="n">
         <v>69.56189118623004</v>
       </c>
       <c r="J13" s="21" t="n">
-        <v>76.72586526358286</v>
+        <v>76.72586359867383</v>
       </c>
       <c r="K13" s="21" t="n">
-        <v>63.15149397265589</v>
+        <v>63.15149561511268</v>
       </c>
       <c r="L13" s="20" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="M13" s="20" t="n">
-        <v>65.78</v>
+        <v>69.28</v>
       </c>
       <c r="N13" s="20" t="inlineStr">
         <is>
@@ -1794,22 +1794,22 @@
         <v>0.002524799493457</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>0.09195747824944769</v>
+        <v>0.0919574997942756</v>
       </c>
       <c r="G14" s="16" t="n">
-        <v>0.1760202663201471</v>
+        <v>0.1760203643556419</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>389.2302534033346</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>423.9524909303481</v>
+        <v>423.9524992951275</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>456.5898683987971</v>
+        <v>456.589906461078</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>364.6187335307732</v>
+        <v>364.6187335307733</v>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="M14" s="14" t="n">
-        <v>65.78</v>
+        <v>69.28</v>
       </c>
       <c r="N14" s="14" t="inlineStr">
         <is>
@@ -1851,19 +1851,19 @@
         <v>-0.0371959299442395</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>0.0233118944998451</v>
+        <v>0.0233118283326481</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>0.1272217020935506</v>
+        <v>0.1272216922975995</v>
       </c>
       <c r="H15" s="18" t="n">
         <v>126.5124489288372</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>134.4631766914795</v>
+        <v>134.4631679971102</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>148.1169247750773</v>
+        <v>148.1169234878894</v>
       </c>
       <c r="K15" s="18" t="n">
         <v>124.8299942016602</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="M15" s="17" t="n">
-        <v>65.78</v>
+        <v>69.28</v>
       </c>
       <c r="N15" s="17" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="M16" s="20" t="n">
-        <v>65.78</v>
+        <v>69.28</v>
       </c>
       <c r="N16" s="20" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>98.15000152587891</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>0.0159447965491297</v>
+        <v>0.0159447519982732</v>
       </c>
       <c r="F17" s="16" t="n">
         <v>0.0349441231528639</v>
@@ -1971,7 +1971,7 @@
         <v>0.0633663517413753</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>99.71498333150582</v>
+        <v>99.71497895883918</v>
       </c>
       <c r="I17" s="15" t="n">
         <v>101.579767266653</v>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="M17" s="14" t="n">
-        <v>65.78</v>
+        <v>69.28</v>
       </c>
       <c r="N17" s="14" t="inlineStr">
         <is>
@@ -2019,25 +2019,25 @@
         <v>274.25</v>
       </c>
       <c r="E18" s="25" t="n">
-        <v>-0.0919187004373557</v>
+        <v>-0.0919187463392733</v>
       </c>
       <c r="F18" s="25" t="n">
-        <v>-0.0127046702754232</v>
+        <v>-0.0127047496231476</v>
       </c>
       <c r="G18" s="25" t="n">
-        <v>0.0358074491049085</v>
+        <v>0.035807354318896</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>249.0412964050552</v>
+        <v>249.0412838164543</v>
       </c>
       <c r="I18" s="24" t="n">
-        <v>270.7657441769652</v>
+        <v>270.7657224158518</v>
       </c>
       <c r="J18" s="24" t="n">
-        <v>284.0701929170212</v>
+        <v>284.0701669219572</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>249.0412964050552</v>
+        <v>249.0412838164543</v>
       </c>
       <c r="L18" s="23" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="M18" s="23" t="n">
-        <v>65.78</v>
+        <v>69.28</v>
       </c>
       <c r="N18" s="23" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-08 06:37</t>
+          <t>Son Güncelleme: 2026-09-09 06:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="J4" s="16" t="n">
-        <v>0.0190914915961079</v>
+        <v>0.0190914915961077</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.0354565735575836</v>
+        <v>0.0354565230645036</v>
       </c>
     </row>
     <row r="5">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="J5" s="16" t="n">
-        <v>0.026892348831564</v>
+        <v>0.0268923488315641</v>
       </c>
       <c r="K5" s="16" t="n">
         <v>0.0493707647628267</v>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="J6" s="16" t="n">
-        <v>0.0190904094969909</v>
+        <v>0.019090409496991</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>0.0485935360435065</v>
+        <v>0.0485933210137139</v>
       </c>
     </row>
     <row r="7">
@@ -2389,7 +2389,7 @@
         <v>0.0225289601725182</v>
       </c>
       <c r="K8" s="22" t="n">
-        <v>-0.0367800783516739</v>
+        <v>-0.0367800335642668</v>
       </c>
     </row>
     <row r="9">
@@ -2429,7 +2429,7 @@
         </is>
       </c>
       <c r="J9" s="22" t="n">
-        <v>0.0235158526951286</v>
+        <v>0.0235158526951287</v>
       </c>
       <c r="K9" s="22" t="n">
         <v>-0.031845613590586</v>
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="J10" s="16" t="n">
-        <v>0.0304330540492296</v>
+        <v>0.0304330540492295</v>
       </c>
       <c r="K10" s="16" t="n">
-        <v>0.09195747824944769</v>
+        <v>0.0919574997942756</v>
       </c>
     </row>
     <row r="11">
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="J11" s="19" t="n">
-        <v>0.0166997058172155</v>
+        <v>0.0166997058172156</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>0.0233118944998451</v>
+        <v>0.0233118283326481</v>
       </c>
     </row>
     <row r="12">
@@ -2647,7 +2647,7 @@
         <v>0.0189257716431987</v>
       </c>
       <c r="K14" s="27" t="n">
-        <v>0.0258271702581398</v>
+        <v>0.0258271723736069</v>
       </c>
     </row>
     <row r="15">
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="J15" s="25" t="n">
-        <v>0.0231990748681045</v>
+        <v>0.0231990748681046</v>
       </c>
       <c r="K15" s="25" t="n">
-        <v>-0.0127046702754232</v>
+        <v>-0.0127047496231476</v>
       </c>
     </row>
     <row r="16">
@@ -2819,7 +2819,7 @@
         <v>0.0155382958378264</v>
       </c>
       <c r="K18" s="27" t="n">
-        <v>0.08996540449809751</v>
+        <v>0.08996539672856251</v>
       </c>
     </row>
     <row r="19">
@@ -2862,7 +2862,7 @@
         <v>0.0127081504930393</v>
       </c>
       <c r="K19" s="27" t="n">
-        <v>0.0999999916062814</v>
+        <v>0.1000000839371915</v>
       </c>
     </row>
     <row r="20">
@@ -2938,7 +2938,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-08 06:37</t>
+          <t>Son Güncelleme: 2026-09-09 06:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3057,7 +3057,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-08 06:37</t>
+          <t>Son Güncelleme: 2026-09-09 06:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3308,7 +3308,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-08 06:37</t>
+          <t>Son Güncelleme: 2026-09-09 06:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14151.599609375</v>
+        <v>14405.2998046875</v>
       </c>
     </row>
     <row r="5">
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13362.80402832031</v>
+        <v>13381.18752929687</v>
       </c>
     </row>
     <row r="6">
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>65.78</v>
+        <v>69.28</v>
       </c>
     </row>
     <row r="9">
@@ -3433,7 +3433,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-08 06:37</t>
+          <t>Son Güncelleme: 2026-09-09 06:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3510,7 +3510,7 @@
         <v>-19838.29062106635</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>11314225.18217773</v>
+        <v>11489854.14120302</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0.0225044067881641</v>
@@ -3540,7 +3540,7 @@
         <v>267029.7336462075</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>11314225.18217773</v>
+        <v>11489854.14120302</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0.0225044067881641</v>
@@ -3570,7 +3570,7 @@
         <v>941159.3549911883</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>11314225.18217773</v>
+        <v>11489854.14120302</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0.0225044067881641</v>
@@ -3600,7 +3600,7 @@
         <v>1628.565106133465</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>11314225.18217773</v>
+        <v>11489854.14120302</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0.0225044067881641</v>
@@ -3630,7 +3630,7 @@
         <v>-158444.7897232156</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>11314225.18217773</v>
+        <v>11489854.14120302</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0.0225044067881641</v>
@@ -3660,7 +3660,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>11314225.18217773</v>
+        <v>11489854.14120302</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0.0225044067881641</v>
